--- a/public/plantilla-permiso-trabajo.xlsx
+++ b/public/plantilla-permiso-trabajo.xlsx
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="27">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -212,8 +212,48 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00404040"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001B2A45"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -286,8 +326,62 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E36C09"/>
+        <bgColor rgb="00E36C09"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007030A0"/>
+        <bgColor rgb="007030A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00548235"/>
+        <bgColor rgb="00548235"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007F4F24"/>
+        <bgColor rgb="007F4F24"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000070C0"/>
+        <bgColor rgb="000070C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00595959"/>
+        <bgColor rgb="00595959"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="27">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -589,6 +683,64 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="009AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="009AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="009AA3B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009AA3B2"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009AA3B2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="009AA3B2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009AA3B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009AA3B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="009AA3B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009AA3B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -598,7 +750,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -890,6 +1042,46 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -899,6 +1091,104 @@
     <cellStyle name="Normal 4" xfId="4"/>
     <cellStyle name="Normal 6 2" xfId="5"/>
   </cellStyles>
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C00000"/>
+          <bgColor rgb="00C00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E36C09"/>
+          <bgColor rgb="00E36C09"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="007030A0"/>
+          <bgColor rgb="007030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC000"/>
+          <bgColor rgb="00FFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00548235"/>
+          <bgColor rgb="00548235"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="007F4F24"/>
+          <bgColor rgb="007F4F24"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="000070C0"/>
+          <bgColor rgb="000070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00595959"/>
+          <bgColor rgb="00595959"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
@@ -920,7 +1210,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="1" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -930,13 +1220,7 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2630233" cy="1259205"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1248,21 +1532,21 @@
     <tabColor theme="4" tint="0.3999755851924192"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L77"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <dimension ref="A1:L74"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.77734375" customWidth="1" style="70" min="1" max="1"/>
-    <col width="13" customWidth="1" style="70" min="2" max="3"/>
-    <col width="15.77734375" customWidth="1" style="70" min="4" max="4"/>
+    <col width="12.78" customWidth="1" style="70" min="1" max="1"/>
+    <col width="13" customWidth="1" style="70" min="2" max="2"/>
+    <col width="13" customWidth="1" style="70" min="3" max="3"/>
+    <col width="15.78" customWidth="1" style="70" min="4" max="4"/>
     <col width="10" customWidth="1" style="70" min="5" max="5"/>
-    <col width="15.77734375" customWidth="1" style="70" min="6" max="6"/>
+    <col width="15.78" customWidth="1" style="70" min="6" max="6"/>
     <col width="11" customWidth="1" style="70" min="7" max="7"/>
-    <col width="15.77734375" customWidth="1" style="70" min="8" max="8"/>
+    <col width="15.78" customWidth="1" style="70" min="8" max="8"/>
     <col width="10" customWidth="1" style="70" min="9" max="9"/>
-    <col width="15.77734375" customWidth="1" style="70" min="10" max="10"/>
+    <col width="15.78" customWidth="1" style="70" min="10" max="10"/>
     <col width="12" customWidth="1" style="70" min="11" max="11"/>
     <col width="13" customWidth="1" style="70" min="12" max="12"/>
-    <col width="8.88671875" customWidth="1" style="70" min="13" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="40.05" customHeight="1" s="70">
@@ -1380,7 +1664,7 @@
     <row r="9" ht="15" customHeight="1" s="70">
       <c r="A9" s="103" t="inlineStr">
         <is>
-          <t>Autorización escrita antes de iniciar: alturas, caliente, espacios confinados, excavaciones y energías peligrosas · Decreto 1072 de 2015 · Resolución 4272 de 2021</t>
+          <t>Autorización escrita antes de iniciar el trabajo · Decreto 1072 de 2015 · Resolución 4272 de 2021 (alturas)</t>
         </is>
       </c>
       <c r="B9" s="115" t="n"/>
@@ -1395,142 +1679,142 @@
       <c r="K9" s="115" t="n"/>
       <c r="L9" s="116" t="n"/>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="70">
-      <c r="A10" s="54" t="inlineStr">
+    <row r="10" ht="30" customHeight="1" s="70">
+      <c r="A10" s="117" t="inlineStr">
+        <is>
+          <t>TIPO DE PERMISO DE TRABAJO</t>
+        </is>
+      </c>
+      <c r="B10" s="38" t="n"/>
+      <c r="C10" s="47" t="n"/>
+      <c r="D10" s="118" t="n"/>
+      <c r="E10" s="131" t="n"/>
+      <c r="F10" s="131" t="n"/>
+      <c r="G10" s="131" t="n"/>
+      <c r="H10" s="131" t="n"/>
+      <c r="I10" s="131" t="n"/>
+      <c r="J10" s="131" t="n"/>
+      <c r="K10" s="131" t="n"/>
+      <c r="L10" s="132" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="70">
+      <c r="A11" s="54" t="inlineStr">
         <is>
           <t>1. DATOS DEL PERMISO</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n"/>
-      <c r="C10" s="38" t="n"/>
-      <c r="D10" s="38" t="n"/>
-      <c r="E10" s="38" t="n"/>
-      <c r="F10" s="38" t="n"/>
-      <c r="G10" s="38" t="n"/>
-      <c r="H10" s="38" t="n"/>
-      <c r="I10" s="38" t="n"/>
-      <c r="J10" s="38" t="n"/>
-      <c r="K10" s="38" t="n"/>
-      <c r="L10" s="47" t="n"/>
-    </row>
-    <row r="11" ht="21" customHeight="1" s="70">
-      <c r="A11" s="33" t="inlineStr">
-        <is>
-          <t>Proyecto / Obra</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="50" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="30" t="n"/>
-      <c r="H11" s="30" t="n"/>
-      <c r="I11" s="30" t="n"/>
-      <c r="J11" s="30" t="n"/>
-      <c r="K11" s="30" t="n"/>
-      <c r="L11" s="31" t="n"/>
+      <c r="B11" s="38" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="38" t="n"/>
+      <c r="E11" s="38" t="n"/>
+      <c r="F11" s="38" t="n"/>
+      <c r="G11" s="38" t="n"/>
+      <c r="H11" s="38" t="n"/>
+      <c r="I11" s="38" t="n"/>
+      <c r="J11" s="38" t="n"/>
+      <c r="K11" s="38" t="n"/>
+      <c r="L11" s="47" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="70">
       <c r="A12" s="33" t="inlineStr">
         <is>
-          <t>Contratista / Empresa</t>
+          <t>Proyecto / Obra</t>
         </is>
       </c>
       <c r="B12" s="31" t="n"/>
-      <c r="C12" s="43" t="n"/>
+      <c r="C12" s="50" t="n"/>
       <c r="D12" s="30" t="n"/>
       <c r="E12" s="30" t="n"/>
       <c r="F12" s="30" t="n"/>
-      <c r="G12" s="31" t="n"/>
-      <c r="H12" s="33" t="inlineStr">
-        <is>
-          <t>Ubicación</t>
-        </is>
-      </c>
-      <c r="I12" s="31" t="n"/>
-      <c r="J12" s="43" t="n"/>
+      <c r="G12" s="30" t="n"/>
+      <c r="H12" s="30" t="n"/>
+      <c r="I12" s="30" t="n"/>
+      <c r="J12" s="30" t="n"/>
       <c r="K12" s="30" t="n"/>
       <c r="L12" s="31" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="70">
       <c r="A13" s="33" t="inlineStr">
         <is>
-          <t>N° de permiso</t>
+          <t>Contratista / Empresa</t>
         </is>
       </c>
       <c r="B13" s="31" t="n"/>
-      <c r="C13" s="48" t="n"/>
-      <c r="D13" s="33" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="E13" s="48" t="n"/>
-      <c r="F13" s="33" t="inlineStr">
-        <is>
-          <t>Hora inicio</t>
-        </is>
-      </c>
-      <c r="G13" s="48" t="n"/>
+      <c r="C13" s="43" t="n"/>
+      <c r="D13" s="30" t="n"/>
+      <c r="E13" s="30" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="31" t="n"/>
       <c r="H13" s="33" t="inlineStr">
         <is>
-          <t>Hora fin</t>
-        </is>
-      </c>
-      <c r="I13" s="48" t="n"/>
-      <c r="J13" s="33" t="inlineStr">
-        <is>
-          <t>Vigencia</t>
-        </is>
-      </c>
-      <c r="K13" s="48" t="n"/>
+          <t>Ubicación</t>
+        </is>
+      </c>
+      <c r="I13" s="31" t="n"/>
+      <c r="J13" s="43" t="n"/>
+      <c r="K13" s="30" t="n"/>
       <c r="L13" s="31" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="70">
       <c r="A14" s="33" t="inlineStr">
         <is>
+          <t>N° de permiso</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="48" t="n"/>
+      <c r="D14" s="33" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="E14" s="48" t="n"/>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>Hora inicio</t>
+        </is>
+      </c>
+      <c r="G14" s="48" t="n"/>
+      <c r="H14" s="33" t="inlineStr">
+        <is>
+          <t>Hora fin</t>
+        </is>
+      </c>
+      <c r="I14" s="48" t="n"/>
+      <c r="J14" s="33" t="inlineStr">
+        <is>
+          <t>Vigencia</t>
+        </is>
+      </c>
+      <c r="K14" s="48" t="n"/>
+      <c r="L14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="21" customHeight="1" s="70">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
           <t>Frente / lugar del trabajo</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n"/>
-      <c r="C14" s="43" t="n"/>
-      <c r="D14" s="30" t="n"/>
-      <c r="E14" s="30" t="n"/>
-      <c r="F14" s="30" t="n"/>
-      <c r="G14" s="31" t="n"/>
-      <c r="H14" s="33" t="inlineStr">
-        <is>
-          <t>Altura o profundidad (m)</t>
-        </is>
-      </c>
-      <c r="I14" s="31" t="n"/>
-      <c r="J14" s="43" t="n"/>
-      <c r="K14" s="30" t="n"/>
-      <c r="L14" s="31" t="n"/>
-    </row>
-    <row r="15" ht="36" customHeight="1" s="70">
-      <c r="A15" s="33" t="inlineStr">
-        <is>
-          <t>Descripción del trabajo</t>
-        </is>
-      </c>
       <c r="B15" s="31" t="n"/>
-      <c r="C15" s="52" t="n"/>
+      <c r="C15" s="43" t="n"/>
       <c r="D15" s="30" t="n"/>
       <c r="E15" s="30" t="n"/>
       <c r="F15" s="30" t="n"/>
-      <c r="G15" s="30" t="n"/>
-      <c r="H15" s="30" t="n"/>
-      <c r="I15" s="30" t="n"/>
-      <c r="J15" s="30" t="n"/>
+      <c r="G15" s="31" t="n"/>
+      <c r="H15" s="33" t="inlineStr">
+        <is>
+          <t>Altura o profundidad (m)</t>
+        </is>
+      </c>
+      <c r="I15" s="31" t="n"/>
+      <c r="J15" s="43" t="n"/>
       <c r="K15" s="30" t="n"/>
       <c r="L15" s="31" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1" s="70">
       <c r="A16" s="33" t="inlineStr">
         <is>
-          <t>Solicitante</t>
+          <t>Equipo, sustancia o circuito</t>
         </is>
       </c>
       <c r="B16" s="31" t="n"/>
@@ -1538,25 +1822,21 @@
       <c r="D16" s="30" t="n"/>
       <c r="E16" s="30" t="n"/>
       <c r="F16" s="30" t="n"/>
-      <c r="G16" s="31" t="n"/>
-      <c r="H16" s="33" t="inlineStr">
-        <is>
-          <t>Cargo</t>
-        </is>
-      </c>
-      <c r="I16" s="31" t="n"/>
-      <c r="J16" s="43" t="n"/>
+      <c r="G16" s="30" t="n"/>
+      <c r="H16" s="30" t="n"/>
+      <c r="I16" s="30" t="n"/>
+      <c r="J16" s="30" t="n"/>
       <c r="K16" s="30" t="n"/>
       <c r="L16" s="31" t="n"/>
     </row>
-    <row r="17" ht="15" customHeight="1" s="70">
-      <c r="A17" s="88" t="inlineStr">
-        <is>
-          <t>Tipo de trabajo (marque los que apliquen)</t>
-        </is>
-      </c>
-      <c r="B17" s="30" t="n"/>
-      <c r="C17" s="30" t="n"/>
+    <row r="17" ht="36" customHeight="1" s="70">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>Descripción del trabajo</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="52" t="n"/>
       <c r="D17" s="30" t="n"/>
       <c r="E17" s="30" t="n"/>
       <c r="F17" s="30" t="n"/>
@@ -1567,125 +1847,103 @@
       <c r="K17" s="30" t="n"/>
       <c r="L17" s="31" t="n"/>
     </row>
-    <row r="18" ht="18" customHeight="1" s="70">
-      <c r="A18" s="89" t="inlineStr">
-        <is>
-          <t>☐ Trabajo en alturas</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="n"/>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="89" t="inlineStr">
-        <is>
-          <t>☐ Trabajo en caliente</t>
-        </is>
-      </c>
+    <row r="18" ht="21" customHeight="1" s="70">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>Solicitante</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="43" t="n"/>
+      <c r="D18" s="30" t="n"/>
       <c r="E18" s="30" t="n"/>
-      <c r="F18" s="31" t="n"/>
-      <c r="G18" s="89" t="inlineStr">
-        <is>
-          <t>☐ Espacios confinados</t>
-        </is>
-      </c>
-      <c r="H18" s="30" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="31" t="n"/>
+      <c r="H18" s="33" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
       <c r="I18" s="31" t="n"/>
-      <c r="J18" s="89" t="inlineStr">
-        <is>
-          <t>☐ Excavaciones y zanjas</t>
-        </is>
-      </c>
+      <c r="J18" s="43" t="n"/>
       <c r="K18" s="30" t="n"/>
       <c r="L18" s="31" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1" s="70">
-      <c r="A19" s="89" t="inlineStr">
-        <is>
-          <t>☐ Riesgo eléctrico / bloqueo (LOTO)</t>
-        </is>
-      </c>
-      <c r="B19" s="30" t="n"/>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="89" t="inlineStr">
-        <is>
-          <t>☐ Izaje de cargas</t>
-        </is>
-      </c>
-      <c r="E19" s="30" t="n"/>
-      <c r="F19" s="31" t="n"/>
-      <c r="G19" s="89" t="inlineStr">
-        <is>
-          <t>☐ Demolición o desmonte</t>
-        </is>
-      </c>
-      <c r="H19" s="30" t="n"/>
-      <c r="I19" s="31" t="n"/>
-      <c r="J19" s="89" t="inlineStr">
-        <is>
-          <t>☐ Otro: ______________</t>
-        </is>
-      </c>
-      <c r="K19" s="30" t="n"/>
-      <c r="L19" s="31" t="n"/>
-    </row>
-    <row r="20" ht="16.5" customHeight="1" s="70">
-      <c r="A20" s="54" t="inlineStr">
+    <row r="19" ht="16.5" customHeight="1" s="70">
+      <c r="A19" s="54" t="inlineStr">
         <is>
           <t>2. PERSONAL QUE EJECUTA EL TRABAJO</t>
         </is>
       </c>
-      <c r="B20" s="38" t="n"/>
-      <c r="C20" s="38" t="n"/>
-      <c r="D20" s="38" t="n"/>
-      <c r="E20" s="38" t="n"/>
-      <c r="F20" s="38" t="n"/>
-      <c r="G20" s="38" t="n"/>
-      <c r="H20" s="38" t="n"/>
-      <c r="I20" s="38" t="n"/>
-      <c r="J20" s="38" t="n"/>
-      <c r="K20" s="38" t="n"/>
-      <c r="L20" s="47" t="n"/>
-    </row>
-    <row r="21" ht="19.05" customHeight="1" s="70">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="B19" s="38" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="38" t="n"/>
+      <c r="E19" s="38" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="38" t="n"/>
+      <c r="H19" s="38" t="n"/>
+      <c r="I19" s="38" t="n"/>
+      <c r="J19" s="38" t="n"/>
+      <c r="K19" s="38" t="n"/>
+      <c r="L19" s="47" t="n"/>
+    </row>
+    <row r="20" ht="19" customHeight="1" s="70">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B21" s="34" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>Nombre completo</t>
         </is>
       </c>
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="34" t="inlineStr">
+        <is>
+          <t>Documento de identidad</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="n"/>
+      <c r="G20" s="34" t="inlineStr">
+        <is>
+          <t>Cargo / oficio</t>
+        </is>
+      </c>
+      <c r="H20" s="31" t="n"/>
+      <c r="I20" s="34" t="inlineStr">
+        <is>
+          <t>Certificación (tipo y vigencia)</t>
+        </is>
+      </c>
+      <c r="J20" s="31" t="n"/>
+      <c r="K20" s="34" t="inlineStr">
+        <is>
+          <t>Firma</t>
+        </is>
+      </c>
+      <c r="L20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1" s="70">
+      <c r="A21" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="29" t="n"/>
       <c r="C21" s="30" t="n"/>
       <c r="D21" s="31" t="n"/>
-      <c r="E21" s="34" t="inlineStr">
-        <is>
-          <t>Documento de identidad</t>
-        </is>
-      </c>
+      <c r="E21" s="29" t="n"/>
       <c r="F21" s="31" t="n"/>
-      <c r="G21" s="34" t="inlineStr">
-        <is>
-          <t>Cargo / oficio</t>
-        </is>
-      </c>
+      <c r="G21" s="29" t="n"/>
       <c r="H21" s="31" t="n"/>
-      <c r="I21" s="34" t="inlineStr">
-        <is>
-          <t>Certificación (tipo y vigencia)</t>
-        </is>
-      </c>
+      <c r="I21" s="29" t="n"/>
       <c r="J21" s="31" t="n"/>
-      <c r="K21" s="34" t="inlineStr">
-        <is>
-          <t>Firma</t>
-        </is>
-      </c>
+      <c r="K21" s="29" t="n"/>
       <c r="L21" s="31" t="n"/>
     </row>
-    <row r="22" ht="28.05" customHeight="1" s="70">
+    <row r="22" ht="28" customHeight="1" s="70">
       <c r="A22" s="57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" s="29" t="n"/>
       <c r="C22" s="30" t="n"/>
@@ -1699,9 +1957,9 @@
       <c r="K22" s="29" t="n"/>
       <c r="L22" s="31" t="n"/>
     </row>
-    <row r="23" ht="28.05" customHeight="1" s="70">
+    <row r="23" ht="28" customHeight="1" s="70">
       <c r="A23" s="57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" s="29" t="n"/>
       <c r="C23" s="30" t="n"/>
@@ -1715,9 +1973,9 @@
       <c r="K23" s="29" t="n"/>
       <c r="L23" s="31" t="n"/>
     </row>
-    <row r="24" ht="28.05" customHeight="1" s="70">
+    <row r="24" ht="28" customHeight="1" s="70">
       <c r="A24" s="57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B24" s="29" t="n"/>
       <c r="C24" s="30" t="n"/>
@@ -1731,9 +1989,9 @@
       <c r="K24" s="29" t="n"/>
       <c r="L24" s="31" t="n"/>
     </row>
-    <row r="25" ht="28.05" customHeight="1" s="70">
+    <row r="25" ht="28" customHeight="1" s="70">
       <c r="A25" s="57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B25" s="29" t="n"/>
       <c r="C25" s="30" t="n"/>
@@ -1747,9 +2005,9 @@
       <c r="K25" s="29" t="n"/>
       <c r="L25" s="31" t="n"/>
     </row>
-    <row r="26" ht="28.05" customHeight="1" s="70">
+    <row r="26" ht="28" customHeight="1" s="70">
       <c r="A26" s="57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B26" s="29" t="n"/>
       <c r="C26" s="30" t="n"/>
@@ -1763,49 +2021,61 @@
       <c r="K26" s="29" t="n"/>
       <c r="L26" s="31" t="n"/>
     </row>
-    <row r="27" ht="28.05" customHeight="1" s="70">
-      <c r="A27" s="57" t="n">
-        <v>6</v>
-      </c>
-      <c r="B27" s="29" t="n"/>
-      <c r="C27" s="30" t="n"/>
-      <c r="D27" s="31" t="n"/>
-      <c r="E27" s="29" t="n"/>
-      <c r="F27" s="31" t="n"/>
-      <c r="G27" s="29" t="n"/>
-      <c r="H27" s="31" t="n"/>
-      <c r="I27" s="29" t="n"/>
-      <c r="J27" s="31" t="n"/>
-      <c r="K27" s="29" t="n"/>
-      <c r="L27" s="31" t="n"/>
-    </row>
-    <row r="28" ht="16.5" customHeight="1" s="70">
-      <c r="A28" s="54" t="inlineStr">
+    <row r="27" ht="16.5" customHeight="1" s="70">
+      <c r="A27" s="54" t="inlineStr">
         <is>
           <t>3. VERIFICACIÓN PREVIA (antes de iniciar)</t>
         </is>
       </c>
-      <c r="B28" s="38" t="n"/>
-      <c r="C28" s="38" t="n"/>
-      <c r="D28" s="38" t="n"/>
-      <c r="E28" s="38" t="n"/>
-      <c r="F28" s="38" t="n"/>
-      <c r="G28" s="38" t="n"/>
-      <c r="H28" s="38" t="n"/>
-      <c r="I28" s="38" t="n"/>
-      <c r="J28" s="38" t="n"/>
-      <c r="K28" s="38" t="n"/>
-      <c r="L28" s="47" t="n"/>
-    </row>
-    <row r="29" ht="19.05" customHeight="1" s="70">
-      <c r="A29" s="34" t="inlineStr">
+      <c r="B27" s="38" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="38" t="n"/>
+      <c r="E27" s="38" t="n"/>
+      <c r="F27" s="38" t="n"/>
+      <c r="G27" s="38" t="n"/>
+      <c r="H27" s="38" t="n"/>
+      <c r="I27" s="38" t="n"/>
+      <c r="J27" s="38" t="n"/>
+      <c r="K27" s="38" t="n"/>
+      <c r="L27" s="47" t="n"/>
+    </row>
+    <row r="28" ht="19" customHeight="1" s="70">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B29" s="34" t="inlineStr">
+      <c r="B28" s="34" t="inlineStr">
         <is>
           <t>Condición que se verifica</t>
+        </is>
+      </c>
+      <c r="C28" s="30" t="n"/>
+      <c r="D28" s="30" t="n"/>
+      <c r="E28" s="30" t="n"/>
+      <c r="F28" s="30" t="n"/>
+      <c r="G28" s="30" t="n"/>
+      <c r="H28" s="31" t="n"/>
+      <c r="I28" s="34" t="inlineStr">
+        <is>
+          <t>¿Cumple?</t>
+        </is>
+      </c>
+      <c r="J28" s="31" t="n"/>
+      <c r="K28" s="34" t="inlineStr">
+        <is>
+          <t>Observación</t>
+        </is>
+      </c>
+      <c r="L28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="17" customHeight="1" s="70">
+      <c r="A29" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="89" t="inlineStr">
+        <is>
+          <t>ATS elaborado, socializado y firmado por todo el personal que ejecuta</t>
         </is>
       </c>
       <c r="C29" s="30" t="n"/>
@@ -1814,26 +2084,18 @@
       <c r="F29" s="30" t="n"/>
       <c r="G29" s="30" t="n"/>
       <c r="H29" s="31" t="n"/>
-      <c r="I29" s="34" t="inlineStr">
-        <is>
-          <t>¿Cumple?</t>
-        </is>
-      </c>
+      <c r="I29" s="57" t="n"/>
       <c r="J29" s="31" t="n"/>
-      <c r="K29" s="34" t="inlineStr">
-        <is>
-          <t>Observación</t>
-        </is>
-      </c>
+      <c r="K29" s="29" t="n"/>
       <c r="L29" s="31" t="n"/>
     </row>
-    <row r="30" ht="16.95" customHeight="1" s="70">
+    <row r="30" ht="17" customHeight="1" s="70">
       <c r="A30" s="57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B30" s="89" t="inlineStr">
         <is>
-          <t>ATS elaborado, socializado y firmado por todo el personal que ejecuta</t>
+          <t>Personal con aptitud médica y capacitación o certificación vigente para este trabajo</t>
         </is>
       </c>
       <c r="C30" s="30" t="n"/>
@@ -1847,13 +2109,13 @@
       <c r="K30" s="29" t="n"/>
       <c r="L30" s="31" t="n"/>
     </row>
-    <row r="31" ht="16.95" customHeight="1" s="70">
+    <row r="31" ht="17" customHeight="1" s="70">
       <c r="A31" s="57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B31" s="89" t="inlineStr">
         <is>
-          <t>Personal con aptitud médica y capacitación o certificación vigente para este trabajo</t>
+          <t>Elementos de protección personal completos, certificados y en buen estado</t>
         </is>
       </c>
       <c r="C31" s="30" t="n"/>
@@ -1867,13 +2129,13 @@
       <c r="K31" s="29" t="n"/>
       <c r="L31" s="31" t="n"/>
     </row>
-    <row r="32" ht="16.95" customHeight="1" s="70">
+    <row r="32" ht="17" customHeight="1" s="70">
       <c r="A32" s="57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B32" s="89" t="inlineStr">
         <is>
-          <t>Elementos de protección personal completos, certificados y en buen estado</t>
+          <t>Área demarcada, señalizada y con acceso restringido a personas ajenas</t>
         </is>
       </c>
       <c r="C32" s="30" t="n"/>
@@ -1887,13 +2149,13 @@
       <c r="K32" s="29" t="n"/>
       <c r="L32" s="31" t="n"/>
     </row>
-    <row r="33" ht="16.95" customHeight="1" s="70">
+    <row r="33" ht="17" customHeight="1" s="70">
       <c r="A33" s="57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B33" s="89" t="inlineStr">
         <is>
-          <t>Área demarcada, señalizada y con acceso restringido a personas ajenas</t>
+          <t>Herramientas, equipos y sistemas de protección inspeccionados</t>
         </is>
       </c>
       <c r="C33" s="30" t="n"/>
@@ -1907,13 +2169,13 @@
       <c r="K33" s="29" t="n"/>
       <c r="L33" s="31" t="n"/>
     </row>
-    <row r="34" ht="16.95" customHeight="1" s="70">
+    <row r="34" ht="17" customHeight="1" s="70">
       <c r="A34" s="57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B34" s="89" t="inlineStr">
         <is>
-          <t>Herramientas, equipos y sistemas de protección inspeccionados</t>
+          <t>Plan de emergencia y de rescate conocido; medio de comunicación disponible</t>
         </is>
       </c>
       <c r="C34" s="30" t="n"/>
@@ -1927,13 +2189,13 @@
       <c r="K34" s="29" t="n"/>
       <c r="L34" s="31" t="n"/>
     </row>
-    <row r="35" ht="16.95" customHeight="1" s="70">
+    <row r="35" ht="17" customHeight="1" s="70">
       <c r="A35" s="57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B35" s="89" t="inlineStr">
         <is>
-          <t>Plan de emergencia y de rescate conocido; medio de comunicación disponible</t>
+          <t>Extintor y botiquín disponibles en el sitio del trabajo</t>
         </is>
       </c>
       <c r="C35" s="30" t="n"/>
@@ -1947,13 +2209,13 @@
       <c r="K35" s="29" t="n"/>
       <c r="L35" s="31" t="n"/>
     </row>
-    <row r="36" ht="16.95" customHeight="1" s="70">
+    <row r="36" ht="17" customHeight="1" s="70">
       <c r="A36" s="57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B36" s="89" t="inlineStr">
         <is>
-          <t>Extintor y botiquín disponibles en el sitio del trabajo</t>
+          <t>Condiciones del entorno evaluadas (lluvia, viento, tormenta eléctrica)</t>
         </is>
       </c>
       <c r="C36" s="30" t="n"/>
@@ -1967,13 +2229,13 @@
       <c r="K36" s="29" t="n"/>
       <c r="L36" s="31" t="n"/>
     </row>
-    <row r="37" ht="16.95" customHeight="1" s="70">
+    <row r="37" ht="17" customHeight="1" s="70">
       <c r="A37" s="57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B37" s="89" t="inlineStr">
         <is>
-          <t>Condiciones del entorno evaluadas (lluvia, viento, tormenta eléctrica)</t>
+          <t>Permisos complementarios tramitados y adjuntos (si aplica)</t>
         </is>
       </c>
       <c r="C37" s="30" t="n"/>
@@ -1987,13 +2249,13 @@
       <c r="K37" s="29" t="n"/>
       <c r="L37" s="31" t="n"/>
     </row>
-    <row r="38" ht="16.95" customHeight="1" s="70">
+    <row r="38" ht="17" customHeight="1" s="70">
       <c r="A38" s="57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B38" s="89" t="inlineStr">
         <is>
-          <t>Permisos complementarios tramitados y adjuntos (si aplica)</t>
+          <t>Coordinación con otras actividades simultáneas en el área</t>
         </is>
       </c>
       <c r="C38" s="30" t="n"/>
@@ -2007,534 +2269,512 @@
       <c r="K38" s="29" t="n"/>
       <c r="L38" s="31" t="n"/>
     </row>
-    <row r="39" ht="16.95" customHeight="1" s="70">
-      <c r="A39" s="57" t="n">
-        <v>10</v>
-      </c>
-      <c r="B39" s="89" t="inlineStr">
-        <is>
-          <t>Coordinación con otras actividades simultáneas en el área</t>
-        </is>
-      </c>
-      <c r="C39" s="30" t="n"/>
-      <c r="D39" s="30" t="n"/>
-      <c r="E39" s="30" t="n"/>
-      <c r="F39" s="30" t="n"/>
-      <c r="G39" s="30" t="n"/>
-      <c r="H39" s="31" t="n"/>
-      <c r="I39" s="57" t="n"/>
-      <c r="J39" s="31" t="n"/>
-      <c r="K39" s="29" t="n"/>
-      <c r="L39" s="31" t="n"/>
-    </row>
-    <row r="40" ht="16.5" customHeight="1" s="70">
-      <c r="A40" s="54" t="inlineStr">
-        <is>
-          <t>4. VERIFICACIÓN ESPECÍFICA (solo lo que aplique al tipo de trabajo)</t>
-        </is>
-      </c>
-      <c r="B40" s="38" t="n"/>
-      <c r="C40" s="38" t="n"/>
-      <c r="D40" s="38" t="n"/>
-      <c r="E40" s="38" t="n"/>
-      <c r="F40" s="38" t="n"/>
-      <c r="G40" s="38" t="n"/>
-      <c r="H40" s="38" t="n"/>
-      <c r="I40" s="38" t="n"/>
-      <c r="J40" s="38" t="n"/>
-      <c r="K40" s="38" t="n"/>
-      <c r="L40" s="47" t="n"/>
-    </row>
-    <row r="41" ht="19.05" customHeight="1" s="70">
-      <c r="A41" s="34" t="inlineStr">
+    <row r="39" ht="16.5" customHeight="1" s="70">
+      <c r="A39" s="54" t="inlineStr">
+        <is>
+          <t>4. REQUISITOS ESPECÍFICOS DEL PERMISO (según el tipo elegido arriba)</t>
+        </is>
+      </c>
+      <c r="B39" s="38" t="n"/>
+      <c r="C39" s="38" t="n"/>
+      <c r="D39" s="38" t="n"/>
+      <c r="E39" s="38" t="n"/>
+      <c r="F39" s="38" t="n"/>
+      <c r="G39" s="38" t="n"/>
+      <c r="H39" s="38" t="n"/>
+      <c r="I39" s="38" t="n"/>
+      <c r="J39" s="38" t="n"/>
+      <c r="K39" s="38" t="n"/>
+      <c r="L39" s="47" t="n"/>
+    </row>
+    <row r="40" ht="19" customHeight="1" s="70">
+      <c r="A40" s="34" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B41" s="34" t="inlineStr">
-        <is>
-          <t>Condición que se verifica</t>
-        </is>
-      </c>
+      <c r="B40" s="34" t="inlineStr">
+        <is>
+          <t>Requisito</t>
+        </is>
+      </c>
+      <c r="C40" s="30" t="n"/>
+      <c r="D40" s="30" t="n"/>
+      <c r="E40" s="30" t="n"/>
+      <c r="F40" s="30" t="n"/>
+      <c r="G40" s="31" t="n"/>
+      <c r="H40" s="34" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="I40" s="34" t="inlineStr">
+        <is>
+          <t>No cumple</t>
+        </is>
+      </c>
+      <c r="J40" s="34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K40" s="34" t="inlineStr">
+        <is>
+          <t>Observación</t>
+        </is>
+      </c>
+      <c r="L40" s="31" t="n"/>
+    </row>
+    <row r="41" ht="24" customHeight="1" s="70">
+      <c r="A41" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" s="89" t="n"/>
       <c r="C41" s="30" t="n"/>
       <c r="D41" s="30" t="n"/>
       <c r="E41" s="30" t="n"/>
       <c r="F41" s="30" t="n"/>
-      <c r="G41" s="30" t="n"/>
-      <c r="H41" s="31" t="n"/>
-      <c r="I41" s="34" t="inlineStr">
-        <is>
-          <t>¿Cumple?</t>
-        </is>
-      </c>
-      <c r="J41" s="31" t="n"/>
-      <c r="K41" s="34" t="inlineStr">
-        <is>
-          <t>Observación</t>
-        </is>
-      </c>
+      <c r="G41" s="31" t="n"/>
+      <c r="H41" s="57" t="n"/>
+      <c r="I41" s="57" t="n"/>
+      <c r="J41" s="57" t="n"/>
+      <c r="K41" s="29" t="n"/>
       <c r="L41" s="31" t="n"/>
     </row>
-    <row r="42" ht="16.95" customHeight="1" s="70">
+    <row r="42" ht="24" customHeight="1" s="70">
       <c r="A42" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="B42" s="89" t="inlineStr">
-        <is>
-          <t>ALTURAS · Puntos de anclaje certificados; arnés, eslingas y línea de vida inspeccionados</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B42" s="89" t="n"/>
       <c r="C42" s="30" t="n"/>
       <c r="D42" s="30" t="n"/>
       <c r="E42" s="30" t="n"/>
       <c r="F42" s="30" t="n"/>
-      <c r="G42" s="30" t="n"/>
-      <c r="H42" s="31" t="n"/>
+      <c r="G42" s="31" t="n"/>
+      <c r="H42" s="57" t="n"/>
       <c r="I42" s="57" t="n"/>
-      <c r="J42" s="31" t="n"/>
+      <c r="J42" s="57" t="n"/>
       <c r="K42" s="29" t="n"/>
       <c r="L42" s="31" t="n"/>
     </row>
-    <row r="43" ht="16.95" customHeight="1" s="70">
+    <row r="43" ht="24" customHeight="1" s="70">
       <c r="A43" s="57" t="n">
-        <v>2</v>
-      </c>
-      <c r="B43" s="89" t="inlineStr">
-        <is>
-          <t>ALTURAS · Andamios o plataformas certificados y con tarjeta de inspección</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B43" s="89" t="n"/>
       <c r="C43" s="30" t="n"/>
       <c r="D43" s="30" t="n"/>
       <c r="E43" s="30" t="n"/>
       <c r="F43" s="30" t="n"/>
-      <c r="G43" s="30" t="n"/>
-      <c r="H43" s="31" t="n"/>
+      <c r="G43" s="31" t="n"/>
+      <c r="H43" s="57" t="n"/>
       <c r="I43" s="57" t="n"/>
-      <c r="J43" s="31" t="n"/>
+      <c r="J43" s="57" t="n"/>
       <c r="K43" s="29" t="n"/>
       <c r="L43" s="31" t="n"/>
     </row>
-    <row r="44" ht="16.95" customHeight="1" s="70">
+    <row r="44" ht="24" customHeight="1" s="70">
       <c r="A44" s="57" t="n">
-        <v>3</v>
-      </c>
-      <c r="B44" s="89" t="inlineStr">
-        <is>
-          <t>ALTURAS · Equipo y personal de rescate en alturas disponibles</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B44" s="89" t="n"/>
       <c r="C44" s="30" t="n"/>
       <c r="D44" s="30" t="n"/>
       <c r="E44" s="30" t="n"/>
       <c r="F44" s="30" t="n"/>
-      <c r="G44" s="30" t="n"/>
-      <c r="H44" s="31" t="n"/>
+      <c r="G44" s="31" t="n"/>
+      <c r="H44" s="57" t="n"/>
       <c r="I44" s="57" t="n"/>
-      <c r="J44" s="31" t="n"/>
+      <c r="J44" s="57" t="n"/>
       <c r="K44" s="29" t="n"/>
       <c r="L44" s="31" t="n"/>
     </row>
-    <row r="45" ht="16.95" customHeight="1" s="70">
+    <row r="45" ht="24" customHeight="1" s="70">
       <c r="A45" s="57" t="n">
-        <v>4</v>
-      </c>
-      <c r="B45" s="89" t="inlineStr">
-        <is>
-          <t>CALIENTE · Área libre de combustibles; extintor y vigía de fuego presentes</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B45" s="89" t="n"/>
       <c r="C45" s="30" t="n"/>
       <c r="D45" s="30" t="n"/>
       <c r="E45" s="30" t="n"/>
       <c r="F45" s="30" t="n"/>
-      <c r="G45" s="30" t="n"/>
-      <c r="H45" s="31" t="n"/>
+      <c r="G45" s="31" t="n"/>
+      <c r="H45" s="57" t="n"/>
       <c r="I45" s="57" t="n"/>
-      <c r="J45" s="31" t="n"/>
+      <c r="J45" s="57" t="n"/>
       <c r="K45" s="29" t="n"/>
       <c r="L45" s="31" t="n"/>
     </row>
-    <row r="46" ht="16.95" customHeight="1" s="70">
+    <row r="46" ht="24" customHeight="1" s="70">
       <c r="A46" s="57" t="n">
-        <v>5</v>
-      </c>
-      <c r="B46" s="89" t="inlineStr">
-        <is>
-          <t>CALIENTE · Cilindros, mangueras y equipos de soldadura o corte inspeccionados</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B46" s="89" t="n"/>
       <c r="C46" s="30" t="n"/>
       <c r="D46" s="30" t="n"/>
       <c r="E46" s="30" t="n"/>
       <c r="F46" s="30" t="n"/>
-      <c r="G46" s="30" t="n"/>
-      <c r="H46" s="31" t="n"/>
+      <c r="G46" s="31" t="n"/>
+      <c r="H46" s="57" t="n"/>
       <c r="I46" s="57" t="n"/>
-      <c r="J46" s="31" t="n"/>
+      <c r="J46" s="57" t="n"/>
       <c r="K46" s="29" t="n"/>
       <c r="L46" s="31" t="n"/>
     </row>
-    <row r="47" ht="16.95" customHeight="1" s="70">
+    <row r="47" ht="24" customHeight="1" s="70">
       <c r="A47" s="57" t="n">
-        <v>6</v>
-      </c>
-      <c r="B47" s="89" t="inlineStr">
-        <is>
-          <t>CALIENTE · Protección contra chispas y escoria (mantas, pantallas)</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B47" s="89" t="n"/>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="30" t="n"/>
       <c r="E47" s="30" t="n"/>
       <c r="F47" s="30" t="n"/>
-      <c r="G47" s="30" t="n"/>
-      <c r="H47" s="31" t="n"/>
+      <c r="G47" s="31" t="n"/>
+      <c r="H47" s="57" t="n"/>
       <c r="I47" s="57" t="n"/>
-      <c r="J47" s="31" t="n"/>
+      <c r="J47" s="57" t="n"/>
       <c r="K47" s="29" t="n"/>
       <c r="L47" s="31" t="n"/>
     </row>
-    <row r="48" ht="16.95" customHeight="1" s="70">
+    <row r="48" ht="24" customHeight="1" s="70">
       <c r="A48" s="57" t="n">
-        <v>7</v>
-      </c>
-      <c r="B48" s="89" t="inlineStr">
-        <is>
-          <t>CONFINADOS · Espacio aislado, ventilado y con medición de gases previa</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B48" s="89" t="n"/>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="30" t="n"/>
       <c r="E48" s="30" t="n"/>
       <c r="F48" s="30" t="n"/>
-      <c r="G48" s="30" t="n"/>
-      <c r="H48" s="31" t="n"/>
+      <c r="G48" s="31" t="n"/>
+      <c r="H48" s="57" t="n"/>
       <c r="I48" s="57" t="n"/>
-      <c r="J48" s="31" t="n"/>
+      <c r="J48" s="57" t="n"/>
       <c r="K48" s="29" t="n"/>
       <c r="L48" s="31" t="n"/>
     </row>
-    <row r="49" ht="16.95" customHeight="1" s="70">
+    <row r="49" ht="24" customHeight="1" s="70">
       <c r="A49" s="57" t="n">
-        <v>8</v>
-      </c>
-      <c r="B49" s="89" t="inlineStr">
-        <is>
-          <t>CONFINADOS · Vigía permanente en el exterior y comunicación constante</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B49" s="89" t="n"/>
       <c r="C49" s="30" t="n"/>
       <c r="D49" s="30" t="n"/>
       <c r="E49" s="30" t="n"/>
       <c r="F49" s="30" t="n"/>
-      <c r="G49" s="30" t="n"/>
-      <c r="H49" s="31" t="n"/>
+      <c r="G49" s="31" t="n"/>
+      <c r="H49" s="57" t="n"/>
       <c r="I49" s="57" t="n"/>
-      <c r="J49" s="31" t="n"/>
+      <c r="J49" s="57" t="n"/>
       <c r="K49" s="29" t="n"/>
       <c r="L49" s="31" t="n"/>
     </row>
-    <row r="50" ht="16.95" customHeight="1" s="70">
+    <row r="50" ht="24" customHeight="1" s="70">
       <c r="A50" s="57" t="n">
-        <v>9</v>
-      </c>
-      <c r="B50" s="89" t="inlineStr">
-        <is>
-          <t>CONFINADOS · Equipo de rescate y de respiración disponible</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B50" s="89" t="n"/>
       <c r="C50" s="30" t="n"/>
       <c r="D50" s="30" t="n"/>
       <c r="E50" s="30" t="n"/>
       <c r="F50" s="30" t="n"/>
-      <c r="G50" s="30" t="n"/>
-      <c r="H50" s="31" t="n"/>
+      <c r="G50" s="31" t="n"/>
+      <c r="H50" s="57" t="n"/>
       <c r="I50" s="57" t="n"/>
-      <c r="J50" s="31" t="n"/>
+      <c r="J50" s="57" t="n"/>
       <c r="K50" s="29" t="n"/>
       <c r="L50" s="31" t="n"/>
     </row>
-    <row r="51" ht="16.95" customHeight="1" s="70">
+    <row r="51" ht="24" customHeight="1" s="70">
       <c r="A51" s="57" t="n">
-        <v>10</v>
-      </c>
-      <c r="B51" s="89" t="inlineStr">
-        <is>
-          <t>EXCAVACIONES · Servicios enterrados localizados y señalizados</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B51" s="89" t="n"/>
       <c r="C51" s="30" t="n"/>
       <c r="D51" s="30" t="n"/>
       <c r="E51" s="30" t="n"/>
       <c r="F51" s="30" t="n"/>
-      <c r="G51" s="30" t="n"/>
-      <c r="H51" s="31" t="n"/>
+      <c r="G51" s="31" t="n"/>
+      <c r="H51" s="57" t="n"/>
       <c r="I51" s="57" t="n"/>
-      <c r="J51" s="31" t="n"/>
+      <c r="J51" s="57" t="n"/>
       <c r="K51" s="29" t="n"/>
       <c r="L51" s="31" t="n"/>
     </row>
-    <row r="52" ht="16.95" customHeight="1" s="70">
+    <row r="52" ht="24" customHeight="1" s="70">
       <c r="A52" s="57" t="n">
-        <v>11</v>
-      </c>
-      <c r="B52" s="89" t="inlineStr">
-        <is>
-          <t>EXCAVACIONES · Taludes, entibados o sistema de contención; acceso y salida seguros</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B52" s="89" t="n"/>
       <c r="C52" s="30" t="n"/>
       <c r="D52" s="30" t="n"/>
       <c r="E52" s="30" t="n"/>
       <c r="F52" s="30" t="n"/>
-      <c r="G52" s="30" t="n"/>
-      <c r="H52" s="31" t="n"/>
+      <c r="G52" s="31" t="n"/>
+      <c r="H52" s="57" t="n"/>
       <c r="I52" s="57" t="n"/>
-      <c r="J52" s="31" t="n"/>
+      <c r="J52" s="57" t="n"/>
       <c r="K52" s="29" t="n"/>
       <c r="L52" s="31" t="n"/>
     </row>
-    <row r="53" ht="16.95" customHeight="1" s="70">
-      <c r="A53" s="57" t="n">
-        <v>12</v>
-      </c>
-      <c r="B53" s="89" t="inlineStr">
-        <is>
-          <t>ELÉCTRICO · Energía aislada, bloqueada, etiquetada y verificada sin tensión</t>
-        </is>
-      </c>
-      <c r="C53" s="30" t="n"/>
-      <c r="D53" s="30" t="n"/>
-      <c r="E53" s="30" t="n"/>
-      <c r="F53" s="30" t="n"/>
-      <c r="G53" s="30" t="n"/>
-      <c r="H53" s="31" t="n"/>
-      <c r="I53" s="57" t="n"/>
-      <c r="J53" s="31" t="n"/>
-      <c r="K53" s="29" t="n"/>
-      <c r="L53" s="31" t="n"/>
-    </row>
-    <row r="54" ht="16.95" customHeight="1" s="70">
-      <c r="A54" s="57" t="n">
-        <v>13</v>
-      </c>
-      <c r="B54" s="89" t="inlineStr">
-        <is>
-          <t>ELÉCTRICO · Elementos dieléctricos y distancias de seguridad respetadas</t>
-        </is>
-      </c>
-      <c r="C54" s="30" t="n"/>
-      <c r="D54" s="30" t="n"/>
-      <c r="E54" s="30" t="n"/>
-      <c r="F54" s="30" t="n"/>
-      <c r="G54" s="30" t="n"/>
-      <c r="H54" s="31" t="n"/>
-      <c r="I54" s="57" t="n"/>
-      <c r="J54" s="31" t="n"/>
-      <c r="K54" s="29" t="n"/>
+    <row r="53" ht="16.5" customHeight="1" s="70">
+      <c r="A53" s="54" t="inlineStr">
+        <is>
+          <t>5. MEDICIÓN DE GASES (espacios confinados, trabajo en caliente, sustancias químicas y excavaciones profundas)</t>
+        </is>
+      </c>
+      <c r="B53" s="38" t="n"/>
+      <c r="C53" s="38" t="n"/>
+      <c r="D53" s="38" t="n"/>
+      <c r="E53" s="38" t="n"/>
+      <c r="F53" s="38" t="n"/>
+      <c r="G53" s="38" t="n"/>
+      <c r="H53" s="38" t="n"/>
+      <c r="I53" s="38" t="n"/>
+      <c r="J53" s="38" t="n"/>
+      <c r="K53" s="38" t="n"/>
+      <c r="L53" s="47" t="n"/>
+    </row>
+    <row r="54" ht="22" customHeight="1" s="70">
+      <c r="A54" s="34" t="inlineStr">
+        <is>
+          <t>Medición</t>
+        </is>
+      </c>
+      <c r="B54" s="31" t="n"/>
+      <c r="C54" s="34" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="D54" s="34" t="inlineStr">
+        <is>
+          <t>Oxígeno O₂ (%)</t>
+        </is>
+      </c>
+      <c r="E54" s="34" t="inlineStr">
+        <is>
+          <t>Explosividad LEL (%)</t>
+        </is>
+      </c>
+      <c r="F54" s="31" t="n"/>
+      <c r="G54" s="34" t="inlineStr">
+        <is>
+          <t>CO (ppm)</t>
+        </is>
+      </c>
+      <c r="H54" s="34" t="inlineStr">
+        <is>
+          <t>H₂S (ppm)</t>
+        </is>
+      </c>
+      <c r="I54" s="34" t="inlineStr">
+        <is>
+          <t>Responsable de la medición</t>
+        </is>
+      </c>
+      <c r="J54" s="30" t="n"/>
+      <c r="K54" s="30" t="n"/>
       <c r="L54" s="31" t="n"/>
     </row>
-    <row r="55" ht="16.95" customHeight="1" s="70">
-      <c r="A55" s="57" t="n">
-        <v>14</v>
-      </c>
-      <c r="B55" s="89" t="inlineStr">
-        <is>
-          <t>IZAJE · Plan de izaje, equipo certificado, señalero y área restringida</t>
-        </is>
-      </c>
-      <c r="C55" s="30" t="n"/>
-      <c r="D55" s="30" t="n"/>
-      <c r="E55" s="30" t="n"/>
-      <c r="F55" s="30" t="n"/>
-      <c r="G55" s="30" t="n"/>
-      <c r="H55" s="31" t="n"/>
-      <c r="I55" s="57" t="n"/>
-      <c r="J55" s="31" t="n"/>
-      <c r="K55" s="29" t="n"/>
+    <row r="55" ht="19" customHeight="1" s="70">
+      <c r="A55" s="29" t="inlineStr">
+        <is>
+          <t>Inicial</t>
+        </is>
+      </c>
+      <c r="B55" s="31" t="n"/>
+      <c r="C55" s="57" t="n"/>
+      <c r="D55" s="57" t="n"/>
+      <c r="E55" s="57" t="n"/>
+      <c r="F55" s="31" t="n"/>
+      <c r="G55" s="57" t="n"/>
+      <c r="H55" s="57" t="n"/>
+      <c r="I55" s="29" t="n"/>
+      <c r="J55" s="30" t="n"/>
+      <c r="K55" s="30" t="n"/>
       <c r="L55" s="31" t="n"/>
     </row>
-    <row r="56" ht="16.5" customHeight="1" s="70">
-      <c r="A56" s="54" t="inlineStr">
-        <is>
-          <t>5. MEDICIÓN DE GASES (espacios confinados y trabajo en caliente, si aplica)</t>
-        </is>
-      </c>
-      <c r="B56" s="38" t="n"/>
-      <c r="C56" s="38" t="n"/>
-      <c r="D56" s="38" t="n"/>
-      <c r="E56" s="38" t="n"/>
-      <c r="F56" s="38" t="n"/>
-      <c r="G56" s="38" t="n"/>
-      <c r="H56" s="38" t="n"/>
-      <c r="I56" s="38" t="n"/>
-      <c r="J56" s="38" t="n"/>
-      <c r="K56" s="38" t="n"/>
-      <c r="L56" s="47" t="n"/>
-    </row>
-    <row r="57" ht="22.05" customHeight="1" s="70">
-      <c r="A57" s="34" t="inlineStr">
-        <is>
-          <t>Medición</t>
+    <row r="56" ht="19" customHeight="1" s="70">
+      <c r="A56" s="29" t="inlineStr">
+        <is>
+          <t>Intermedia</t>
+        </is>
+      </c>
+      <c r="B56" s="31" t="n"/>
+      <c r="C56" s="57" t="n"/>
+      <c r="D56" s="57" t="n"/>
+      <c r="E56" s="57" t="n"/>
+      <c r="F56" s="31" t="n"/>
+      <c r="G56" s="57" t="n"/>
+      <c r="H56" s="57" t="n"/>
+      <c r="I56" s="29" t="n"/>
+      <c r="J56" s="30" t="n"/>
+      <c r="K56" s="30" t="n"/>
+      <c r="L56" s="31" t="n"/>
+    </row>
+    <row r="57" ht="19" customHeight="1" s="70">
+      <c r="A57" s="29" t="inlineStr">
+        <is>
+          <t>Final</t>
         </is>
       </c>
       <c r="B57" s="31" t="n"/>
-      <c r="C57" s="34" t="inlineStr">
-        <is>
-          <t>Hora</t>
-        </is>
-      </c>
-      <c r="D57" s="34" t="inlineStr">
-        <is>
-          <t>Oxígeno O₂ (%)</t>
-        </is>
-      </c>
-      <c r="E57" s="34" t="inlineStr">
-        <is>
-          <t>Explosividad LEL (%)</t>
-        </is>
-      </c>
+      <c r="C57" s="57" t="n"/>
+      <c r="D57" s="57" t="n"/>
+      <c r="E57" s="57" t="n"/>
       <c r="F57" s="31" t="n"/>
-      <c r="G57" s="34" t="inlineStr">
-        <is>
-          <t>CO (ppm)</t>
-        </is>
-      </c>
-      <c r="H57" s="34" t="inlineStr">
-        <is>
-          <t>H₂S (ppm)</t>
-        </is>
-      </c>
-      <c r="I57" s="34" t="inlineStr">
-        <is>
-          <t>Responsable de la medición</t>
-        </is>
-      </c>
+      <c r="G57" s="57" t="n"/>
+      <c r="H57" s="57" t="n"/>
+      <c r="I57" s="29" t="n"/>
       <c r="J57" s="30" t="n"/>
       <c r="K57" s="30" t="n"/>
       <c r="L57" s="31" t="n"/>
     </row>
-    <row r="58" ht="19.05" customHeight="1" s="70">
-      <c r="A58" s="29" t="inlineStr">
-        <is>
-          <t>Inicial</t>
-        </is>
-      </c>
-      <c r="B58" s="31" t="n"/>
-      <c r="C58" s="57" t="n"/>
-      <c r="D58" s="57" t="n"/>
-      <c r="E58" s="57" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="57" t="n"/>
-      <c r="H58" s="57" t="n"/>
-      <c r="I58" s="29" t="n"/>
-      <c r="J58" s="30" t="n"/>
-      <c r="K58" s="30" t="n"/>
-      <c r="L58" s="31" t="n"/>
-    </row>
-    <row r="59" ht="19.05" customHeight="1" s="70">
-      <c r="A59" s="29" t="inlineStr">
-        <is>
-          <t>Intermedia</t>
-        </is>
-      </c>
-      <c r="B59" s="31" t="n"/>
-      <c r="C59" s="57" t="n"/>
-      <c r="D59" s="57" t="n"/>
-      <c r="E59" s="57" t="n"/>
-      <c r="F59" s="31" t="n"/>
-      <c r="G59" s="57" t="n"/>
-      <c r="H59" s="57" t="n"/>
-      <c r="I59" s="29" t="n"/>
-      <c r="J59" s="30" t="n"/>
-      <c r="K59" s="30" t="n"/>
-      <c r="L59" s="31" t="n"/>
-    </row>
-    <row r="60" ht="19.05" customHeight="1" s="70">
-      <c r="A60" s="29" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="B60" s="31" t="n"/>
-      <c r="C60" s="57" t="n"/>
-      <c r="D60" s="57" t="n"/>
-      <c r="E60" s="57" t="n"/>
-      <c r="F60" s="31" t="n"/>
-      <c r="G60" s="57" t="n"/>
-      <c r="H60" s="57" t="n"/>
-      <c r="I60" s="29" t="n"/>
+    <row r="58" ht="16" customHeight="1" s="70">
+      <c r="A58" s="103" t="inlineStr">
+        <is>
+          <t>Registre las lecturas. Los límites aceptables son los definidos en el procedimiento del proyecto. Obligatoria en espacios confinados.</t>
+        </is>
+      </c>
+      <c r="B58" s="115" t="n"/>
+      <c r="C58" s="115" t="n"/>
+      <c r="D58" s="115" t="n"/>
+      <c r="E58" s="115" t="n"/>
+      <c r="F58" s="115" t="n"/>
+      <c r="G58" s="115" t="n"/>
+      <c r="H58" s="115" t="n"/>
+      <c r="I58" s="115" t="n"/>
+      <c r="J58" s="115" t="n"/>
+      <c r="K58" s="115" t="n"/>
+      <c r="L58" s="116" t="n"/>
+    </row>
+    <row r="59" ht="16.5" customHeight="1" s="70">
+      <c r="A59" s="54" t="inlineStr">
+        <is>
+          <t>6. AUTORIZACIÓN</t>
+        </is>
+      </c>
+      <c r="B59" s="38" t="n"/>
+      <c r="C59" s="38" t="n"/>
+      <c r="D59" s="38" t="n"/>
+      <c r="E59" s="38" t="n"/>
+      <c r="F59" s="38" t="n"/>
+      <c r="G59" s="38" t="n"/>
+      <c r="H59" s="38" t="n"/>
+      <c r="I59" s="38" t="n"/>
+      <c r="J59" s="38" t="n"/>
+      <c r="K59" s="38" t="n"/>
+      <c r="L59" s="47" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1" s="70">
+      <c r="A60" s="51" t="inlineStr">
+        <is>
+          <t>SOLICITANTE</t>
+        </is>
+      </c>
+      <c r="B60" s="30" t="n"/>
+      <c r="C60" s="30" t="n"/>
+      <c r="D60" s="31" t="n"/>
+      <c r="E60" s="51" t="inlineStr">
+        <is>
+          <t>AUTORIZA — RESPONSABLE SST / RESIDENTE</t>
+        </is>
+      </c>
+      <c r="F60" s="30" t="n"/>
+      <c r="G60" s="30" t="n"/>
+      <c r="H60" s="31" t="n"/>
+      <c r="I60" s="51" t="inlineStr">
+        <is>
+          <t>VIGÍA / SUPERVISOR DEL TRABAJO</t>
+        </is>
+      </c>
       <c r="J60" s="30" t="n"/>
       <c r="K60" s="30" t="n"/>
       <c r="L60" s="31" t="n"/>
     </row>
-    <row r="61" ht="16.05" customHeight="1" s="70">
-      <c r="A61" s="103" t="inlineStr">
-        <is>
-          <t>Registre las lecturas. Los límites aceptables son los definidos en el procedimiento del proyecto para espacios confinados y trabajo en caliente.</t>
-        </is>
-      </c>
-      <c r="B61" s="115" t="n"/>
-      <c r="C61" s="115" t="n"/>
-      <c r="D61" s="115" t="n"/>
-      <c r="E61" s="115" t="n"/>
-      <c r="F61" s="115" t="n"/>
-      <c r="G61" s="115" t="n"/>
-      <c r="H61" s="115" t="n"/>
-      <c r="I61" s="115" t="n"/>
-      <c r="J61" s="115" t="n"/>
-      <c r="K61" s="115" t="n"/>
-      <c r="L61" s="116" t="n"/>
-    </row>
-    <row r="62" ht="16.5" customHeight="1" s="70">
-      <c r="A62" s="54" t="inlineStr">
-        <is>
-          <t>6. AUTORIZACIÓN</t>
-        </is>
-      </c>
-      <c r="B62" s="38" t="n"/>
-      <c r="C62" s="38" t="n"/>
-      <c r="D62" s="38" t="n"/>
-      <c r="E62" s="38" t="n"/>
-      <c r="F62" s="38" t="n"/>
-      <c r="G62" s="38" t="n"/>
-      <c r="H62" s="38" t="n"/>
-      <c r="I62" s="38" t="n"/>
-      <c r="J62" s="38" t="n"/>
-      <c r="K62" s="38" t="n"/>
-      <c r="L62" s="47" t="n"/>
-    </row>
-    <row r="63" ht="18" customHeight="1" s="70">
-      <c r="A63" s="51" t="inlineStr">
-        <is>
-          <t>SOLICITANTE</t>
-        </is>
-      </c>
-      <c r="B63" s="30" t="n"/>
-      <c r="C63" s="30" t="n"/>
+    <row r="61" ht="42" customHeight="1" s="70">
+      <c r="A61" s="39" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="B61" s="31" t="n"/>
+      <c r="C61" s="43" t="n"/>
+      <c r="D61" s="31" t="n"/>
+      <c r="E61" s="39" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F61" s="31" t="n"/>
+      <c r="G61" s="43" t="n"/>
+      <c r="H61" s="31" t="n"/>
+      <c r="I61" s="39" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="J61" s="31" t="n"/>
+      <c r="K61" s="43" t="n"/>
+      <c r="L61" s="31" t="n"/>
+    </row>
+    <row r="62" ht="21" customHeight="1" s="70">
+      <c r="A62" s="39" t="inlineStr">
+        <is>
+          <t>Nombre:</t>
+        </is>
+      </c>
+      <c r="B62" s="31" t="n"/>
+      <c r="C62" s="43" t="n"/>
+      <c r="D62" s="31" t="n"/>
+      <c r="E62" s="39" t="inlineStr">
+        <is>
+          <t>Nombre:</t>
+        </is>
+      </c>
+      <c r="F62" s="31" t="n"/>
+      <c r="G62" s="43" t="n"/>
+      <c r="H62" s="31" t="n"/>
+      <c r="I62" s="39" t="inlineStr">
+        <is>
+          <t>Nombre:</t>
+        </is>
+      </c>
+      <c r="J62" s="31" t="n"/>
+      <c r="K62" s="43" t="n"/>
+      <c r="L62" s="31" t="n"/>
+    </row>
+    <row r="63" ht="21" customHeight="1" s="70">
+      <c r="A63" s="39" t="inlineStr">
+        <is>
+          <t>Cargo:</t>
+        </is>
+      </c>
+      <c r="B63" s="31" t="n"/>
+      <c r="C63" s="43" t="n"/>
       <c r="D63" s="31" t="n"/>
-      <c r="E63" s="51" t="inlineStr">
-        <is>
-          <t>AUTORIZA — RESPONSABLE SST / RESIDENTE</t>
-        </is>
-      </c>
-      <c r="F63" s="30" t="n"/>
-      <c r="G63" s="30" t="n"/>
+      <c r="E63" s="39" t="inlineStr">
+        <is>
+          <t>Cargo:</t>
+        </is>
+      </c>
+      <c r="F63" s="31" t="n"/>
+      <c r="G63" s="43" t="n"/>
       <c r="H63" s="31" t="n"/>
-      <c r="I63" s="51" t="inlineStr">
-        <is>
-          <t>VIGÍA / SUPERVISOR DEL TRABAJO</t>
-        </is>
-      </c>
-      <c r="J63" s="30" t="n"/>
-      <c r="K63" s="30" t="n"/>
+      <c r="I63" s="39" t="inlineStr">
+        <is>
+          <t>Cargo:</t>
+        </is>
+      </c>
+      <c r="J63" s="31" t="n"/>
+      <c r="K63" s="43" t="n"/>
       <c r="L63" s="31" t="n"/>
     </row>
-    <row r="64" ht="42" customHeight="1" s="70">
+    <row r="64" ht="21" customHeight="1" s="70">
       <c r="A64" s="39" t="inlineStr">
         <is>
-          <t>Firma:</t>
+          <t>Hora:</t>
         </is>
       </c>
       <c r="B64" s="31" t="n"/>
@@ -2542,7 +2782,7 @@
       <c r="D64" s="31" t="n"/>
       <c r="E64" s="39" t="inlineStr">
         <is>
-          <t>Firma:</t>
+          <t>Hora:</t>
         </is>
       </c>
       <c r="F64" s="31" t="n"/>
@@ -2550,497 +2790,396 @@
       <c r="H64" s="31" t="n"/>
       <c r="I64" s="39" t="inlineStr">
         <is>
-          <t>Firma:</t>
+          <t>Hora:</t>
         </is>
       </c>
       <c r="J64" s="31" t="n"/>
       <c r="K64" s="43" t="n"/>
       <c r="L64" s="31" t="n"/>
     </row>
-    <row r="65" ht="21" customHeight="1" s="70">
-      <c r="A65" s="39" t="inlineStr">
-        <is>
-          <t>Nombre:</t>
-        </is>
-      </c>
-      <c r="B65" s="31" t="n"/>
-      <c r="C65" s="43" t="n"/>
-      <c r="D65" s="31" t="n"/>
-      <c r="E65" s="39" t="inlineStr">
-        <is>
-          <t>Nombre:</t>
-        </is>
-      </c>
-      <c r="F65" s="31" t="n"/>
-      <c r="G65" s="43" t="n"/>
-      <c r="H65" s="31" t="n"/>
-      <c r="I65" s="39" t="inlineStr">
-        <is>
-          <t>Nombre:</t>
-        </is>
-      </c>
-      <c r="J65" s="31" t="n"/>
-      <c r="K65" s="43" t="n"/>
-      <c r="L65" s="31" t="n"/>
-    </row>
-    <row r="66" ht="21" customHeight="1" s="70">
-      <c r="A66" s="39" t="inlineStr">
-        <is>
-          <t>Cargo:</t>
+    <row r="65" ht="16.5" customHeight="1" s="70">
+      <c r="A65" s="54" t="inlineStr">
+        <is>
+          <t>7. CIERRE DEL PERMISO</t>
+        </is>
+      </c>
+      <c r="B65" s="38" t="n"/>
+      <c r="C65" s="38" t="n"/>
+      <c r="D65" s="38" t="n"/>
+      <c r="E65" s="38" t="n"/>
+      <c r="F65" s="38" t="n"/>
+      <c r="G65" s="38" t="n"/>
+      <c r="H65" s="38" t="n"/>
+      <c r="I65" s="38" t="n"/>
+      <c r="J65" s="38" t="n"/>
+      <c r="K65" s="38" t="n"/>
+      <c r="L65" s="47" t="n"/>
+    </row>
+    <row r="66" ht="24" customHeight="1" s="70">
+      <c r="A66" s="33" t="inlineStr">
+        <is>
+          <t>Hora de cierre</t>
         </is>
       </c>
       <c r="B66" s="31" t="n"/>
-      <c r="C66" s="43" t="n"/>
+      <c r="C66" s="48" t="n"/>
       <c r="D66" s="31" t="n"/>
-      <c r="E66" s="39" t="inlineStr">
-        <is>
-          <t>Cargo:</t>
+      <c r="E66" s="33" t="inlineStr">
+        <is>
+          <t>¿Trabajo terminado?</t>
         </is>
       </c>
       <c r="F66" s="31" t="n"/>
-      <c r="G66" s="43" t="n"/>
+      <c r="G66" s="48" t="n"/>
       <c r="H66" s="31" t="n"/>
-      <c r="I66" s="39" t="inlineStr">
-        <is>
-          <t>Cargo:</t>
+      <c r="I66" s="33" t="inlineStr">
+        <is>
+          <t>¿Área en orden y sin energía residual?</t>
         </is>
       </c>
       <c r="J66" s="31" t="n"/>
-      <c r="K66" s="43" t="n"/>
+      <c r="K66" s="48" t="n"/>
       <c r="L66" s="31" t="n"/>
     </row>
-    <row r="67" ht="21" customHeight="1" s="70">
-      <c r="A67" s="39" t="inlineStr">
-        <is>
-          <t>Hora:</t>
+    <row r="67" ht="30" customHeight="1" s="70">
+      <c r="A67" s="33" t="inlineStr">
+        <is>
+          <t>Observaciones / novedades</t>
         </is>
       </c>
       <c r="B67" s="31" t="n"/>
-      <c r="C67" s="43" t="n"/>
-      <c r="D67" s="31" t="n"/>
-      <c r="E67" s="39" t="inlineStr">
-        <is>
-          <t>Hora:</t>
-        </is>
-      </c>
-      <c r="F67" s="31" t="n"/>
-      <c r="G67" s="43" t="n"/>
-      <c r="H67" s="31" t="n"/>
-      <c r="I67" s="39" t="inlineStr">
-        <is>
-          <t>Hora:</t>
-        </is>
-      </c>
-      <c r="J67" s="31" t="n"/>
-      <c r="K67" s="43" t="n"/>
+      <c r="C67" s="52" t="n"/>
+      <c r="D67" s="30" t="n"/>
+      <c r="E67" s="30" t="n"/>
+      <c r="F67" s="30" t="n"/>
+      <c r="G67" s="30" t="n"/>
+      <c r="H67" s="30" t="n"/>
+      <c r="I67" s="30" t="n"/>
+      <c r="J67" s="30" t="n"/>
+      <c r="K67" s="30" t="n"/>
       <c r="L67" s="31" t="n"/>
     </row>
-    <row r="68" ht="16.5" customHeight="1" s="70">
-      <c r="A68" s="54" t="inlineStr">
-        <is>
-          <t>7. CIERRE DEL PERMISO</t>
-        </is>
-      </c>
-      <c r="B68" s="38" t="n"/>
-      <c r="C68" s="38" t="n"/>
-      <c r="D68" s="38" t="n"/>
-      <c r="E68" s="38" t="n"/>
-      <c r="F68" s="38" t="n"/>
-      <c r="G68" s="38" t="n"/>
-      <c r="H68" s="38" t="n"/>
-      <c r="I68" s="38" t="n"/>
-      <c r="J68" s="38" t="n"/>
-      <c r="K68" s="38" t="n"/>
-      <c r="L68" s="47" t="n"/>
-    </row>
-    <row r="69" ht="24" customHeight="1" s="70">
-      <c r="A69" s="33" t="inlineStr">
-        <is>
-          <t>Hora de cierre</t>
-        </is>
-      </c>
-      <c r="B69" s="31" t="n"/>
-      <c r="C69" s="48" t="n"/>
-      <c r="D69" s="31" t="n"/>
-      <c r="E69" s="33" t="inlineStr">
-        <is>
-          <t>¿Trabajo terminado?</t>
-        </is>
-      </c>
+    <row r="68" ht="24" customHeight="1" s="70">
+      <c r="A68" s="33" t="inlineStr">
+        <is>
+          <t>Motivo de suspensión o cancelación</t>
+        </is>
+      </c>
+      <c r="B68" s="31" t="n"/>
+      <c r="C68" s="52" t="n"/>
+      <c r="D68" s="30" t="n"/>
+      <c r="E68" s="30" t="n"/>
+      <c r="F68" s="30" t="n"/>
+      <c r="G68" s="30" t="n"/>
+      <c r="H68" s="30" t="n"/>
+      <c r="I68" s="30" t="n"/>
+      <c r="J68" s="30" t="n"/>
+      <c r="K68" s="30" t="n"/>
+      <c r="L68" s="31" t="n"/>
+    </row>
+    <row r="69" ht="18" customHeight="1" s="70">
+      <c r="A69" s="51" t="inlineStr">
+        <is>
+          <t>CIERRA — SOLICITANTE</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="n"/>
+      <c r="C69" s="30" t="n"/>
+      <c r="D69" s="30" t="n"/>
+      <c r="E69" s="30" t="n"/>
       <c r="F69" s="31" t="n"/>
-      <c r="G69" s="48" t="n"/>
-      <c r="H69" s="31" t="n"/>
-      <c r="I69" s="33" t="inlineStr">
-        <is>
-          <t>¿Área en orden y sin energía residual?</t>
-        </is>
-      </c>
-      <c r="J69" s="31" t="n"/>
-      <c r="K69" s="48" t="n"/>
+      <c r="G69" s="51" t="inlineStr">
+        <is>
+          <t>RECIBE — RESPONSABLE SST / RESIDENTE</t>
+        </is>
+      </c>
+      <c r="H69" s="30" t="n"/>
+      <c r="I69" s="30" t="n"/>
+      <c r="J69" s="30" t="n"/>
+      <c r="K69" s="30" t="n"/>
       <c r="L69" s="31" t="n"/>
     </row>
-    <row r="70" ht="30" customHeight="1" s="70">
-      <c r="A70" s="33" t="inlineStr">
-        <is>
-          <t>Observaciones / novedades</t>
+    <row r="70" ht="42" customHeight="1" s="70">
+      <c r="A70" s="39" t="inlineStr">
+        <is>
+          <t>Firma:</t>
         </is>
       </c>
       <c r="B70" s="31" t="n"/>
-      <c r="C70" s="52" t="n"/>
+      <c r="C70" s="43" t="n"/>
       <c r="D70" s="30" t="n"/>
       <c r="E70" s="30" t="n"/>
-      <c r="F70" s="30" t="n"/>
-      <c r="G70" s="30" t="n"/>
-      <c r="H70" s="30" t="n"/>
-      <c r="I70" s="30" t="n"/>
+      <c r="F70" s="31" t="n"/>
+      <c r="G70" s="39" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="H70" s="31" t="n"/>
+      <c r="I70" s="43" t="n"/>
       <c r="J70" s="30" t="n"/>
       <c r="K70" s="30" t="n"/>
       <c r="L70" s="31" t="n"/>
     </row>
-    <row r="71" ht="24" customHeight="1" s="70">
-      <c r="A71" s="33" t="inlineStr">
-        <is>
-          <t>Motivo de suspensión o cancelación</t>
+    <row r="71" ht="21" customHeight="1" s="70">
+      <c r="A71" s="39" t="inlineStr">
+        <is>
+          <t>Nombre:</t>
         </is>
       </c>
       <c r="B71" s="31" t="n"/>
-      <c r="C71" s="52" t="n"/>
+      <c r="C71" s="43" t="n"/>
       <c r="D71" s="30" t="n"/>
       <c r="E71" s="30" t="n"/>
-      <c r="F71" s="30" t="n"/>
-      <c r="G71" s="30" t="n"/>
-      <c r="H71" s="30" t="n"/>
-      <c r="I71" s="30" t="n"/>
+      <c r="F71" s="31" t="n"/>
+      <c r="G71" s="39" t="inlineStr">
+        <is>
+          <t>Nombre:</t>
+        </is>
+      </c>
+      <c r="H71" s="31" t="n"/>
+      <c r="I71" s="43" t="n"/>
       <c r="J71" s="30" t="n"/>
       <c r="K71" s="30" t="n"/>
       <c r="L71" s="31" t="n"/>
     </row>
-    <row r="72" ht="18" customHeight="1" s="70">
-      <c r="A72" s="51" t="inlineStr">
-        <is>
-          <t>CIERRA — SOLICITANTE</t>
-        </is>
-      </c>
-      <c r="B72" s="30" t="n"/>
-      <c r="C72" s="30" t="n"/>
+    <row r="72" ht="21" customHeight="1" s="70">
+      <c r="A72" s="39" t="inlineStr">
+        <is>
+          <t>Cargo:</t>
+        </is>
+      </c>
+      <c r="B72" s="31" t="n"/>
+      <c r="C72" s="43" t="n"/>
       <c r="D72" s="30" t="n"/>
       <c r="E72" s="30" t="n"/>
       <c r="F72" s="31" t="n"/>
-      <c r="G72" s="51" t="inlineStr">
-        <is>
-          <t>RECIBE — RESPONSABLE SST / RESIDENTE</t>
-        </is>
-      </c>
-      <c r="H72" s="30" t="n"/>
-      <c r="I72" s="30" t="n"/>
+      <c r="G72" s="39" t="inlineStr">
+        <is>
+          <t>Cargo:</t>
+        </is>
+      </c>
+      <c r="H72" s="31" t="n"/>
+      <c r="I72" s="43" t="n"/>
       <c r="J72" s="30" t="n"/>
       <c r="K72" s="30" t="n"/>
       <c r="L72" s="31" t="n"/>
     </row>
-    <row r="73" ht="42" customHeight="1" s="70">
-      <c r="A73" s="39" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="B73" s="31" t="n"/>
-      <c r="C73" s="43" t="n"/>
-      <c r="D73" s="30" t="n"/>
-      <c r="E73" s="30" t="n"/>
-      <c r="F73" s="31" t="n"/>
-      <c r="G73" s="39" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="H73" s="31" t="n"/>
-      <c r="I73" s="43" t="n"/>
-      <c r="J73" s="30" t="n"/>
-      <c r="K73" s="30" t="n"/>
-      <c r="L73" s="31" t="n"/>
-    </row>
-    <row r="74" ht="21" customHeight="1" s="70">
-      <c r="A74" s="39" t="inlineStr">
-        <is>
-          <t>Nombre:</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="n"/>
-      <c r="C74" s="43" t="n"/>
-      <c r="D74" s="30" t="n"/>
-      <c r="E74" s="30" t="n"/>
-      <c r="F74" s="31" t="n"/>
-      <c r="G74" s="39" t="inlineStr">
-        <is>
-          <t>Nombre:</t>
-        </is>
-      </c>
-      <c r="H74" s="31" t="n"/>
-      <c r="I74" s="43" t="n"/>
-      <c r="J74" s="30" t="n"/>
-      <c r="K74" s="30" t="n"/>
-      <c r="L74" s="31" t="n"/>
-    </row>
-    <row r="75" ht="21" customHeight="1" s="70">
-      <c r="A75" s="39" t="inlineStr">
-        <is>
-          <t>Cargo:</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n"/>
-      <c r="C75" s="43" t="n"/>
-      <c r="D75" s="30" t="n"/>
-      <c r="E75" s="30" t="n"/>
-      <c r="F75" s="31" t="n"/>
-      <c r="G75" s="39" t="inlineStr">
-        <is>
-          <t>Cargo:</t>
-        </is>
-      </c>
-      <c r="H75" s="31" t="n"/>
-      <c r="I75" s="43" t="n"/>
-      <c r="J75" s="30" t="n"/>
-      <c r="K75" s="30" t="n"/>
-      <c r="L75" s="31" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="61" t="inlineStr">
+    <row r="73"/>
+    <row r="74">
+      <c r="A74" s="61" t="inlineStr">
         <is>
           <t>REV. 04/10/2026</t>
         </is>
       </c>
-      <c r="G77" s="63">
+      <c r="G74" s="63">
         <f>K5</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="222">
-    <mergeCell ref="C71:L71"/>
+  <mergeCells count="198">
+    <mergeCell ref="G21:H21"/>
     <mergeCell ref="K49:L49"/>
-    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="A64:B64"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="E62:F62"/>
     <mergeCell ref="K24:L24"/>
     <mergeCell ref="K33:L33"/>
-    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="G71:H71"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C72:F72"/>
     <mergeCell ref="G23:H23"/>
     <mergeCell ref="B33:H33"/>
-    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="G69:L69"/>
     <mergeCell ref="A70:B70"/>
-    <mergeCell ref="B51:H51"/>
     <mergeCell ref="C64:D64"/>
     <mergeCell ref="I26:J26"/>
     <mergeCell ref="E64:F64"/>
     <mergeCell ref="K26:L26"/>
     <mergeCell ref="K35:L35"/>
     <mergeCell ref="B32:H32"/>
+    <mergeCell ref="A54:B54"/>
     <mergeCell ref="D1:L2"/>
-    <mergeCell ref="B41:H41"/>
     <mergeCell ref="B35:H35"/>
+    <mergeCell ref="C63:D63"/>
     <mergeCell ref="I25:J25"/>
     <mergeCell ref="K50:L50"/>
+    <mergeCell ref="E63:F63"/>
     <mergeCell ref="G66:H66"/>
-    <mergeCell ref="A74:B74"/>
     <mergeCell ref="I66:J66"/>
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="K52:L52"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="C73:F73"/>
-    <mergeCell ref="B52:H52"/>
     <mergeCell ref="D5:I5"/>
-    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B45:G45"/>
     <mergeCell ref="K42:L42"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="K53:L53"/>
-    <mergeCell ref="I58:L58"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="B53:H53"/>
-    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="D10:L10"/>
+    <mergeCell ref="B47:G47"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="K28:L28"/>
     <mergeCell ref="K37:L37"/>
     <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="C12:L12"/>
     <mergeCell ref="B29:H29"/>
     <mergeCell ref="G22:H22"/>
     <mergeCell ref="D6:I6"/>
-    <mergeCell ref="I69:J69"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="K69:L69"/>
+    <mergeCell ref="C18:G18"/>
     <mergeCell ref="B37:H37"/>
-    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="J15:L15"/>
     <mergeCell ref="I30:J30"/>
     <mergeCell ref="K30:L30"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="C70:L70"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="G74:L74"/>
+    <mergeCell ref="A61:B61"/>
     <mergeCell ref="K64:L64"/>
     <mergeCell ref="K21:L21"/>
     <mergeCell ref="K51:L51"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="I54:J54"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K63:L63"/>
     <mergeCell ref="K41:L41"/>
-    <mergeCell ref="B54:H54"/>
-    <mergeCell ref="C15:L15"/>
-    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="B51:G51"/>
     <mergeCell ref="K43:L43"/>
-    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="I70:L70"/>
     <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
     <mergeCell ref="A71:B71"/>
-    <mergeCell ref="I24:J24"/>
     <mergeCell ref="I57:L57"/>
-    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="B41:G41"/>
     <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="A40:L40"/>
+    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="I54:L54"/>
+    <mergeCell ref="A58:L58"/>
+    <mergeCell ref="I72:L72"/>
     <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G72:L72"/>
+    <mergeCell ref="C16:L16"/>
     <mergeCell ref="G26:H26"/>
     <mergeCell ref="I35:J35"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="I56:L56"/>
+    <mergeCell ref="I71:L71"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A63:B63"/>
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="K66:L66"/>
     <mergeCell ref="C66:D66"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="E66:F66"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="H14:I14"/>
     <mergeCell ref="K6:L6"/>
-    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C71:F71"/>
     <mergeCell ref="B34:H34"/>
-    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="B28:H28"/>
     <mergeCell ref="K25:L25"/>
     <mergeCell ref="B23:D23"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="K5:L5"/>
     <mergeCell ref="B30:H30"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="K5:L5"/>
     <mergeCell ref="J4:L4"/>
     <mergeCell ref="K45:L45"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="I59:L59"/>
-    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="C67:L67"/>
     <mergeCell ref="K29:L29"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="I60:L60"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="I74:L74"/>
-    <mergeCell ref="A65:B65"/>
     <mergeCell ref="K47:L47"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="A75:B75"/>
     <mergeCell ref="K44:L44"/>
-    <mergeCell ref="B47:H47"/>
-    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D3:L3"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="E69:F69"/>
     <mergeCell ref="K31:L31"/>
+    <mergeCell ref="B40:G40"/>
     <mergeCell ref="K46:L46"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="D3:L3"/>
+    <mergeCell ref="K40:L40"/>
     <mergeCell ref="B31:H31"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="I21:J21"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="J18:L18"/>
     <mergeCell ref="A57:B57"/>
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="I23:J23"/>
-    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="E61:F61"/>
     <mergeCell ref="K23:L23"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="G64:H64"/>
+    <mergeCell ref="A59:L59"/>
     <mergeCell ref="I64:J64"/>
-    <mergeCell ref="G73:H73"/>
     <mergeCell ref="E57:F57"/>
-    <mergeCell ref="G77:L77"/>
     <mergeCell ref="K7:L7"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="E54:F54"/>
     <mergeCell ref="B22:D22"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="A61:L61"/>
-    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="E56:F56"/>
     <mergeCell ref="A67:B67"/>
-    <mergeCell ref="I65:J65"/>
     <mergeCell ref="I34:J34"/>
+    <mergeCell ref="C70:F70"/>
     <mergeCell ref="K34:L34"/>
-    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="B42:G42"/>
     <mergeCell ref="E24:F24"/>
-    <mergeCell ref="I73:L73"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="A56:L56"/>
+    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:L17"/>
     <mergeCell ref="I36:J36"/>
+    <mergeCell ref="A27:L27"/>
     <mergeCell ref="K36:L36"/>
-    <mergeCell ref="I63:L63"/>
+    <mergeCell ref="B44:G44"/>
     <mergeCell ref="B36:H36"/>
-    <mergeCell ref="B50:H50"/>
     <mergeCell ref="A16:B16"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="C68:L68"/>
     <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="I53:J53"/>
     <mergeCell ref="I22:J22"/>
-    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="K22:L22"/>
-    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="A53:L53"/>
     <mergeCell ref="B24:D24"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="A62:L62"/>
-    <mergeCell ref="C74:F74"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A68:L68"/>
-    <mergeCell ref="I55:J55"/>
-    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A19:L19"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="I39:J39"/>
     <mergeCell ref="A9:L9"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="K61:L61"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="A39:L39"/>
     <mergeCell ref="K48:L48"/>
-    <mergeCell ref="I75:L75"/>
     <mergeCell ref="I29:J29"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="C75:F75"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="B46:G46"/>
     <mergeCell ref="I38:J38"/>
+    <mergeCell ref="A11:L11"/>
     <mergeCell ref="K38:L38"/>
-    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="B38:H38"/>
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="I55:L55"/>
     <mergeCell ref="I31:J31"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="A69:F69"/>
     <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A65:L65"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.7" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 Página &amp;P de &amp;N</oddFooter>
@@ -3050,7 +3189,7 @@
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="39" min="0" max="16383" man="1"/>
+    <brk id="38" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/public/plantilla-permiso-trabajo.xlsx
+++ b/public/plantilla-permiso-trabajo.xlsx
@@ -253,7 +253,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -372,12 +372,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="000070C0"/>
         <bgColor rgb="000070C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00595959"/>
-        <bgColor rgb="00595959"/>
       </patternFill>
     </fill>
   </fills>
@@ -750,7 +744,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -1072,9 +1066,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="20" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1091,7 +1082,7 @@
     <cellStyle name="Normal 4" xfId="4"/>
     <cellStyle name="Normal 6 2" xfId="5"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="7">
     <dxf>
       <font>
         <b val="1"/>
@@ -1173,18 +1164,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="000070C0"/>
           <bgColor rgb="000070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="00FFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00595959"/>
-          <bgColor rgb="00595959"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1688,14 +1667,14 @@
       <c r="B10" s="38" t="n"/>
       <c r="C10" s="47" t="n"/>
       <c r="D10" s="118" t="n"/>
-      <c r="E10" s="131" t="n"/>
-      <c r="F10" s="131" t="n"/>
-      <c r="G10" s="131" t="n"/>
-      <c r="H10" s="131" t="n"/>
-      <c r="I10" s="131" t="n"/>
-      <c r="J10" s="131" t="n"/>
-      <c r="K10" s="131" t="n"/>
-      <c r="L10" s="132" t="n"/>
+      <c r="E10" s="130" t="n"/>
+      <c r="F10" s="130" t="n"/>
+      <c r="G10" s="130" t="n"/>
+      <c r="H10" s="130" t="n"/>
+      <c r="I10" s="130" t="n"/>
+      <c r="J10" s="130" t="n"/>
+      <c r="K10" s="130" t="n"/>
+      <c r="L10" s="131" t="n"/>
     </row>
     <row r="11" ht="16.5" customHeight="1" s="70">
       <c r="A11" s="54" t="inlineStr">

--- a/public/plantilla-permiso-trabajo.xlsx
+++ b/public/plantilla-permiso-trabajo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="2" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Permisos de Trabajo" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="34">
+  <fonts count="38">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -214,9 +214,41 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <sz val="7"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -253,7 +285,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -328,6 +360,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF0F6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
         <bgColor rgb="00D9D9D9"/>
       </patternFill>
@@ -340,8 +384,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E36C09"/>
-        <bgColor rgb="00E36C09"/>
+        <fgColor rgb="000070C0"/>
+        <bgColor rgb="000070C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000A651"/>
+        <bgColor rgb="0000A651"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F57C00"/>
+        <bgColor rgb="00F57C00"/>
       </patternFill>
     </fill>
     <fill>
@@ -352,30 +420,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00548235"/>
-        <bgColor rgb="00548235"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="007F4F24"/>
         <bgColor rgb="007F4F24"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000070C0"/>
-        <bgColor rgb="000070C0"/>
+        <fgColor rgb="00595959"/>
+        <bgColor rgb="00595959"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -659,6 +715,17 @@
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="thin">
         <color theme="3" tint="0.5999633777886288"/>
@@ -744,7 +811,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -816,263 +883,454 @@
     <xf numFmtId="9" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="18" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="19" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="20" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="22" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1082,7 +1340,7 @@
     <cellStyle name="Normal 4" xfId="4"/>
     <cellStyle name="Normal 6 2" xfId="5"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="9">
     <dxf>
       <font>
         <b val="1"/>
@@ -1102,20 +1360,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00E36C09"/>
-          <bgColor rgb="00E36C09"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="00FFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="007030A0"/>
-          <bgColor rgb="007030A0"/>
+          <fgColor rgb="000070C0"/>
+          <bgColor rgb="000070C0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1134,12 +1380,48 @@
     <dxf>
       <font>
         <b val="1"/>
+        <color rgb="00000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFFFFF"/>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="0000A651"/>
+          <bgColor rgb="0000A651"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F57C00"/>
+          <bgColor rgb="00F57C00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
         <color rgb="00FFFFFF"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00548235"/>
-          <bgColor rgb="00548235"/>
+          <fgColor rgb="007030A0"/>
+          <bgColor rgb="007030A0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1162,8 +1444,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="000070C0"/>
-          <bgColor rgb="000070C0"/>
+          <fgColor rgb="00595959"/>
+          <bgColor rgb="00595959"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1189,8 +1471,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Image 1" descr="Picture"/>
-        <xdr:cNvPicPr/>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
@@ -1199,7 +1483,13 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2630233" cy="1259205"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1511,1654 +1801,1722 @@
     <tabColor theme="4" tint="0.3999755851924192"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:M74"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col width="12.78" customWidth="1" style="70" min="1" max="1"/>
-    <col width="13" customWidth="1" style="70" min="2" max="2"/>
-    <col width="13" customWidth="1" style="70" min="3" max="3"/>
-    <col width="15.78" customWidth="1" style="70" min="4" max="4"/>
-    <col width="10" customWidth="1" style="70" min="5" max="5"/>
-    <col width="15.78" customWidth="1" style="70" min="6" max="6"/>
-    <col width="11" customWidth="1" style="70" min="7" max="7"/>
-    <col width="15.78" customWidth="1" style="70" min="8" max="8"/>
-    <col width="10" customWidth="1" style="70" min="9" max="9"/>
-    <col width="15.78" customWidth="1" style="70" min="10" max="10"/>
-    <col width="12" customWidth="1" style="70" min="11" max="11"/>
-    <col width="13" customWidth="1" style="70" min="12" max="12"/>
+    <col width="12.77734375" customWidth="1" style="109" min="1" max="1"/>
+    <col width="13" customWidth="1" style="109" min="2" max="3"/>
+    <col width="15.77734375" customWidth="1" style="109" min="4" max="10"/>
+    <col width="20.77734375" customWidth="1" style="109" min="11" max="11"/>
+    <col width="15.77734375" customWidth="1" style="109" min="12" max="12"/>
+    <col width="13" customWidth="1" style="109" min="13" max="13"/>
+    <col width="8.88671875" customWidth="1" style="109" min="14" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.05" customHeight="1" s="70">
-      <c r="D1" s="35" t="inlineStr">
+    <row r="1" ht="40.05" customHeight="1" s="109">
+      <c r="D1" s="116" t="inlineStr">
         <is>
           <t>PERMISO DE TRABAJO DE ALTO RIESGO</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="14.4" customHeight="1" s="70">
-      <c r="D2" s="37" t="n"/>
-      <c r="E2" s="38" t="n"/>
-      <c r="F2" s="38" t="n"/>
-      <c r="G2" s="38" t="n"/>
-      <c r="H2" s="38" t="n"/>
-      <c r="I2" s="38" t="n"/>
-      <c r="J2" s="38" t="n"/>
-      <c r="K2" s="38" t="n"/>
-      <c r="L2" s="38" t="n"/>
-    </row>
-    <row r="3" ht="4.95" customHeight="1" s="70">
-      <c r="D3" s="75" t="n"/>
-      <c r="E3" s="56" t="n"/>
-      <c r="F3" s="56" t="n"/>
-      <c r="G3" s="56" t="n"/>
-      <c r="H3" s="56" t="n"/>
-      <c r="I3" s="56" t="n"/>
-      <c r="J3" s="56" t="n"/>
-      <c r="K3" s="56" t="n"/>
-      <c r="L3" s="56" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="70">
-      <c r="J4" s="53" t="inlineStr">
+    <row r="2" ht="14.4" customHeight="1" s="109">
+      <c r="D2" s="101" t="n"/>
+      <c r="E2" s="93" t="n"/>
+      <c r="F2" s="93" t="n"/>
+      <c r="G2" s="93" t="n"/>
+      <c r="H2" s="93" t="n"/>
+      <c r="I2" s="93" t="n"/>
+      <c r="J2" s="93" t="n"/>
+      <c r="K2" s="93" t="n"/>
+      <c r="L2" s="93" t="n"/>
+      <c r="M2" s="93" t="n"/>
+    </row>
+    <row r="3" ht="4.95" customHeight="1" s="109">
+      <c r="D3" s="117" t="n"/>
+      <c r="E3" s="96" t="n"/>
+      <c r="F3" s="96" t="n"/>
+      <c r="G3" s="96" t="n"/>
+      <c r="H3" s="96" t="n"/>
+      <c r="I3" s="96" t="n"/>
+      <c r="J3" s="96" t="n"/>
+      <c r="K3" s="96" t="n"/>
+      <c r="L3" s="96" t="n"/>
+      <c r="M3" s="96" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="109">
+      <c r="D4" s="119" t="n"/>
+      <c r="J4" s="100" t="n"/>
+      <c r="K4" s="179" t="inlineStr">
         <is>
           <t>CONTROL DOCUMENTAL</t>
         </is>
       </c>
-      <c r="K4" s="30" t="n"/>
-      <c r="L4" s="31" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="70">
-      <c r="D5" s="40" t="inlineStr">
+      <c r="L4" s="86" t="n"/>
+      <c r="M4" s="87" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="109">
+      <c r="D5" s="180" t="inlineStr">
         <is>
           <t>REFORMAS Y REMODELACIONES</t>
         </is>
       </c>
-      <c r="I5" s="41" t="n"/>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="100" t="n"/>
+      <c r="K5" s="126" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="K5" s="49" t="inlineStr">
+      <c r="L5" s="174" t="inlineStr">
         <is>
           <t>RYR-SS-007</t>
         </is>
       </c>
-      <c r="L5" s="31" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="70">
-      <c r="D6" s="44" t="inlineStr">
+      <c r="M5" s="87" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="109">
+      <c r="D6" s="181" t="inlineStr">
         <is>
           <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN.</t>
         </is>
       </c>
-      <c r="I6" s="41" t="n"/>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="100" t="n"/>
+      <c r="K6" s="126" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="K6" s="49" t="n">
+      <c r="L6" s="174" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="31" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="70">
-      <c r="D7" s="80" t="n"/>
-      <c r="E7" s="80" t="n"/>
-      <c r="F7" s="80" t="n"/>
-      <c r="G7" s="80" t="n"/>
-      <c r="H7" s="80" t="n"/>
-      <c r="I7" s="81" t="n"/>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="M6" s="87" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="109">
+      <c r="D7" s="130" t="n"/>
+      <c r="J7" s="100" t="n"/>
+      <c r="K7" s="126" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="K7" s="49" t="inlineStr">
+      <c r="L7" s="174" t="inlineStr">
         <is>
           <t>04/10/2026</t>
         </is>
       </c>
-      <c r="L7" s="31" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="70">
-      <c r="D8" s="66" t="n"/>
-      <c r="E8" s="66" t="n"/>
-      <c r="F8" s="66" t="n"/>
-      <c r="G8" s="66" t="n"/>
-      <c r="H8" s="66" t="n"/>
-      <c r="I8" s="81" t="n"/>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="M7" s="87" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="109">
+      <c r="D8" s="132" t="n"/>
+      <c r="E8" s="182" t="n"/>
+      <c r="F8" s="182" t="n"/>
+      <c r="G8" s="182" t="n"/>
+      <c r="H8" s="182" t="n"/>
+      <c r="I8" s="182" t="n"/>
+      <c r="J8" s="183" t="n"/>
+      <c r="K8" s="126" t="inlineStr">
         <is>
           <t>Página</t>
         </is>
       </c>
-      <c r="K8" s="49" t="inlineStr">
+      <c r="L8" s="174" t="inlineStr">
         <is>
           <t>1 de 2</t>
         </is>
       </c>
-      <c r="L8" s="31" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="70">
-      <c r="A9" s="103" t="inlineStr">
+      <c r="M8" s="87" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="109">
+      <c r="A9" s="133" t="inlineStr">
         <is>
           <t>Autorización escrita antes de iniciar el trabajo · Decreto 1072 de 2015 · Resolución 4272 de 2021 (alturas)</t>
         </is>
       </c>
-      <c r="B9" s="115" t="n"/>
-      <c r="C9" s="115" t="n"/>
-      <c r="D9" s="115" t="n"/>
-      <c r="E9" s="115" t="n"/>
-      <c r="F9" s="115" t="n"/>
-      <c r="G9" s="115" t="n"/>
-      <c r="H9" s="115" t="n"/>
-      <c r="I9" s="115" t="n"/>
-      <c r="J9" s="115" t="n"/>
-      <c r="K9" s="115" t="n"/>
-      <c r="L9" s="116" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1" s="70">
-      <c r="A10" s="117" t="inlineStr">
+      <c r="B9" s="134" t="n"/>
+      <c r="C9" s="134" t="n"/>
+      <c r="D9" s="134" t="n"/>
+      <c r="E9" s="134" t="n"/>
+      <c r="F9" s="134" t="n"/>
+      <c r="G9" s="134" t="n"/>
+      <c r="H9" s="134" t="n"/>
+      <c r="I9" s="134" t="n"/>
+      <c r="J9" s="134" t="n"/>
+      <c r="K9" s="134" t="n"/>
+      <c r="L9" s="134" t="n"/>
+      <c r="M9" s="135" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1" s="109">
+      <c r="A10" s="136" t="inlineStr">
         <is>
           <t>TIPO DE PERMISO DE TRABAJO</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n"/>
-      <c r="C10" s="47" t="n"/>
-      <c r="D10" s="118" t="n"/>
-      <c r="E10" s="130" t="n"/>
-      <c r="F10" s="130" t="n"/>
-      <c r="G10" s="130" t="n"/>
-      <c r="H10" s="130" t="n"/>
-      <c r="I10" s="130" t="n"/>
-      <c r="J10" s="130" t="n"/>
-      <c r="K10" s="130" t="n"/>
-      <c r="L10" s="131" t="n"/>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" s="70">
-      <c r="A11" s="54" t="inlineStr">
+      <c r="B10" s="93" t="n"/>
+      <c r="C10" s="94" t="n"/>
+      <c r="D10" s="184" t="n"/>
+      <c r="E10" s="199" t="n"/>
+      <c r="F10" s="199" t="n"/>
+      <c r="G10" s="199" t="n"/>
+      <c r="H10" s="199" t="n"/>
+      <c r="I10" s="199" t="n"/>
+      <c r="J10" s="199" t="n"/>
+      <c r="K10" s="199" t="n"/>
+      <c r="L10" s="199" t="n"/>
+      <c r="M10" s="200" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="109">
+      <c r="A11" s="137" t="inlineStr">
         <is>
           <t>1. DATOS DEL PERMISO</t>
         </is>
       </c>
-      <c r="B11" s="38" t="n"/>
-      <c r="C11" s="38" t="n"/>
-      <c r="D11" s="38" t="n"/>
-      <c r="E11" s="38" t="n"/>
-      <c r="F11" s="38" t="n"/>
-      <c r="G11" s="38" t="n"/>
-      <c r="H11" s="38" t="n"/>
-      <c r="I11" s="38" t="n"/>
-      <c r="J11" s="38" t="n"/>
-      <c r="K11" s="38" t="n"/>
-      <c r="L11" s="47" t="n"/>
-    </row>
-    <row r="12" ht="21" customHeight="1" s="70">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="B11" s="93" t="n"/>
+      <c r="C11" s="93" t="n"/>
+      <c r="D11" s="93" t="n"/>
+      <c r="E11" s="93" t="n"/>
+      <c r="F11" s="93" t="n"/>
+      <c r="G11" s="93" t="n"/>
+      <c r="H11" s="93" t="n"/>
+      <c r="I11" s="93" t="n"/>
+      <c r="J11" s="93" t="n"/>
+      <c r="K11" s="93" t="n"/>
+      <c r="L11" s="93" t="n"/>
+      <c r="M11" s="94" t="n"/>
+    </row>
+    <row r="12" ht="21" customHeight="1" s="109">
+      <c r="A12" s="143" t="inlineStr">
         <is>
           <t>Proyecto / Obra</t>
         </is>
       </c>
-      <c r="B12" s="31" t="n"/>
-      <c r="C12" s="50" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="30" t="n"/>
-      <c r="H12" s="30" t="n"/>
-      <c r="I12" s="30" t="n"/>
-      <c r="J12" s="30" t="n"/>
-      <c r="K12" s="30" t="n"/>
-      <c r="L12" s="31" t="n"/>
-    </row>
-    <row r="13" ht="21" customHeight="1" s="70">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="B12" s="87" t="n"/>
+      <c r="C12" s="139" t="n"/>
+      <c r="D12" s="86" t="n"/>
+      <c r="E12" s="86" t="n"/>
+      <c r="F12" s="86" t="n"/>
+      <c r="G12" s="86" t="n"/>
+      <c r="H12" s="86" t="n"/>
+      <c r="I12" s="86" t="n"/>
+      <c r="J12" s="86" t="n"/>
+      <c r="K12" s="86" t="n"/>
+      <c r="L12" s="86" t="n"/>
+      <c r="M12" s="87" t="n"/>
+    </row>
+    <row r="13" ht="21" customHeight="1" s="109">
+      <c r="A13" s="143" t="inlineStr">
         <is>
           <t>Contratista / Empresa</t>
         </is>
       </c>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="43" t="n"/>
-      <c r="D13" s="30" t="n"/>
-      <c r="E13" s="30" t="n"/>
-      <c r="F13" s="30" t="n"/>
-      <c r="G13" s="31" t="n"/>
-      <c r="H13" s="33" t="inlineStr">
+      <c r="B13" s="87" t="n"/>
+      <c r="C13" s="140" t="n"/>
+      <c r="D13" s="86" t="n"/>
+      <c r="E13" s="86" t="n"/>
+      <c r="F13" s="86" t="n"/>
+      <c r="G13" s="87" t="n"/>
+      <c r="H13" s="143" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="I13" s="31" t="n"/>
-      <c r="J13" s="43" t="n"/>
-      <c r="K13" s="30" t="n"/>
-      <c r="L13" s="31" t="n"/>
-    </row>
-    <row r="14" ht="21" customHeight="1" s="70">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="I13" s="87" t="n"/>
+      <c r="J13" s="140" t="n"/>
+      <c r="K13" s="86" t="n"/>
+      <c r="L13" s="86" t="n"/>
+      <c r="M13" s="87" t="n"/>
+    </row>
+    <row r="14" ht="21" customHeight="1" s="109">
+      <c r="A14" s="143" t="inlineStr">
         <is>
           <t>N° de permiso</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n"/>
-      <c r="C14" s="48" t="n"/>
-      <c r="D14" s="33" t="inlineStr">
+      <c r="B14" s="87" t="n"/>
+      <c r="C14" s="146" t="n"/>
+      <c r="D14" s="143" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="E14" s="48" t="n"/>
-      <c r="F14" s="33" t="inlineStr">
+      <c r="E14" s="146" t="n"/>
+      <c r="F14" s="143" t="inlineStr">
         <is>
           <t>Hora inicio</t>
         </is>
       </c>
-      <c r="G14" s="48" t="n"/>
-      <c r="H14" s="33" t="inlineStr">
+      <c r="G14" s="146" t="n"/>
+      <c r="H14" s="143" t="inlineStr">
         <is>
           <t>Hora fin</t>
         </is>
       </c>
-      <c r="I14" s="48" t="n"/>
-      <c r="J14" s="33" t="inlineStr">
+      <c r="I14" s="146" t="n"/>
+      <c r="J14" s="143" t="inlineStr">
         <is>
           <t>Vigencia</t>
         </is>
       </c>
-      <c r="K14" s="48" t="n"/>
-      <c r="L14" s="31" t="n"/>
-    </row>
-    <row r="15" ht="21" customHeight="1" s="70">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="K14" s="87" t="n"/>
+      <c r="L14" s="146" t="n"/>
+      <c r="M14" s="87" t="n"/>
+    </row>
+    <row r="15" ht="21" customHeight="1" s="109">
+      <c r="A15" s="143" t="inlineStr">
         <is>
           <t>Frente / lugar del trabajo</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n"/>
-      <c r="C15" s="43" t="n"/>
-      <c r="D15" s="30" t="n"/>
-      <c r="E15" s="30" t="n"/>
-      <c r="F15" s="30" t="n"/>
-      <c r="G15" s="31" t="n"/>
-      <c r="H15" s="33" t="inlineStr">
+      <c r="B15" s="87" t="n"/>
+      <c r="C15" s="140" t="n"/>
+      <c r="D15" s="86" t="n"/>
+      <c r="E15" s="86" t="n"/>
+      <c r="F15" s="86" t="n"/>
+      <c r="G15" s="87" t="n"/>
+      <c r="H15" s="143" t="inlineStr">
         <is>
           <t>Altura o profundidad (m)</t>
         </is>
       </c>
-      <c r="I15" s="31" t="n"/>
-      <c r="J15" s="43" t="n"/>
-      <c r="K15" s="30" t="n"/>
-      <c r="L15" s="31" t="n"/>
-    </row>
-    <row r="16" ht="21" customHeight="1" s="70">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="I15" s="87" t="n"/>
+      <c r="J15" s="140" t="n"/>
+      <c r="K15" s="86" t="n"/>
+      <c r="L15" s="86" t="n"/>
+      <c r="M15" s="87" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1" s="109">
+      <c r="A16" s="143" t="inlineStr">
         <is>
           <t>Equipo, sustancia o circuito</t>
         </is>
       </c>
-      <c r="B16" s="31" t="n"/>
-      <c r="C16" s="43" t="n"/>
-      <c r="D16" s="30" t="n"/>
-      <c r="E16" s="30" t="n"/>
-      <c r="F16" s="30" t="n"/>
-      <c r="G16" s="30" t="n"/>
-      <c r="H16" s="30" t="n"/>
-      <c r="I16" s="30" t="n"/>
-      <c r="J16" s="30" t="n"/>
-      <c r="K16" s="30" t="n"/>
-      <c r="L16" s="31" t="n"/>
-    </row>
-    <row r="17" ht="36" customHeight="1" s="70">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="B16" s="87" t="n"/>
+      <c r="C16" s="140" t="n"/>
+      <c r="D16" s="86" t="n"/>
+      <c r="E16" s="86" t="n"/>
+      <c r="F16" s="86" t="n"/>
+      <c r="G16" s="86" t="n"/>
+      <c r="H16" s="86" t="n"/>
+      <c r="I16" s="86" t="n"/>
+      <c r="J16" s="86" t="n"/>
+      <c r="K16" s="86" t="n"/>
+      <c r="L16" s="86" t="n"/>
+      <c r="M16" s="87" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1" s="109">
+      <c r="A17" s="143" t="inlineStr">
         <is>
           <t>Descripción del trabajo</t>
         </is>
       </c>
-      <c r="B17" s="31" t="n"/>
-      <c r="C17" s="52" t="n"/>
-      <c r="D17" s="30" t="n"/>
-      <c r="E17" s="30" t="n"/>
-      <c r="F17" s="30" t="n"/>
-      <c r="G17" s="30" t="n"/>
-      <c r="H17" s="30" t="n"/>
-      <c r="I17" s="30" t="n"/>
-      <c r="J17" s="30" t="n"/>
-      <c r="K17" s="30" t="n"/>
-      <c r="L17" s="31" t="n"/>
-    </row>
-    <row r="18" ht="21" customHeight="1" s="70">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="B17" s="87" t="n"/>
+      <c r="C17" s="147" t="n"/>
+      <c r="D17" s="86" t="n"/>
+      <c r="E17" s="86" t="n"/>
+      <c r="F17" s="86" t="n"/>
+      <c r="G17" s="86" t="n"/>
+      <c r="H17" s="86" t="n"/>
+      <c r="I17" s="86" t="n"/>
+      <c r="J17" s="86" t="n"/>
+      <c r="K17" s="86" t="n"/>
+      <c r="L17" s="86" t="n"/>
+      <c r="M17" s="87" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1" s="109">
+      <c r="A18" s="143" t="inlineStr">
         <is>
           <t>Solicitante</t>
         </is>
       </c>
-      <c r="B18" s="31" t="n"/>
-      <c r="C18" s="43" t="n"/>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="30" t="n"/>
-      <c r="F18" s="30" t="n"/>
-      <c r="G18" s="31" t="n"/>
-      <c r="H18" s="33" t="inlineStr">
+      <c r="B18" s="87" t="n"/>
+      <c r="C18" s="140" t="n"/>
+      <c r="D18" s="86" t="n"/>
+      <c r="E18" s="86" t="n"/>
+      <c r="F18" s="86" t="n"/>
+      <c r="G18" s="87" t="n"/>
+      <c r="H18" s="143" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="I18" s="31" t="n"/>
-      <c r="J18" s="43" t="n"/>
-      <c r="K18" s="30" t="n"/>
-      <c r="L18" s="31" t="n"/>
-    </row>
-    <row r="19" ht="16.5" customHeight="1" s="70">
-      <c r="A19" s="54" t="inlineStr">
+      <c r="I18" s="87" t="n"/>
+      <c r="J18" s="140" t="n"/>
+      <c r="K18" s="86" t="n"/>
+      <c r="L18" s="86" t="n"/>
+      <c r="M18" s="87" t="n"/>
+    </row>
+    <row r="19" ht="16.5" customHeight="1" s="109">
+      <c r="A19" s="137" t="inlineStr">
         <is>
           <t>2. PERSONAL QUE EJECUTA EL TRABAJO</t>
         </is>
       </c>
-      <c r="B19" s="38" t="n"/>
-      <c r="C19" s="38" t="n"/>
-      <c r="D19" s="38" t="n"/>
-      <c r="E19" s="38" t="n"/>
-      <c r="F19" s="38" t="n"/>
-      <c r="G19" s="38" t="n"/>
-      <c r="H19" s="38" t="n"/>
-      <c r="I19" s="38" t="n"/>
-      <c r="J19" s="38" t="n"/>
-      <c r="K19" s="38" t="n"/>
-      <c r="L19" s="47" t="n"/>
-    </row>
-    <row r="20" ht="19" customHeight="1" s="70">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="B19" s="93" t="n"/>
+      <c r="C19" s="93" t="n"/>
+      <c r="D19" s="93" t="n"/>
+      <c r="E19" s="93" t="n"/>
+      <c r="F19" s="93" t="n"/>
+      <c r="G19" s="93" t="n"/>
+      <c r="H19" s="93" t="n"/>
+      <c r="I19" s="93" t="n"/>
+      <c r="J19" s="93" t="n"/>
+      <c r="K19" s="93" t="n"/>
+      <c r="L19" s="93" t="n"/>
+      <c r="M19" s="94" t="n"/>
+    </row>
+    <row r="20" ht="19.05" customHeight="1" s="109">
+      <c r="A20" s="149" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B20" s="34" t="inlineStr">
+      <c r="B20" s="149" t="inlineStr">
         <is>
           <t>Nombre completo</t>
         </is>
       </c>
-      <c r="C20" s="30" t="n"/>
-      <c r="D20" s="31" t="n"/>
-      <c r="E20" s="34" t="inlineStr">
+      <c r="C20" s="86" t="n"/>
+      <c r="D20" s="87" t="n"/>
+      <c r="E20" s="149" t="inlineStr">
         <is>
           <t>Documento de identidad</t>
         </is>
       </c>
-      <c r="F20" s="31" t="n"/>
-      <c r="G20" s="34" t="inlineStr">
+      <c r="F20" s="87" t="n"/>
+      <c r="G20" s="149" t="inlineStr">
         <is>
           <t>Cargo / oficio</t>
         </is>
       </c>
-      <c r="H20" s="31" t="n"/>
-      <c r="I20" s="34" t="inlineStr">
-        <is>
-          <t>Certificación (tipo y vigencia)</t>
-        </is>
-      </c>
-      <c r="J20" s="31" t="n"/>
-      <c r="K20" s="34" t="inlineStr">
+      <c r="H20" s="87" t="n"/>
+      <c r="I20" s="149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo de Certificación </t>
+        </is>
+      </c>
+      <c r="J20" s="87" t="n"/>
+      <c r="K20" s="150" t="inlineStr">
+        <is>
+          <t>Fecha de vencimiento</t>
+        </is>
+      </c>
+      <c r="L20" s="149" t="inlineStr">
         <is>
           <t>Firma</t>
         </is>
       </c>
-      <c r="L20" s="31" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1" s="70">
-      <c r="A21" s="57" t="n">
+      <c r="M20" s="87" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="109">
+      <c r="A21" s="174" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="29" t="n"/>
-      <c r="C21" s="30" t="n"/>
-      <c r="D21" s="31" t="n"/>
-      <c r="E21" s="29" t="n"/>
-      <c r="F21" s="31" t="n"/>
-      <c r="G21" s="29" t="n"/>
-      <c r="H21" s="31" t="n"/>
-      <c r="I21" s="29" t="n"/>
-      <c r="J21" s="31" t="n"/>
-      <c r="K21" s="29" t="n"/>
-      <c r="L21" s="31" t="n"/>
-    </row>
-    <row r="22" ht="28" customHeight="1" s="70">
-      <c r="A22" s="57" t="n">
+      <c r="B21" s="175" t="n"/>
+      <c r="C21" s="86" t="n"/>
+      <c r="D21" s="87" t="n"/>
+      <c r="E21" s="175" t="n"/>
+      <c r="F21" s="87" t="n"/>
+      <c r="G21" s="175" t="n"/>
+      <c r="H21" s="87" t="n"/>
+      <c r="I21" s="175" t="n"/>
+      <c r="J21" s="87" t="n"/>
+      <c r="K21" s="178" t="n"/>
+      <c r="L21" s="175" t="n"/>
+      <c r="M21" s="87" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1" s="109">
+      <c r="A22" s="174" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="29" t="n"/>
-      <c r="C22" s="30" t="n"/>
-      <c r="D22" s="31" t="n"/>
-      <c r="E22" s="29" t="n"/>
-      <c r="F22" s="31" t="n"/>
-      <c r="G22" s="29" t="n"/>
-      <c r="H22" s="31" t="n"/>
-      <c r="I22" s="29" t="n"/>
-      <c r="J22" s="31" t="n"/>
-      <c r="K22" s="29" t="n"/>
-      <c r="L22" s="31" t="n"/>
-    </row>
-    <row r="23" ht="28" customHeight="1" s="70">
-      <c r="A23" s="57" t="n">
+      <c r="B22" s="175" t="n"/>
+      <c r="C22" s="86" t="n"/>
+      <c r="D22" s="87" t="n"/>
+      <c r="E22" s="175" t="n"/>
+      <c r="F22" s="87" t="n"/>
+      <c r="G22" s="175" t="n"/>
+      <c r="H22" s="87" t="n"/>
+      <c r="I22" s="175" t="n"/>
+      <c r="J22" s="87" t="n"/>
+      <c r="K22" s="178" t="n"/>
+      <c r="L22" s="175" t="n"/>
+      <c r="M22" s="87" t="n"/>
+    </row>
+    <row r="23" ht="30" customHeight="1" s="109">
+      <c r="A23" s="174" t="n">
         <v>3</v>
       </c>
-      <c r="B23" s="29" t="n"/>
-      <c r="C23" s="30" t="n"/>
-      <c r="D23" s="31" t="n"/>
-      <c r="E23" s="29" t="n"/>
-      <c r="F23" s="31" t="n"/>
-      <c r="G23" s="29" t="n"/>
-      <c r="H23" s="31" t="n"/>
-      <c r="I23" s="29" t="n"/>
-      <c r="J23" s="31" t="n"/>
-      <c r="K23" s="29" t="n"/>
-      <c r="L23" s="31" t="n"/>
-    </row>
-    <row r="24" ht="28" customHeight="1" s="70">
-      <c r="A24" s="57" t="n">
+      <c r="B23" s="175" t="n"/>
+      <c r="C23" s="86" t="n"/>
+      <c r="D23" s="87" t="n"/>
+      <c r="E23" s="175" t="n"/>
+      <c r="F23" s="87" t="n"/>
+      <c r="G23" s="175" t="n"/>
+      <c r="H23" s="87" t="n"/>
+      <c r="I23" s="175" t="n"/>
+      <c r="J23" s="87" t="n"/>
+      <c r="K23" s="178" t="n"/>
+      <c r="L23" s="175" t="n"/>
+      <c r="M23" s="87" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1" s="109">
+      <c r="A24" s="174" t="n">
         <v>4</v>
       </c>
-      <c r="B24" s="29" t="n"/>
-      <c r="C24" s="30" t="n"/>
-      <c r="D24" s="31" t="n"/>
-      <c r="E24" s="29" t="n"/>
-      <c r="F24" s="31" t="n"/>
-      <c r="G24" s="29" t="n"/>
-      <c r="H24" s="31" t="n"/>
-      <c r="I24" s="29" t="n"/>
-      <c r="J24" s="31" t="n"/>
-      <c r="K24" s="29" t="n"/>
-      <c r="L24" s="31" t="n"/>
-    </row>
-    <row r="25" ht="28" customHeight="1" s="70">
-      <c r="A25" s="57" t="n">
+      <c r="B24" s="175" t="n"/>
+      <c r="C24" s="86" t="n"/>
+      <c r="D24" s="87" t="n"/>
+      <c r="E24" s="175" t="n"/>
+      <c r="F24" s="87" t="n"/>
+      <c r="G24" s="175" t="n"/>
+      <c r="H24" s="87" t="n"/>
+      <c r="I24" s="175" t="n"/>
+      <c r="J24" s="87" t="n"/>
+      <c r="K24" s="178" t="n"/>
+      <c r="L24" s="175" t="n"/>
+      <c r="M24" s="87" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1" s="109">
+      <c r="A25" s="174" t="n">
         <v>5</v>
       </c>
-      <c r="B25" s="29" t="n"/>
-      <c r="C25" s="30" t="n"/>
-      <c r="D25" s="31" t="n"/>
-      <c r="E25" s="29" t="n"/>
-      <c r="F25" s="31" t="n"/>
-      <c r="G25" s="29" t="n"/>
-      <c r="H25" s="31" t="n"/>
-      <c r="I25" s="29" t="n"/>
-      <c r="J25" s="31" t="n"/>
-      <c r="K25" s="29" t="n"/>
-      <c r="L25" s="31" t="n"/>
-    </row>
-    <row r="26" ht="28" customHeight="1" s="70">
-      <c r="A26" s="57" t="n">
+      <c r="B25" s="175" t="n"/>
+      <c r="C25" s="86" t="n"/>
+      <c r="D25" s="87" t="n"/>
+      <c r="E25" s="175" t="n"/>
+      <c r="F25" s="87" t="n"/>
+      <c r="G25" s="175" t="n"/>
+      <c r="H25" s="87" t="n"/>
+      <c r="I25" s="175" t="n"/>
+      <c r="J25" s="87" t="n"/>
+      <c r="K25" s="178" t="n"/>
+      <c r="L25" s="175" t="n"/>
+      <c r="M25" s="87" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1" s="109">
+      <c r="A26" s="174" t="n">
         <v>6</v>
       </c>
-      <c r="B26" s="29" t="n"/>
-      <c r="C26" s="30" t="n"/>
-      <c r="D26" s="31" t="n"/>
-      <c r="E26" s="29" t="n"/>
-      <c r="F26" s="31" t="n"/>
-      <c r="G26" s="29" t="n"/>
-      <c r="H26" s="31" t="n"/>
-      <c r="I26" s="29" t="n"/>
-      <c r="J26" s="31" t="n"/>
-      <c r="K26" s="29" t="n"/>
-      <c r="L26" s="31" t="n"/>
-    </row>
-    <row r="27" ht="16.5" customHeight="1" s="70">
-      <c r="A27" s="54" t="inlineStr">
+      <c r="B26" s="175" t="n"/>
+      <c r="C26" s="86" t="n"/>
+      <c r="D26" s="87" t="n"/>
+      <c r="E26" s="175" t="n"/>
+      <c r="F26" s="87" t="n"/>
+      <c r="G26" s="175" t="n"/>
+      <c r="H26" s="87" t="n"/>
+      <c r="I26" s="175" t="n"/>
+      <c r="J26" s="87" t="n"/>
+      <c r="K26" s="178" t="n"/>
+      <c r="L26" s="175" t="n"/>
+      <c r="M26" s="87" t="n"/>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" s="109">
+      <c r="A27" s="137" t="inlineStr">
         <is>
           <t>3. VERIFICACIÓN PREVIA (antes de iniciar)</t>
         </is>
       </c>
-      <c r="B27" s="38" t="n"/>
-      <c r="C27" s="38" t="n"/>
-      <c r="D27" s="38" t="n"/>
-      <c r="E27" s="38" t="n"/>
-      <c r="F27" s="38" t="n"/>
-      <c r="G27" s="38" t="n"/>
-      <c r="H27" s="38" t="n"/>
-      <c r="I27" s="38" t="n"/>
-      <c r="J27" s="38" t="n"/>
-      <c r="K27" s="38" t="n"/>
-      <c r="L27" s="47" t="n"/>
-    </row>
-    <row r="28" ht="19" customHeight="1" s="70">
-      <c r="A28" s="34" t="inlineStr">
+      <c r="B27" s="93" t="n"/>
+      <c r="C27" s="93" t="n"/>
+      <c r="D27" s="93" t="n"/>
+      <c r="E27" s="93" t="n"/>
+      <c r="F27" s="93" t="n"/>
+      <c r="G27" s="93" t="n"/>
+      <c r="H27" s="93" t="n"/>
+      <c r="I27" s="93" t="n"/>
+      <c r="J27" s="93" t="n"/>
+      <c r="K27" s="93" t="n"/>
+      <c r="L27" s="93" t="n"/>
+      <c r="M27" s="94" t="n"/>
+    </row>
+    <row r="28" ht="19.05" customHeight="1" s="109">
+      <c r="A28" s="149" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B28" s="34" t="inlineStr">
+      <c r="B28" s="149" t="inlineStr">
         <is>
           <t>Condición que se verifica</t>
         </is>
       </c>
-      <c r="C28" s="30" t="n"/>
-      <c r="D28" s="30" t="n"/>
-      <c r="E28" s="30" t="n"/>
-      <c r="F28" s="30" t="n"/>
-      <c r="G28" s="30" t="n"/>
-      <c r="H28" s="31" t="n"/>
-      <c r="I28" s="34" t="inlineStr">
+      <c r="C28" s="86" t="n"/>
+      <c r="D28" s="86" t="n"/>
+      <c r="E28" s="86" t="n"/>
+      <c r="F28" s="86" t="n"/>
+      <c r="G28" s="86" t="n"/>
+      <c r="H28" s="87" t="n"/>
+      <c r="I28" s="149" t="inlineStr">
         <is>
           <t>¿Cumple?</t>
         </is>
       </c>
-      <c r="J28" s="31" t="n"/>
-      <c r="K28" s="34" t="inlineStr">
+      <c r="J28" s="87" t="n"/>
+      <c r="K28" s="149" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
-      <c r="L28" s="31" t="n"/>
-    </row>
-    <row r="29" ht="17" customHeight="1" s="70">
-      <c r="A29" s="57" t="n">
+      <c r="L28" s="86" t="n"/>
+      <c r="M28" s="87" t="n"/>
+    </row>
+    <row r="29" ht="16.95" customHeight="1" s="109">
+      <c r="A29" s="158" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="89" t="inlineStr">
+      <c r="B29" s="157" t="inlineStr">
         <is>
           <t>ATS elaborado, socializado y firmado por todo el personal que ejecuta</t>
         </is>
       </c>
-      <c r="C29" s="30" t="n"/>
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="30" t="n"/>
-      <c r="F29" s="30" t="n"/>
-      <c r="G29" s="30" t="n"/>
-      <c r="H29" s="31" t="n"/>
-      <c r="I29" s="57" t="n"/>
-      <c r="J29" s="31" t="n"/>
-      <c r="K29" s="29" t="n"/>
-      <c r="L29" s="31" t="n"/>
-    </row>
-    <row r="30" ht="17" customHeight="1" s="70">
-      <c r="A30" s="57" t="n">
+      <c r="C29" s="86" t="n"/>
+      <c r="D29" s="86" t="n"/>
+      <c r="E29" s="86" t="n"/>
+      <c r="F29" s="86" t="n"/>
+      <c r="G29" s="86" t="n"/>
+      <c r="H29" s="87" t="n"/>
+      <c r="I29" s="158" t="n"/>
+      <c r="J29" s="87" t="n"/>
+      <c r="K29" s="185" t="n"/>
+      <c r="L29" s="86" t="n"/>
+      <c r="M29" s="87" t="n"/>
+    </row>
+    <row r="30" ht="16.95" customHeight="1" s="109">
+      <c r="A30" s="158" t="n">
         <v>2</v>
       </c>
-      <c r="B30" s="89" t="inlineStr">
+      <c r="B30" s="157" t="inlineStr">
         <is>
           <t>Personal con aptitud médica y capacitación o certificación vigente para este trabajo</t>
         </is>
       </c>
-      <c r="C30" s="30" t="n"/>
-      <c r="D30" s="30" t="n"/>
-      <c r="E30" s="30" t="n"/>
-      <c r="F30" s="30" t="n"/>
-      <c r="G30" s="30" t="n"/>
-      <c r="H30" s="31" t="n"/>
-      <c r="I30" s="57" t="n"/>
-      <c r="J30" s="31" t="n"/>
-      <c r="K30" s="29" t="n"/>
-      <c r="L30" s="31" t="n"/>
-    </row>
-    <row r="31" ht="17" customHeight="1" s="70">
-      <c r="A31" s="57" t="n">
+      <c r="C30" s="86" t="n"/>
+      <c r="D30" s="86" t="n"/>
+      <c r="E30" s="86" t="n"/>
+      <c r="F30" s="86" t="n"/>
+      <c r="G30" s="86" t="n"/>
+      <c r="H30" s="87" t="n"/>
+      <c r="I30" s="158" t="n"/>
+      <c r="J30" s="87" t="n"/>
+      <c r="K30" s="185" t="n"/>
+      <c r="L30" s="86" t="n"/>
+      <c r="M30" s="87" t="n"/>
+    </row>
+    <row r="31" ht="16.95" customHeight="1" s="109">
+      <c r="A31" s="158" t="n">
         <v>3</v>
       </c>
-      <c r="B31" s="89" t="inlineStr">
+      <c r="B31" s="157" t="inlineStr">
         <is>
           <t>Elementos de protección personal completos, certificados y en buen estado</t>
         </is>
       </c>
-      <c r="C31" s="30" t="n"/>
-      <c r="D31" s="30" t="n"/>
-      <c r="E31" s="30" t="n"/>
-      <c r="F31" s="30" t="n"/>
-      <c r="G31" s="30" t="n"/>
-      <c r="H31" s="31" t="n"/>
-      <c r="I31" s="57" t="n"/>
-      <c r="J31" s="31" t="n"/>
-      <c r="K31" s="29" t="n"/>
-      <c r="L31" s="31" t="n"/>
-    </row>
-    <row r="32" ht="17" customHeight="1" s="70">
-      <c r="A32" s="57" t="n">
+      <c r="C31" s="86" t="n"/>
+      <c r="D31" s="86" t="n"/>
+      <c r="E31" s="86" t="n"/>
+      <c r="F31" s="86" t="n"/>
+      <c r="G31" s="86" t="n"/>
+      <c r="H31" s="87" t="n"/>
+      <c r="I31" s="158" t="n"/>
+      <c r="J31" s="87" t="n"/>
+      <c r="K31" s="185" t="n"/>
+      <c r="L31" s="86" t="n"/>
+      <c r="M31" s="87" t="n"/>
+    </row>
+    <row r="32" ht="16.95" customHeight="1" s="109">
+      <c r="A32" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="B32" s="89" t="inlineStr">
+      <c r="B32" s="157" t="inlineStr">
         <is>
           <t>Área demarcada, señalizada y con acceso restringido a personas ajenas</t>
         </is>
       </c>
-      <c r="C32" s="30" t="n"/>
-      <c r="D32" s="30" t="n"/>
-      <c r="E32" s="30" t="n"/>
-      <c r="F32" s="30" t="n"/>
-      <c r="G32" s="30" t="n"/>
-      <c r="H32" s="31" t="n"/>
-      <c r="I32" s="57" t="n"/>
-      <c r="J32" s="31" t="n"/>
-      <c r="K32" s="29" t="n"/>
-      <c r="L32" s="31" t="n"/>
-    </row>
-    <row r="33" ht="17" customHeight="1" s="70">
-      <c r="A33" s="57" t="n">
+      <c r="C32" s="86" t="n"/>
+      <c r="D32" s="86" t="n"/>
+      <c r="E32" s="86" t="n"/>
+      <c r="F32" s="86" t="n"/>
+      <c r="G32" s="86" t="n"/>
+      <c r="H32" s="87" t="n"/>
+      <c r="I32" s="158" t="n"/>
+      <c r="J32" s="87" t="n"/>
+      <c r="K32" s="185" t="n"/>
+      <c r="L32" s="86" t="n"/>
+      <c r="M32" s="87" t="n"/>
+    </row>
+    <row r="33" ht="16.95" customHeight="1" s="109">
+      <c r="A33" s="158" t="n">
         <v>5</v>
       </c>
-      <c r="B33" s="89" t="inlineStr">
+      <c r="B33" s="157" t="inlineStr">
         <is>
           <t>Herramientas, equipos y sistemas de protección inspeccionados</t>
         </is>
       </c>
-      <c r="C33" s="30" t="n"/>
-      <c r="D33" s="30" t="n"/>
-      <c r="E33" s="30" t="n"/>
-      <c r="F33" s="30" t="n"/>
-      <c r="G33" s="30" t="n"/>
-      <c r="H33" s="31" t="n"/>
-      <c r="I33" s="57" t="n"/>
-      <c r="J33" s="31" t="n"/>
-      <c r="K33" s="29" t="n"/>
-      <c r="L33" s="31" t="n"/>
-    </row>
-    <row r="34" ht="17" customHeight="1" s="70">
-      <c r="A34" s="57" t="n">
+      <c r="C33" s="86" t="n"/>
+      <c r="D33" s="86" t="n"/>
+      <c r="E33" s="86" t="n"/>
+      <c r="F33" s="86" t="n"/>
+      <c r="G33" s="86" t="n"/>
+      <c r="H33" s="87" t="n"/>
+      <c r="I33" s="158" t="n"/>
+      <c r="J33" s="87" t="n"/>
+      <c r="K33" s="185" t="n"/>
+      <c r="L33" s="86" t="n"/>
+      <c r="M33" s="87" t="n"/>
+    </row>
+    <row r="34" ht="16.95" customHeight="1" s="109">
+      <c r="A34" s="158" t="n">
         <v>6</v>
       </c>
-      <c r="B34" s="89" t="inlineStr">
+      <c r="B34" s="157" t="inlineStr">
         <is>
           <t>Plan de emergencia y de rescate conocido; medio de comunicación disponible</t>
         </is>
       </c>
-      <c r="C34" s="30" t="n"/>
-      <c r="D34" s="30" t="n"/>
-      <c r="E34" s="30" t="n"/>
-      <c r="F34" s="30" t="n"/>
-      <c r="G34" s="30" t="n"/>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="57" t="n"/>
-      <c r="J34" s="31" t="n"/>
-      <c r="K34" s="29" t="n"/>
-      <c r="L34" s="31" t="n"/>
-    </row>
-    <row r="35" ht="17" customHeight="1" s="70">
-      <c r="A35" s="57" t="n">
+      <c r="C34" s="86" t="n"/>
+      <c r="D34" s="86" t="n"/>
+      <c r="E34" s="86" t="n"/>
+      <c r="F34" s="86" t="n"/>
+      <c r="G34" s="86" t="n"/>
+      <c r="H34" s="87" t="n"/>
+      <c r="I34" s="158" t="n"/>
+      <c r="J34" s="87" t="n"/>
+      <c r="K34" s="185" t="n"/>
+      <c r="L34" s="86" t="n"/>
+      <c r="M34" s="87" t="n"/>
+    </row>
+    <row r="35" ht="16.95" customHeight="1" s="109">
+      <c r="A35" s="158" t="n">
         <v>7</v>
       </c>
-      <c r="B35" s="89" t="inlineStr">
+      <c r="B35" s="157" t="inlineStr">
         <is>
           <t>Extintor y botiquín disponibles en el sitio del trabajo</t>
         </is>
       </c>
-      <c r="C35" s="30" t="n"/>
-      <c r="D35" s="30" t="n"/>
-      <c r="E35" s="30" t="n"/>
-      <c r="F35" s="30" t="n"/>
-      <c r="G35" s="30" t="n"/>
-      <c r="H35" s="31" t="n"/>
-      <c r="I35" s="57" t="n"/>
-      <c r="J35" s="31" t="n"/>
-      <c r="K35" s="29" t="n"/>
-      <c r="L35" s="31" t="n"/>
-    </row>
-    <row r="36" ht="17" customHeight="1" s="70">
-      <c r="A36" s="57" t="n">
+      <c r="C35" s="86" t="n"/>
+      <c r="D35" s="86" t="n"/>
+      <c r="E35" s="86" t="n"/>
+      <c r="F35" s="86" t="n"/>
+      <c r="G35" s="86" t="n"/>
+      <c r="H35" s="87" t="n"/>
+      <c r="I35" s="158" t="n"/>
+      <c r="J35" s="87" t="n"/>
+      <c r="K35" s="185" t="n"/>
+      <c r="L35" s="86" t="n"/>
+      <c r="M35" s="87" t="n"/>
+    </row>
+    <row r="36" ht="16.95" customHeight="1" s="109">
+      <c r="A36" s="158" t="n">
         <v>8</v>
       </c>
-      <c r="B36" s="89" t="inlineStr">
+      <c r="B36" s="157" t="inlineStr">
         <is>
           <t>Condiciones del entorno evaluadas (lluvia, viento, tormenta eléctrica)</t>
         </is>
       </c>
-      <c r="C36" s="30" t="n"/>
-      <c r="D36" s="30" t="n"/>
-      <c r="E36" s="30" t="n"/>
-      <c r="F36" s="30" t="n"/>
-      <c r="G36" s="30" t="n"/>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="57" t="n"/>
-      <c r="J36" s="31" t="n"/>
-      <c r="K36" s="29" t="n"/>
-      <c r="L36" s="31" t="n"/>
-    </row>
-    <row r="37" ht="17" customHeight="1" s="70">
-      <c r="A37" s="57" t="n">
+      <c r="C36" s="86" t="n"/>
+      <c r="D36" s="86" t="n"/>
+      <c r="E36" s="86" t="n"/>
+      <c r="F36" s="86" t="n"/>
+      <c r="G36" s="86" t="n"/>
+      <c r="H36" s="87" t="n"/>
+      <c r="I36" s="158" t="n"/>
+      <c r="J36" s="87" t="n"/>
+      <c r="K36" s="185" t="n"/>
+      <c r="L36" s="86" t="n"/>
+      <c r="M36" s="87" t="n"/>
+    </row>
+    <row r="37" ht="16.95" customHeight="1" s="109">
+      <c r="A37" s="158" t="n">
         <v>9</v>
       </c>
-      <c r="B37" s="89" t="inlineStr">
+      <c r="B37" s="157" t="inlineStr">
         <is>
           <t>Permisos complementarios tramitados y adjuntos (si aplica)</t>
         </is>
       </c>
-      <c r="C37" s="30" t="n"/>
-      <c r="D37" s="30" t="n"/>
-      <c r="E37" s="30" t="n"/>
-      <c r="F37" s="30" t="n"/>
-      <c r="G37" s="30" t="n"/>
-      <c r="H37" s="31" t="n"/>
-      <c r="I37" s="57" t="n"/>
-      <c r="J37" s="31" t="n"/>
-      <c r="K37" s="29" t="n"/>
-      <c r="L37" s="31" t="n"/>
-    </row>
-    <row r="38" ht="17" customHeight="1" s="70">
-      <c r="A38" s="57" t="n">
+      <c r="C37" s="86" t="n"/>
+      <c r="D37" s="86" t="n"/>
+      <c r="E37" s="86" t="n"/>
+      <c r="F37" s="86" t="n"/>
+      <c r="G37" s="86" t="n"/>
+      <c r="H37" s="87" t="n"/>
+      <c r="I37" s="158" t="n"/>
+      <c r="J37" s="87" t="n"/>
+      <c r="K37" s="185" t="n"/>
+      <c r="L37" s="86" t="n"/>
+      <c r="M37" s="87" t="n"/>
+    </row>
+    <row r="38" ht="16.95" customHeight="1" s="109">
+      <c r="A38" s="158" t="n">
         <v>10</v>
       </c>
-      <c r="B38" s="89" t="inlineStr">
+      <c r="B38" s="157" t="inlineStr">
         <is>
           <t>Coordinación con otras actividades simultáneas en el área</t>
         </is>
       </c>
-      <c r="C38" s="30" t="n"/>
-      <c r="D38" s="30" t="n"/>
-      <c r="E38" s="30" t="n"/>
-      <c r="F38" s="30" t="n"/>
-      <c r="G38" s="30" t="n"/>
-      <c r="H38" s="31" t="n"/>
-      <c r="I38" s="57" t="n"/>
-      <c r="J38" s="31" t="n"/>
-      <c r="K38" s="29" t="n"/>
-      <c r="L38" s="31" t="n"/>
-    </row>
-    <row r="39" ht="16.5" customHeight="1" s="70">
-      <c r="A39" s="54" t="inlineStr">
+      <c r="C38" s="86" t="n"/>
+      <c r="D38" s="86" t="n"/>
+      <c r="E38" s="86" t="n"/>
+      <c r="F38" s="86" t="n"/>
+      <c r="G38" s="86" t="n"/>
+      <c r="H38" s="87" t="n"/>
+      <c r="I38" s="158" t="n"/>
+      <c r="J38" s="87" t="n"/>
+      <c r="K38" s="185" t="n"/>
+      <c r="L38" s="86" t="n"/>
+      <c r="M38" s="87" t="n"/>
+    </row>
+    <row r="39" ht="16.5" customHeight="1" s="109">
+      <c r="A39" s="137" t="inlineStr">
         <is>
           <t>4. REQUISITOS ESPECÍFICOS DEL PERMISO (según el tipo elegido arriba)</t>
         </is>
       </c>
-      <c r="B39" s="38" t="n"/>
-      <c r="C39" s="38" t="n"/>
-      <c r="D39" s="38" t="n"/>
-      <c r="E39" s="38" t="n"/>
-      <c r="F39" s="38" t="n"/>
-      <c r="G39" s="38" t="n"/>
-      <c r="H39" s="38" t="n"/>
-      <c r="I39" s="38" t="n"/>
-      <c r="J39" s="38" t="n"/>
-      <c r="K39" s="38" t="n"/>
-      <c r="L39" s="47" t="n"/>
-    </row>
-    <row r="40" ht="19" customHeight="1" s="70">
-      <c r="A40" s="34" t="inlineStr">
+      <c r="B39" s="93" t="n"/>
+      <c r="C39" s="93" t="n"/>
+      <c r="D39" s="93" t="n"/>
+      <c r="E39" s="93" t="n"/>
+      <c r="F39" s="93" t="n"/>
+      <c r="G39" s="93" t="n"/>
+      <c r="H39" s="93" t="n"/>
+      <c r="I39" s="93" t="n"/>
+      <c r="J39" s="93" t="n"/>
+      <c r="K39" s="93" t="n"/>
+      <c r="L39" s="93" t="n"/>
+      <c r="M39" s="94" t="n"/>
+    </row>
+    <row r="40" ht="19.05" customHeight="1" s="109">
+      <c r="A40" s="149" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B40" s="34" t="inlineStr">
+      <c r="B40" s="149" t="inlineStr">
         <is>
           <t>Requisito</t>
         </is>
       </c>
-      <c r="C40" s="30" t="n"/>
-      <c r="D40" s="30" t="n"/>
-      <c r="E40" s="30" t="n"/>
-      <c r="F40" s="30" t="n"/>
-      <c r="G40" s="31" t="n"/>
-      <c r="H40" s="34" t="inlineStr">
+      <c r="C40" s="86" t="n"/>
+      <c r="D40" s="86" t="n"/>
+      <c r="E40" s="86" t="n"/>
+      <c r="F40" s="86" t="n"/>
+      <c r="G40" s="87" t="n"/>
+      <c r="H40" s="149" t="inlineStr">
         <is>
           <t>Cumple</t>
         </is>
       </c>
-      <c r="I40" s="34" t="inlineStr">
+      <c r="I40" s="149" t="inlineStr">
         <is>
           <t>No cumple</t>
         </is>
       </c>
-      <c r="J40" s="34" t="inlineStr">
+      <c r="J40" s="149" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K40" s="34" t="inlineStr">
+      <c r="K40" s="149" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
-      <c r="L40" s="31" t="n"/>
-    </row>
-    <row r="41" ht="24" customHeight="1" s="70">
-      <c r="A41" s="57" t="n">
+      <c r="L40" s="86" t="n"/>
+      <c r="M40" s="87" t="n"/>
+    </row>
+    <row r="41" ht="24" customHeight="1" s="109">
+      <c r="A41" s="158" t="n">
         <v>1</v>
       </c>
-      <c r="B41" s="89" t="n"/>
-      <c r="C41" s="30" t="n"/>
-      <c r="D41" s="30" t="n"/>
-      <c r="E41" s="30" t="n"/>
-      <c r="F41" s="30" t="n"/>
-      <c r="G41" s="31" t="n"/>
-      <c r="H41" s="57" t="n"/>
-      <c r="I41" s="57" t="n"/>
-      <c r="J41" s="57" t="n"/>
-      <c r="K41" s="29" t="n"/>
-      <c r="L41" s="31" t="n"/>
-    </row>
-    <row r="42" ht="24" customHeight="1" s="70">
-      <c r="A42" s="57" t="n">
+      <c r="B41" s="157" t="n"/>
+      <c r="C41" s="86" t="n"/>
+      <c r="D41" s="86" t="n"/>
+      <c r="E41" s="86" t="n"/>
+      <c r="F41" s="86" t="n"/>
+      <c r="G41" s="87" t="n"/>
+      <c r="H41" s="158" t="n"/>
+      <c r="I41" s="158" t="n"/>
+      <c r="J41" s="158" t="n"/>
+      <c r="K41" s="158" t="n"/>
+      <c r="L41" s="86" t="n"/>
+      <c r="M41" s="87" t="n"/>
+    </row>
+    <row r="42" ht="24" customHeight="1" s="109">
+      <c r="A42" s="158" t="n">
         <v>2</v>
       </c>
-      <c r="B42" s="89" t="n"/>
-      <c r="C42" s="30" t="n"/>
-      <c r="D42" s="30" t="n"/>
-      <c r="E42" s="30" t="n"/>
-      <c r="F42" s="30" t="n"/>
-      <c r="G42" s="31" t="n"/>
-      <c r="H42" s="57" t="n"/>
-      <c r="I42" s="57" t="n"/>
-      <c r="J42" s="57" t="n"/>
-      <c r="K42" s="29" t="n"/>
-      <c r="L42" s="31" t="n"/>
-    </row>
-    <row r="43" ht="24" customHeight="1" s="70">
-      <c r="A43" s="57" t="n">
+      <c r="B42" s="157" t="n"/>
+      <c r="C42" s="86" t="n"/>
+      <c r="D42" s="86" t="n"/>
+      <c r="E42" s="86" t="n"/>
+      <c r="F42" s="86" t="n"/>
+      <c r="G42" s="87" t="n"/>
+      <c r="H42" s="158" t="n"/>
+      <c r="I42" s="158" t="n"/>
+      <c r="J42" s="158" t="n"/>
+      <c r="K42" s="158" t="n"/>
+      <c r="L42" s="86" t="n"/>
+      <c r="M42" s="87" t="n"/>
+    </row>
+    <row r="43" ht="24" customHeight="1" s="109">
+      <c r="A43" s="158" t="n">
         <v>3</v>
       </c>
-      <c r="B43" s="89" t="n"/>
-      <c r="C43" s="30" t="n"/>
-      <c r="D43" s="30" t="n"/>
-      <c r="E43" s="30" t="n"/>
-      <c r="F43" s="30" t="n"/>
-      <c r="G43" s="31" t="n"/>
-      <c r="H43" s="57" t="n"/>
-      <c r="I43" s="57" t="n"/>
-      <c r="J43" s="57" t="n"/>
-      <c r="K43" s="29" t="n"/>
-      <c r="L43" s="31" t="n"/>
-    </row>
-    <row r="44" ht="24" customHeight="1" s="70">
-      <c r="A44" s="57" t="n">
+      <c r="B43" s="157" t="n"/>
+      <c r="C43" s="86" t="n"/>
+      <c r="D43" s="86" t="n"/>
+      <c r="E43" s="86" t="n"/>
+      <c r="F43" s="86" t="n"/>
+      <c r="G43" s="87" t="n"/>
+      <c r="H43" s="158" t="n"/>
+      <c r="I43" s="158" t="n"/>
+      <c r="J43" s="158" t="n"/>
+      <c r="K43" s="158" t="n"/>
+      <c r="L43" s="86" t="n"/>
+      <c r="M43" s="87" t="n"/>
+    </row>
+    <row r="44" ht="24" customHeight="1" s="109">
+      <c r="A44" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="B44" s="89" t="n"/>
-      <c r="C44" s="30" t="n"/>
-      <c r="D44" s="30" t="n"/>
-      <c r="E44" s="30" t="n"/>
-      <c r="F44" s="30" t="n"/>
-      <c r="G44" s="31" t="n"/>
-      <c r="H44" s="57" t="n"/>
-      <c r="I44" s="57" t="n"/>
-      <c r="J44" s="57" t="n"/>
-      <c r="K44" s="29" t="n"/>
-      <c r="L44" s="31" t="n"/>
-    </row>
-    <row r="45" ht="24" customHeight="1" s="70">
-      <c r="A45" s="57" t="n">
+      <c r="B44" s="157" t="n"/>
+      <c r="C44" s="86" t="n"/>
+      <c r="D44" s="86" t="n"/>
+      <c r="E44" s="86" t="n"/>
+      <c r="F44" s="86" t="n"/>
+      <c r="G44" s="87" t="n"/>
+      <c r="H44" s="158" t="n"/>
+      <c r="I44" s="158" t="n"/>
+      <c r="J44" s="158" t="n"/>
+      <c r="K44" s="158" t="n"/>
+      <c r="L44" s="86" t="n"/>
+      <c r="M44" s="87" t="n"/>
+    </row>
+    <row r="45" ht="24" customHeight="1" s="109">
+      <c r="A45" s="158" t="n">
         <v>5</v>
       </c>
-      <c r="B45" s="89" t="n"/>
-      <c r="C45" s="30" t="n"/>
-      <c r="D45" s="30" t="n"/>
-      <c r="E45" s="30" t="n"/>
-      <c r="F45" s="30" t="n"/>
-      <c r="G45" s="31" t="n"/>
-      <c r="H45" s="57" t="n"/>
-      <c r="I45" s="57" t="n"/>
-      <c r="J45" s="57" t="n"/>
-      <c r="K45" s="29" t="n"/>
-      <c r="L45" s="31" t="n"/>
-    </row>
-    <row r="46" ht="24" customHeight="1" s="70">
-      <c r="A46" s="57" t="n">
+      <c r="B45" s="157" t="n"/>
+      <c r="C45" s="86" t="n"/>
+      <c r="D45" s="86" t="n"/>
+      <c r="E45" s="86" t="n"/>
+      <c r="F45" s="86" t="n"/>
+      <c r="G45" s="87" t="n"/>
+      <c r="H45" s="158" t="n"/>
+      <c r="I45" s="158" t="n"/>
+      <c r="J45" s="158" t="n"/>
+      <c r="K45" s="158" t="n"/>
+      <c r="L45" s="86" t="n"/>
+      <c r="M45" s="87" t="n"/>
+    </row>
+    <row r="46" ht="24" customHeight="1" s="109">
+      <c r="A46" s="158" t="n">
         <v>6</v>
       </c>
-      <c r="B46" s="89" t="n"/>
-      <c r="C46" s="30" t="n"/>
-      <c r="D46" s="30" t="n"/>
-      <c r="E46" s="30" t="n"/>
-      <c r="F46" s="30" t="n"/>
-      <c r="G46" s="31" t="n"/>
-      <c r="H46" s="57" t="n"/>
-      <c r="I46" s="57" t="n"/>
-      <c r="J46" s="57" t="n"/>
-      <c r="K46" s="29" t="n"/>
-      <c r="L46" s="31" t="n"/>
-    </row>
-    <row r="47" ht="24" customHeight="1" s="70">
-      <c r="A47" s="57" t="n">
+      <c r="B46" s="157" t="n"/>
+      <c r="C46" s="86" t="n"/>
+      <c r="D46" s="86" t="n"/>
+      <c r="E46" s="86" t="n"/>
+      <c r="F46" s="86" t="n"/>
+      <c r="G46" s="87" t="n"/>
+      <c r="H46" s="158" t="n"/>
+      <c r="I46" s="158" t="n"/>
+      <c r="J46" s="158" t="n"/>
+      <c r="K46" s="158" t="n"/>
+      <c r="L46" s="86" t="n"/>
+      <c r="M46" s="87" t="n"/>
+    </row>
+    <row r="47" ht="24" customHeight="1" s="109">
+      <c r="A47" s="158" t="n">
         <v>7</v>
       </c>
-      <c r="B47" s="89" t="n"/>
-      <c r="C47" s="30" t="n"/>
-      <c r="D47" s="30" t="n"/>
-      <c r="E47" s="30" t="n"/>
-      <c r="F47" s="30" t="n"/>
-      <c r="G47" s="31" t="n"/>
-      <c r="H47" s="57" t="n"/>
-      <c r="I47" s="57" t="n"/>
-      <c r="J47" s="57" t="n"/>
-      <c r="K47" s="29" t="n"/>
-      <c r="L47" s="31" t="n"/>
-    </row>
-    <row r="48" ht="24" customHeight="1" s="70">
-      <c r="A48" s="57" t="n">
+      <c r="B47" s="157" t="n"/>
+      <c r="C47" s="86" t="n"/>
+      <c r="D47" s="86" t="n"/>
+      <c r="E47" s="86" t="n"/>
+      <c r="F47" s="86" t="n"/>
+      <c r="G47" s="87" t="n"/>
+      <c r="H47" s="158" t="n"/>
+      <c r="I47" s="158" t="n"/>
+      <c r="J47" s="158" t="n"/>
+      <c r="K47" s="158" t="n"/>
+      <c r="L47" s="86" t="n"/>
+      <c r="M47" s="87" t="n"/>
+    </row>
+    <row r="48" ht="24" customHeight="1" s="109">
+      <c r="A48" s="158" t="n">
         <v>8</v>
       </c>
-      <c r="B48" s="89" t="n"/>
-      <c r="C48" s="30" t="n"/>
-      <c r="D48" s="30" t="n"/>
-      <c r="E48" s="30" t="n"/>
-      <c r="F48" s="30" t="n"/>
-      <c r="G48" s="31" t="n"/>
-      <c r="H48" s="57" t="n"/>
-      <c r="I48" s="57" t="n"/>
-      <c r="J48" s="57" t="n"/>
-      <c r="K48" s="29" t="n"/>
-      <c r="L48" s="31" t="n"/>
-    </row>
-    <row r="49" ht="24" customHeight="1" s="70">
-      <c r="A49" s="57" t="n">
+      <c r="B48" s="157" t="n"/>
+      <c r="C48" s="86" t="n"/>
+      <c r="D48" s="86" t="n"/>
+      <c r="E48" s="86" t="n"/>
+      <c r="F48" s="86" t="n"/>
+      <c r="G48" s="87" t="n"/>
+      <c r="H48" s="158" t="n"/>
+      <c r="I48" s="158" t="n"/>
+      <c r="J48" s="158" t="n"/>
+      <c r="K48" s="158" t="n"/>
+      <c r="L48" s="86" t="n"/>
+      <c r="M48" s="87" t="n"/>
+    </row>
+    <row r="49" ht="24" customHeight="1" s="109">
+      <c r="A49" s="158" t="n">
         <v>9</v>
       </c>
-      <c r="B49" s="89" t="n"/>
-      <c r="C49" s="30" t="n"/>
-      <c r="D49" s="30" t="n"/>
-      <c r="E49" s="30" t="n"/>
-      <c r="F49" s="30" t="n"/>
-      <c r="G49" s="31" t="n"/>
-      <c r="H49" s="57" t="n"/>
-      <c r="I49" s="57" t="n"/>
-      <c r="J49" s="57" t="n"/>
-      <c r="K49" s="29" t="n"/>
-      <c r="L49" s="31" t="n"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" s="70">
-      <c r="A50" s="57" t="n">
+      <c r="B49" s="157" t="n"/>
+      <c r="C49" s="86" t="n"/>
+      <c r="D49" s="86" t="n"/>
+      <c r="E49" s="86" t="n"/>
+      <c r="F49" s="86" t="n"/>
+      <c r="G49" s="87" t="n"/>
+      <c r="H49" s="158" t="n"/>
+      <c r="I49" s="158" t="n"/>
+      <c r="J49" s="158" t="n"/>
+      <c r="K49" s="158" t="n"/>
+      <c r="L49" s="86" t="n"/>
+      <c r="M49" s="87" t="n"/>
+    </row>
+    <row r="50" ht="24" customHeight="1" s="109">
+      <c r="A50" s="158" t="n">
         <v>10</v>
       </c>
-      <c r="B50" s="89" t="n"/>
-      <c r="C50" s="30" t="n"/>
-      <c r="D50" s="30" t="n"/>
-      <c r="E50" s="30" t="n"/>
-      <c r="F50" s="30" t="n"/>
-      <c r="G50" s="31" t="n"/>
-      <c r="H50" s="57" t="n"/>
-      <c r="I50" s="57" t="n"/>
-      <c r="J50" s="57" t="n"/>
-      <c r="K50" s="29" t="n"/>
-      <c r="L50" s="31" t="n"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" s="70">
-      <c r="A51" s="57" t="n">
+      <c r="B50" s="157" t="n"/>
+      <c r="C50" s="86" t="n"/>
+      <c r="D50" s="86" t="n"/>
+      <c r="E50" s="86" t="n"/>
+      <c r="F50" s="86" t="n"/>
+      <c r="G50" s="87" t="n"/>
+      <c r="H50" s="158" t="n"/>
+      <c r="I50" s="158" t="n"/>
+      <c r="J50" s="158" t="n"/>
+      <c r="K50" s="158" t="n"/>
+      <c r="L50" s="86" t="n"/>
+      <c r="M50" s="87" t="n"/>
+    </row>
+    <row r="51" ht="24" customHeight="1" s="109">
+      <c r="A51" s="158" t="n">
         <v>11</v>
       </c>
-      <c r="B51" s="89" t="n"/>
-      <c r="C51" s="30" t="n"/>
-      <c r="D51" s="30" t="n"/>
-      <c r="E51" s="30" t="n"/>
-      <c r="F51" s="30" t="n"/>
-      <c r="G51" s="31" t="n"/>
-      <c r="H51" s="57" t="n"/>
-      <c r="I51" s="57" t="n"/>
-      <c r="J51" s="57" t="n"/>
-      <c r="K51" s="29" t="n"/>
-      <c r="L51" s="31" t="n"/>
-    </row>
-    <row r="52" ht="24" customHeight="1" s="70">
-      <c r="A52" s="57" t="n">
+      <c r="B51" s="157" t="n"/>
+      <c r="C51" s="86" t="n"/>
+      <c r="D51" s="86" t="n"/>
+      <c r="E51" s="86" t="n"/>
+      <c r="F51" s="86" t="n"/>
+      <c r="G51" s="87" t="n"/>
+      <c r="H51" s="158" t="n"/>
+      <c r="I51" s="158" t="n"/>
+      <c r="J51" s="158" t="n"/>
+      <c r="K51" s="158" t="n"/>
+      <c r="L51" s="86" t="n"/>
+      <c r="M51" s="87" t="n"/>
+    </row>
+    <row r="52" ht="24" customHeight="1" s="109">
+      <c r="A52" s="158" t="n">
         <v>12</v>
       </c>
-      <c r="B52" s="89" t="n"/>
-      <c r="C52" s="30" t="n"/>
-      <c r="D52" s="30" t="n"/>
-      <c r="E52" s="30" t="n"/>
-      <c r="F52" s="30" t="n"/>
-      <c r="G52" s="31" t="n"/>
-      <c r="H52" s="57" t="n"/>
-      <c r="I52" s="57" t="n"/>
-      <c r="J52" s="57" t="n"/>
-      <c r="K52" s="29" t="n"/>
-      <c r="L52" s="31" t="n"/>
-    </row>
-    <row r="53" ht="16.5" customHeight="1" s="70">
-      <c r="A53" s="54" t="inlineStr">
+      <c r="B52" s="157" t="n"/>
+      <c r="C52" s="86" t="n"/>
+      <c r="D52" s="86" t="n"/>
+      <c r="E52" s="86" t="n"/>
+      <c r="F52" s="86" t="n"/>
+      <c r="G52" s="87" t="n"/>
+      <c r="H52" s="158" t="n"/>
+      <c r="I52" s="158" t="n"/>
+      <c r="J52" s="158" t="n"/>
+      <c r="K52" s="158" t="n"/>
+      <c r="L52" s="86" t="n"/>
+      <c r="M52" s="87" t="n"/>
+    </row>
+    <row r="53" ht="16.5" customHeight="1" s="109">
+      <c r="A53" s="137" t="inlineStr">
         <is>
           <t>5. MEDICIÓN DE GASES (espacios confinados, trabajo en caliente, sustancias químicas y excavaciones profundas)</t>
         </is>
       </c>
-      <c r="B53" s="38" t="n"/>
-      <c r="C53" s="38" t="n"/>
-      <c r="D53" s="38" t="n"/>
-      <c r="E53" s="38" t="n"/>
-      <c r="F53" s="38" t="n"/>
-      <c r="G53" s="38" t="n"/>
-      <c r="H53" s="38" t="n"/>
-      <c r="I53" s="38" t="n"/>
-      <c r="J53" s="38" t="n"/>
-      <c r="K53" s="38" t="n"/>
-      <c r="L53" s="47" t="n"/>
-    </row>
-    <row r="54" ht="22" customHeight="1" s="70">
-      <c r="A54" s="34" t="inlineStr">
+      <c r="B53" s="93" t="n"/>
+      <c r="C53" s="93" t="n"/>
+      <c r="D53" s="93" t="n"/>
+      <c r="E53" s="93" t="n"/>
+      <c r="F53" s="93" t="n"/>
+      <c r="G53" s="93" t="n"/>
+      <c r="H53" s="93" t="n"/>
+      <c r="I53" s="93" t="n"/>
+      <c r="J53" s="93" t="n"/>
+      <c r="K53" s="93" t="n"/>
+      <c r="L53" s="93" t="n"/>
+      <c r="M53" s="94" t="n"/>
+    </row>
+    <row r="54" ht="22.05" customHeight="1" s="109">
+      <c r="A54" s="149" t="inlineStr">
         <is>
           <t>Medición</t>
         </is>
       </c>
-      <c r="B54" s="31" t="n"/>
-      <c r="C54" s="34" t="inlineStr">
+      <c r="B54" s="87" t="n"/>
+      <c r="C54" s="149" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="D54" s="34" t="inlineStr">
+      <c r="D54" s="149" t="inlineStr">
         <is>
           <t>Oxígeno O₂ (%)</t>
         </is>
       </c>
-      <c r="E54" s="34" t="inlineStr">
+      <c r="E54" s="149" t="inlineStr">
         <is>
           <t>Explosividad LEL (%)</t>
         </is>
       </c>
-      <c r="F54" s="31" t="n"/>
-      <c r="G54" s="34" t="inlineStr">
+      <c r="F54" s="87" t="n"/>
+      <c r="G54" s="149" t="inlineStr">
         <is>
           <t>CO (ppm)</t>
         </is>
       </c>
-      <c r="H54" s="34" t="inlineStr">
+      <c r="H54" s="149" t="inlineStr">
         <is>
           <t>H₂S (ppm)</t>
         </is>
       </c>
-      <c r="I54" s="34" t="inlineStr">
+      <c r="I54" s="149" t="inlineStr">
         <is>
           <t>Responsable de la medición</t>
         </is>
       </c>
-      <c r="J54" s="30" t="n"/>
-      <c r="K54" s="30" t="n"/>
-      <c r="L54" s="31" t="n"/>
-    </row>
-    <row r="55" ht="19" customHeight="1" s="70">
-      <c r="A55" s="29" t="inlineStr">
+      <c r="J54" s="86" t="n"/>
+      <c r="K54" s="86" t="n"/>
+      <c r="L54" s="86" t="n"/>
+      <c r="M54" s="87" t="n"/>
+    </row>
+    <row r="55" ht="19.05" customHeight="1" s="109">
+      <c r="A55" s="163" t="inlineStr">
         <is>
           <t>Inicial</t>
         </is>
       </c>
-      <c r="B55" s="31" t="n"/>
-      <c r="C55" s="57" t="n"/>
-      <c r="D55" s="57" t="n"/>
-      <c r="E55" s="57" t="n"/>
-      <c r="F55" s="31" t="n"/>
-      <c r="G55" s="57" t="n"/>
-      <c r="H55" s="57" t="n"/>
-      <c r="I55" s="29" t="n"/>
-      <c r="J55" s="30" t="n"/>
-      <c r="K55" s="30" t="n"/>
-      <c r="L55" s="31" t="n"/>
-    </row>
-    <row r="56" ht="19" customHeight="1" s="70">
-      <c r="A56" s="29" t="inlineStr">
+      <c r="B55" s="87" t="n"/>
+      <c r="C55" s="158" t="n"/>
+      <c r="D55" s="158" t="n"/>
+      <c r="E55" s="158" t="n"/>
+      <c r="F55" s="87" t="n"/>
+      <c r="G55" s="158" t="n"/>
+      <c r="H55" s="158" t="n"/>
+      <c r="I55" s="163" t="n"/>
+      <c r="J55" s="86" t="n"/>
+      <c r="K55" s="86" t="n"/>
+      <c r="L55" s="86" t="n"/>
+      <c r="M55" s="87" t="n"/>
+    </row>
+    <row r="56" ht="19.05" customHeight="1" s="109">
+      <c r="A56" s="163" t="inlineStr">
         <is>
           <t>Intermedia</t>
         </is>
       </c>
-      <c r="B56" s="31" t="n"/>
-      <c r="C56" s="57" t="n"/>
-      <c r="D56" s="57" t="n"/>
-      <c r="E56" s="57" t="n"/>
-      <c r="F56" s="31" t="n"/>
-      <c r="G56" s="57" t="n"/>
-      <c r="H56" s="57" t="n"/>
-      <c r="I56" s="29" t="n"/>
-      <c r="J56" s="30" t="n"/>
-      <c r="K56" s="30" t="n"/>
-      <c r="L56" s="31" t="n"/>
-    </row>
-    <row r="57" ht="19" customHeight="1" s="70">
-      <c r="A57" s="29" t="inlineStr">
+      <c r="B56" s="87" t="n"/>
+      <c r="C56" s="158" t="n"/>
+      <c r="D56" s="158" t="n"/>
+      <c r="E56" s="158" t="n"/>
+      <c r="F56" s="87" t="n"/>
+      <c r="G56" s="158" t="n"/>
+      <c r="H56" s="158" t="n"/>
+      <c r="I56" s="163" t="n"/>
+      <c r="J56" s="86" t="n"/>
+      <c r="K56" s="86" t="n"/>
+      <c r="L56" s="86" t="n"/>
+      <c r="M56" s="87" t="n"/>
+    </row>
+    <row r="57" ht="19.05" customHeight="1" s="109">
+      <c r="A57" s="163" t="inlineStr">
         <is>
           <t>Final</t>
         </is>
       </c>
-      <c r="B57" s="31" t="n"/>
-      <c r="C57" s="57" t="n"/>
-      <c r="D57" s="57" t="n"/>
-      <c r="E57" s="57" t="n"/>
-      <c r="F57" s="31" t="n"/>
-      <c r="G57" s="57" t="n"/>
-      <c r="H57" s="57" t="n"/>
-      <c r="I57" s="29" t="n"/>
-      <c r="J57" s="30" t="n"/>
-      <c r="K57" s="30" t="n"/>
-      <c r="L57" s="31" t="n"/>
-    </row>
-    <row r="58" ht="16" customHeight="1" s="70">
-      <c r="A58" s="103" t="inlineStr">
+      <c r="B57" s="87" t="n"/>
+      <c r="C57" s="158" t="n"/>
+      <c r="D57" s="158" t="n"/>
+      <c r="E57" s="158" t="n"/>
+      <c r="F57" s="87" t="n"/>
+      <c r="G57" s="158" t="n"/>
+      <c r="H57" s="158" t="n"/>
+      <c r="I57" s="163" t="n"/>
+      <c r="J57" s="86" t="n"/>
+      <c r="K57" s="86" t="n"/>
+      <c r="L57" s="86" t="n"/>
+      <c r="M57" s="87" t="n"/>
+    </row>
+    <row r="58" ht="16.05" customHeight="1" s="109">
+      <c r="A58" s="133" t="inlineStr">
         <is>
           <t>Registre las lecturas. Los límites aceptables son los definidos en el procedimiento del proyecto. Obligatoria en espacios confinados.</t>
         </is>
       </c>
-      <c r="B58" s="115" t="n"/>
-      <c r="C58" s="115" t="n"/>
-      <c r="D58" s="115" t="n"/>
-      <c r="E58" s="115" t="n"/>
-      <c r="F58" s="115" t="n"/>
-      <c r="G58" s="115" t="n"/>
-      <c r="H58" s="115" t="n"/>
-      <c r="I58" s="115" t="n"/>
-      <c r="J58" s="115" t="n"/>
-      <c r="K58" s="115" t="n"/>
-      <c r="L58" s="116" t="n"/>
-    </row>
-    <row r="59" ht="16.5" customHeight="1" s="70">
-      <c r="A59" s="54" t="inlineStr">
+      <c r="B58" s="134" t="n"/>
+      <c r="C58" s="134" t="n"/>
+      <c r="D58" s="134" t="n"/>
+      <c r="E58" s="134" t="n"/>
+      <c r="F58" s="134" t="n"/>
+      <c r="G58" s="134" t="n"/>
+      <c r="H58" s="134" t="n"/>
+      <c r="I58" s="134" t="n"/>
+      <c r="J58" s="134" t="n"/>
+      <c r="K58" s="134" t="n"/>
+      <c r="L58" s="134" t="n"/>
+      <c r="M58" s="135" t="n"/>
+    </row>
+    <row r="59" ht="16.5" customHeight="1" s="109">
+      <c r="A59" s="137" t="inlineStr">
         <is>
           <t>6. AUTORIZACIÓN</t>
         </is>
       </c>
-      <c r="B59" s="38" t="n"/>
-      <c r="C59" s="38" t="n"/>
-      <c r="D59" s="38" t="n"/>
-      <c r="E59" s="38" t="n"/>
-      <c r="F59" s="38" t="n"/>
-      <c r="G59" s="38" t="n"/>
-      <c r="H59" s="38" t="n"/>
-      <c r="I59" s="38" t="n"/>
-      <c r="J59" s="38" t="n"/>
-      <c r="K59" s="38" t="n"/>
-      <c r="L59" s="47" t="n"/>
-    </row>
-    <row r="60" ht="18" customHeight="1" s="70">
-      <c r="A60" s="51" t="inlineStr">
+      <c r="B59" s="93" t="n"/>
+      <c r="C59" s="93" t="n"/>
+      <c r="D59" s="93" t="n"/>
+      <c r="E59" s="93" t="n"/>
+      <c r="F59" s="93" t="n"/>
+      <c r="G59" s="93" t="n"/>
+      <c r="H59" s="93" t="n"/>
+      <c r="I59" s="93" t="n"/>
+      <c r="J59" s="93" t="n"/>
+      <c r="K59" s="93" t="n"/>
+      <c r="L59" s="93" t="n"/>
+      <c r="M59" s="94" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1" s="109">
+      <c r="A60" s="164" t="inlineStr">
         <is>
           <t>SOLICITANTE</t>
         </is>
       </c>
-      <c r="B60" s="30" t="n"/>
-      <c r="C60" s="30" t="n"/>
-      <c r="D60" s="31" t="n"/>
-      <c r="E60" s="51" t="inlineStr">
+      <c r="B60" s="86" t="n"/>
+      <c r="C60" s="86" t="n"/>
+      <c r="D60" s="87" t="n"/>
+      <c r="E60" s="164" t="inlineStr">
         <is>
           <t>AUTORIZA — RESPONSABLE SST / RESIDENTE</t>
         </is>
       </c>
-      <c r="F60" s="30" t="n"/>
-      <c r="G60" s="30" t="n"/>
-      <c r="H60" s="31" t="n"/>
-      <c r="I60" s="51" t="inlineStr">
+      <c r="F60" s="86" t="n"/>
+      <c r="G60" s="86" t="n"/>
+      <c r="H60" s="87" t="n"/>
+      <c r="I60" s="164" t="inlineStr">
         <is>
           <t>VIGÍA / SUPERVISOR DEL TRABAJO</t>
         </is>
       </c>
-      <c r="J60" s="30" t="n"/>
-      <c r="K60" s="30" t="n"/>
-      <c r="L60" s="31" t="n"/>
-    </row>
-    <row r="61" ht="42" customHeight="1" s="70">
-      <c r="A61" s="39" t="inlineStr">
+      <c r="J60" s="86" t="n"/>
+      <c r="K60" s="86" t="n"/>
+      <c r="L60" s="86" t="n"/>
+      <c r="M60" s="87" t="n"/>
+    </row>
+    <row r="61" ht="42" customHeight="1" s="109">
+      <c r="A61" s="165" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="B61" s="31" t="n"/>
-      <c r="C61" s="43" t="n"/>
-      <c r="D61" s="31" t="n"/>
-      <c r="E61" s="39" t="inlineStr">
+      <c r="B61" s="87" t="n"/>
+      <c r="C61" s="140" t="n"/>
+      <c r="D61" s="87" t="n"/>
+      <c r="E61" s="165" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F61" s="31" t="n"/>
-      <c r="G61" s="43" t="n"/>
-      <c r="H61" s="31" t="n"/>
-      <c r="I61" s="39" t="inlineStr">
+      <c r="F61" s="87" t="n"/>
+      <c r="G61" s="140" t="n"/>
+      <c r="H61" s="87" t="n"/>
+      <c r="I61" s="165" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="J61" s="31" t="n"/>
-      <c r="K61" s="43" t="n"/>
-      <c r="L61" s="31" t="n"/>
-    </row>
-    <row r="62" ht="21" customHeight="1" s="70">
-      <c r="A62" s="39" t="inlineStr">
+      <c r="J61" s="87" t="n"/>
+      <c r="K61" s="185" t="n"/>
+      <c r="L61" s="86" t="n"/>
+      <c r="M61" s="87" t="n"/>
+    </row>
+    <row r="62" ht="21" customHeight="1" s="109">
+      <c r="A62" s="165" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="B62" s="31" t="n"/>
-      <c r="C62" s="43" t="n"/>
-      <c r="D62" s="31" t="n"/>
-      <c r="E62" s="39" t="inlineStr">
+      <c r="B62" s="87" t="n"/>
+      <c r="C62" s="140" t="n"/>
+      <c r="D62" s="87" t="n"/>
+      <c r="E62" s="165" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="F62" s="31" t="n"/>
-      <c r="G62" s="43" t="n"/>
-      <c r="H62" s="31" t="n"/>
-      <c r="I62" s="39" t="inlineStr">
+      <c r="F62" s="87" t="n"/>
+      <c r="G62" s="140" t="n"/>
+      <c r="H62" s="87" t="n"/>
+      <c r="I62" s="165" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="J62" s="31" t="n"/>
-      <c r="K62" s="43" t="n"/>
-      <c r="L62" s="31" t="n"/>
-    </row>
-    <row r="63" ht="21" customHeight="1" s="70">
-      <c r="A63" s="39" t="inlineStr">
+      <c r="J62" s="87" t="n"/>
+      <c r="K62" s="140" t="n"/>
+      <c r="L62" s="86" t="n"/>
+      <c r="M62" s="87" t="n"/>
+    </row>
+    <row r="63" ht="21" customHeight="1" s="109">
+      <c r="A63" s="165" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="B63" s="31" t="n"/>
-      <c r="C63" s="43" t="n"/>
-      <c r="D63" s="31" t="n"/>
-      <c r="E63" s="39" t="inlineStr">
+      <c r="B63" s="87" t="n"/>
+      <c r="C63" s="140" t="n"/>
+      <c r="D63" s="87" t="n"/>
+      <c r="E63" s="165" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="F63" s="31" t="n"/>
-      <c r="G63" s="43" t="n"/>
-      <c r="H63" s="31" t="n"/>
-      <c r="I63" s="39" t="inlineStr">
+      <c r="F63" s="87" t="n"/>
+      <c r="G63" s="140" t="n"/>
+      <c r="H63" s="87" t="n"/>
+      <c r="I63" s="165" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="J63" s="31" t="n"/>
-      <c r="K63" s="43" t="n"/>
-      <c r="L63" s="31" t="n"/>
-    </row>
-    <row r="64" ht="21" customHeight="1" s="70">
-      <c r="A64" s="39" t="inlineStr">
+      <c r="J63" s="87" t="n"/>
+      <c r="K63" s="140" t="n"/>
+      <c r="L63" s="86" t="n"/>
+      <c r="M63" s="87" t="n"/>
+    </row>
+    <row r="64" ht="21" customHeight="1" s="109">
+      <c r="A64" s="165" t="inlineStr">
         <is>
           <t>Hora:</t>
         </is>
       </c>
-      <c r="B64" s="31" t="n"/>
-      <c r="C64" s="43" t="n"/>
-      <c r="D64" s="31" t="n"/>
-      <c r="E64" s="39" t="inlineStr">
+      <c r="B64" s="87" t="n"/>
+      <c r="C64" s="140" t="n"/>
+      <c r="D64" s="87" t="n"/>
+      <c r="E64" s="165" t="inlineStr">
         <is>
           <t>Hora:</t>
         </is>
       </c>
-      <c r="F64" s="31" t="n"/>
-      <c r="G64" s="43" t="n"/>
-      <c r="H64" s="31" t="n"/>
-      <c r="I64" s="39" t="inlineStr">
+      <c r="F64" s="87" t="n"/>
+      <c r="G64" s="140" t="n"/>
+      <c r="H64" s="87" t="n"/>
+      <c r="I64" s="165" t="inlineStr">
         <is>
           <t>Hora:</t>
         </is>
       </c>
-      <c r="J64" s="31" t="n"/>
-      <c r="K64" s="43" t="n"/>
-      <c r="L64" s="31" t="n"/>
-    </row>
-    <row r="65" ht="16.5" customHeight="1" s="70">
-      <c r="A65" s="54" t="inlineStr">
+      <c r="J64" s="87" t="n"/>
+      <c r="K64" s="140" t="n"/>
+      <c r="L64" s="86" t="n"/>
+      <c r="M64" s="87" t="n"/>
+    </row>
+    <row r="65" ht="16.5" customHeight="1" s="109">
+      <c r="A65" s="137" t="inlineStr">
         <is>
           <t>7. CIERRE DEL PERMISO</t>
         </is>
       </c>
-      <c r="B65" s="38" t="n"/>
-      <c r="C65" s="38" t="n"/>
-      <c r="D65" s="38" t="n"/>
-      <c r="E65" s="38" t="n"/>
-      <c r="F65" s="38" t="n"/>
-      <c r="G65" s="38" t="n"/>
-      <c r="H65" s="38" t="n"/>
-      <c r="I65" s="38" t="n"/>
-      <c r="J65" s="38" t="n"/>
-      <c r="K65" s="38" t="n"/>
-      <c r="L65" s="47" t="n"/>
-    </row>
-    <row r="66" ht="24" customHeight="1" s="70">
-      <c r="A66" s="33" t="inlineStr">
+      <c r="B65" s="93" t="n"/>
+      <c r="C65" s="93" t="n"/>
+      <c r="D65" s="93" t="n"/>
+      <c r="E65" s="93" t="n"/>
+      <c r="F65" s="93" t="n"/>
+      <c r="G65" s="93" t="n"/>
+      <c r="H65" s="93" t="n"/>
+      <c r="I65" s="93" t="n"/>
+      <c r="J65" s="93" t="n"/>
+      <c r="K65" s="93" t="n"/>
+      <c r="L65" s="93" t="n"/>
+      <c r="M65" s="94" t="n"/>
+    </row>
+    <row r="66" ht="24" customHeight="1" s="109">
+      <c r="A66" s="143" t="inlineStr">
         <is>
           <t>Hora de cierre</t>
         </is>
       </c>
-      <c r="B66" s="31" t="n"/>
-      <c r="C66" s="48" t="n"/>
-      <c r="D66" s="31" t="n"/>
-      <c r="E66" s="33" t="inlineStr">
+      <c r="B66" s="87" t="n"/>
+      <c r="C66" s="146" t="n"/>
+      <c r="D66" s="87" t="n"/>
+      <c r="E66" s="143" t="inlineStr">
         <is>
           <t>¿Trabajo terminado?</t>
         </is>
       </c>
-      <c r="F66" s="31" t="n"/>
-      <c r="G66" s="48" t="n"/>
-      <c r="H66" s="31" t="n"/>
-      <c r="I66" s="33" t="inlineStr">
+      <c r="F66" s="87" t="n"/>
+      <c r="G66" s="146" t="n"/>
+      <c r="H66" s="87" t="n"/>
+      <c r="I66" s="143" t="inlineStr">
         <is>
           <t>¿Área en orden y sin energía residual?</t>
         </is>
       </c>
-      <c r="J66" s="31" t="n"/>
-      <c r="K66" s="48" t="n"/>
-      <c r="L66" s="31" t="n"/>
-    </row>
-    <row r="67" ht="30" customHeight="1" s="70">
-      <c r="A67" s="33" t="inlineStr">
+      <c r="J66" s="87" t="n"/>
+      <c r="K66" s="186" t="n"/>
+      <c r="L66" s="86" t="n"/>
+      <c r="M66" s="87" t="n"/>
+    </row>
+    <row r="67" ht="30" customHeight="1" s="109">
+      <c r="A67" s="143" t="inlineStr">
         <is>
           <t>Observaciones / novedades</t>
         </is>
       </c>
-      <c r="B67" s="31" t="n"/>
-      <c r="C67" s="52" t="n"/>
-      <c r="D67" s="30" t="n"/>
-      <c r="E67" s="30" t="n"/>
-      <c r="F67" s="30" t="n"/>
-      <c r="G67" s="30" t="n"/>
-      <c r="H67" s="30" t="n"/>
-      <c r="I67" s="30" t="n"/>
-      <c r="J67" s="30" t="n"/>
-      <c r="K67" s="30" t="n"/>
-      <c r="L67" s="31" t="n"/>
-    </row>
-    <row r="68" ht="24" customHeight="1" s="70">
-      <c r="A68" s="33" t="inlineStr">
+      <c r="B67" s="87" t="n"/>
+      <c r="C67" s="147" t="n"/>
+      <c r="D67" s="86" t="n"/>
+      <c r="E67" s="86" t="n"/>
+      <c r="F67" s="86" t="n"/>
+      <c r="G67" s="86" t="n"/>
+      <c r="H67" s="86" t="n"/>
+      <c r="I67" s="86" t="n"/>
+      <c r="J67" s="86" t="n"/>
+      <c r="K67" s="86" t="n"/>
+      <c r="L67" s="86" t="n"/>
+      <c r="M67" s="87" t="n"/>
+    </row>
+    <row r="68" ht="24" customHeight="1" s="109">
+      <c r="A68" s="143" t="inlineStr">
         <is>
           <t>Motivo de suspensión o cancelación</t>
         </is>
       </c>
-      <c r="B68" s="31" t="n"/>
-      <c r="C68" s="52" t="n"/>
-      <c r="D68" s="30" t="n"/>
-      <c r="E68" s="30" t="n"/>
-      <c r="F68" s="30" t="n"/>
-      <c r="G68" s="30" t="n"/>
-      <c r="H68" s="30" t="n"/>
-      <c r="I68" s="30" t="n"/>
-      <c r="J68" s="30" t="n"/>
-      <c r="K68" s="30" t="n"/>
-      <c r="L68" s="31" t="n"/>
-    </row>
-    <row r="69" ht="18" customHeight="1" s="70">
-      <c r="A69" s="51" t="inlineStr">
+      <c r="B68" s="87" t="n"/>
+      <c r="C68" s="147" t="n"/>
+      <c r="D68" s="86" t="n"/>
+      <c r="E68" s="86" t="n"/>
+      <c r="F68" s="86" t="n"/>
+      <c r="G68" s="86" t="n"/>
+      <c r="H68" s="86" t="n"/>
+      <c r="I68" s="86" t="n"/>
+      <c r="J68" s="86" t="n"/>
+      <c r="K68" s="86" t="n"/>
+      <c r="L68" s="86" t="n"/>
+      <c r="M68" s="87" t="n"/>
+    </row>
+    <row r="69" ht="18" customHeight="1" s="109">
+      <c r="A69" s="164" t="inlineStr">
         <is>
           <t>CIERRA — SOLICITANTE</t>
         </is>
       </c>
-      <c r="B69" s="30" t="n"/>
-      <c r="C69" s="30" t="n"/>
-      <c r="D69" s="30" t="n"/>
-      <c r="E69" s="30" t="n"/>
-      <c r="F69" s="31" t="n"/>
-      <c r="G69" s="51" t="inlineStr">
+      <c r="B69" s="86" t="n"/>
+      <c r="C69" s="86" t="n"/>
+      <c r="D69" s="86" t="n"/>
+      <c r="E69" s="86" t="n"/>
+      <c r="F69" s="87" t="n"/>
+      <c r="G69" s="164" t="inlineStr">
         <is>
           <t>RECIBE — RESPONSABLE SST / RESIDENTE</t>
         </is>
       </c>
-      <c r="H69" s="30" t="n"/>
-      <c r="I69" s="30" t="n"/>
-      <c r="J69" s="30" t="n"/>
-      <c r="K69" s="30" t="n"/>
-      <c r="L69" s="31" t="n"/>
-    </row>
-    <row r="70" ht="42" customHeight="1" s="70">
-      <c r="A70" s="39" t="inlineStr">
+      <c r="H69" s="86" t="n"/>
+      <c r="I69" s="86" t="n"/>
+      <c r="J69" s="86" t="n"/>
+      <c r="K69" s="86" t="n"/>
+      <c r="L69" s="86" t="n"/>
+      <c r="M69" s="87" t="n"/>
+    </row>
+    <row r="70" ht="42" customHeight="1" s="109">
+      <c r="A70" s="165" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="B70" s="31" t="n"/>
-      <c r="C70" s="43" t="n"/>
-      <c r="D70" s="30" t="n"/>
-      <c r="E70" s="30" t="n"/>
-      <c r="F70" s="31" t="n"/>
-      <c r="G70" s="39" t="inlineStr">
+      <c r="B70" s="87" t="n"/>
+      <c r="C70" s="140" t="n"/>
+      <c r="D70" s="86" t="n"/>
+      <c r="E70" s="86" t="n"/>
+      <c r="F70" s="87" t="n"/>
+      <c r="G70" s="165" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="H70" s="31" t="n"/>
-      <c r="I70" s="43" t="n"/>
-      <c r="J70" s="30" t="n"/>
-      <c r="K70" s="30" t="n"/>
-      <c r="L70" s="31" t="n"/>
-    </row>
-    <row r="71" ht="21" customHeight="1" s="70">
-      <c r="A71" s="39" t="inlineStr">
+      <c r="H70" s="87" t="n"/>
+      <c r="I70" s="140" t="n"/>
+      <c r="J70" s="86" t="n"/>
+      <c r="K70" s="86" t="n"/>
+      <c r="L70" s="86" t="n"/>
+      <c r="M70" s="87" t="n"/>
+    </row>
+    <row r="71" ht="21" customHeight="1" s="109">
+      <c r="A71" s="165" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="B71" s="31" t="n"/>
-      <c r="C71" s="43" t="n"/>
-      <c r="D71" s="30" t="n"/>
-      <c r="E71" s="30" t="n"/>
-      <c r="F71" s="31" t="n"/>
-      <c r="G71" s="39" t="inlineStr">
+      <c r="B71" s="87" t="n"/>
+      <c r="C71" s="140" t="n"/>
+      <c r="D71" s="86" t="n"/>
+      <c r="E71" s="86" t="n"/>
+      <c r="F71" s="87" t="n"/>
+      <c r="G71" s="165" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="H71" s="31" t="n"/>
-      <c r="I71" s="43" t="n"/>
-      <c r="J71" s="30" t="n"/>
-      <c r="K71" s="30" t="n"/>
-      <c r="L71" s="31" t="n"/>
-    </row>
-    <row r="72" ht="21" customHeight="1" s="70">
-      <c r="A72" s="39" t="inlineStr">
+      <c r="H71" s="87" t="n"/>
+      <c r="I71" s="140" t="n"/>
+      <c r="J71" s="86" t="n"/>
+      <c r="K71" s="86" t="n"/>
+      <c r="L71" s="86" t="n"/>
+      <c r="M71" s="87" t="n"/>
+    </row>
+    <row r="72" ht="21" customHeight="1" s="109">
+      <c r="A72" s="165" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="B72" s="31" t="n"/>
-      <c r="C72" s="43" t="n"/>
-      <c r="D72" s="30" t="n"/>
-      <c r="E72" s="30" t="n"/>
-      <c r="F72" s="31" t="n"/>
-      <c r="G72" s="39" t="inlineStr">
+      <c r="B72" s="87" t="n"/>
+      <c r="C72" s="140" t="n"/>
+      <c r="D72" s="86" t="n"/>
+      <c r="E72" s="86" t="n"/>
+      <c r="F72" s="87" t="n"/>
+      <c r="G72" s="165" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="H72" s="31" t="n"/>
-      <c r="I72" s="43" t="n"/>
-      <c r="J72" s="30" t="n"/>
-      <c r="K72" s="30" t="n"/>
-      <c r="L72" s="31" t="n"/>
+      <c r="H72" s="87" t="n"/>
+      <c r="I72" s="140" t="n"/>
+      <c r="J72" s="86" t="n"/>
+      <c r="K72" s="86" t="n"/>
+      <c r="L72" s="86" t="n"/>
+      <c r="M72" s="87" t="n"/>
     </row>
     <row r="73"/>
     <row r="74">
-      <c r="A74" s="61" t="inlineStr">
+      <c r="A74" s="169" t="inlineStr">
         <is>
           <t>REV. 04/10/2026</t>
         </is>
       </c>
-      <c r="G74" s="63">
-        <f>K5</f>
+      <c r="G74" s="170">
+        <f>L5</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="198">
+  <mergeCells count="202">
     <mergeCell ref="G21:H21"/>
-    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="A64:B64"/>
     <mergeCell ref="C62:D62"/>
-    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="K46:M46"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="K40:M40"/>
     <mergeCell ref="G71:H71"/>
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="C72:F72"/>
     <mergeCell ref="G23:H23"/>
     <mergeCell ref="B33:H33"/>
-    <mergeCell ref="G69:L69"/>
     <mergeCell ref="A70:B70"/>
     <mergeCell ref="C64:D64"/>
     <mergeCell ref="I26:J26"/>
+    <mergeCell ref="J18:M18"/>
     <mergeCell ref="E64:F64"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="I70:M70"/>
     <mergeCell ref="B32:H32"/>
     <mergeCell ref="A54:B54"/>
-    <mergeCell ref="D1:L2"/>
     <mergeCell ref="B35:H35"/>
     <mergeCell ref="C63:D63"/>
+    <mergeCell ref="A58:M58"/>
+    <mergeCell ref="I54:M54"/>
+    <mergeCell ref="E63:F63"/>
     <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="I72:M72"/>
+    <mergeCell ref="C16:M16"/>
     <mergeCell ref="G66:H66"/>
+    <mergeCell ref="L5:M5"/>
     <mergeCell ref="I66:J66"/>
     <mergeCell ref="A56:B56"/>
+    <mergeCell ref="L14:M14"/>
     <mergeCell ref="A60:D60"/>
     <mergeCell ref="B20:D20"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="I56:M56"/>
+    <mergeCell ref="K66:M66"/>
     <mergeCell ref="B45:G45"/>
-    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="K34:M34"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="H13:I13"/>
-    <mergeCell ref="D10:L10"/>
+    <mergeCell ref="C17:M17"/>
     <mergeCell ref="B47:G47"/>
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="G20:H20"/>
+    <mergeCell ref="L21:M21"/>
     <mergeCell ref="I20:J20"/>
-    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="A27:M27"/>
     <mergeCell ref="A68:B68"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="C67:M67"/>
+    <mergeCell ref="K45:M45"/>
     <mergeCell ref="H15:I15"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="K37:L37"/>
     <mergeCell ref="E22:F22"/>
-    <mergeCell ref="C12:L12"/>
     <mergeCell ref="B29:H29"/>
     <mergeCell ref="G22:H22"/>
-    <mergeCell ref="D6:I6"/>
     <mergeCell ref="C18:G18"/>
+    <mergeCell ref="K29:M29"/>
     <mergeCell ref="B37:H37"/>
-    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="I60:M60"/>
     <mergeCell ref="I30:J30"/>
-    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="K47:M47"/>
+    <mergeCell ref="L7:M7"/>
     <mergeCell ref="E55:F55"/>
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="D3:M3"/>
+    <mergeCell ref="K31:M31"/>
     <mergeCell ref="G61:H61"/>
     <mergeCell ref="I61:J61"/>
     <mergeCell ref="G70:H70"/>
-    <mergeCell ref="G74:L74"/>
     <mergeCell ref="A61:B61"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="K51:L51"/>
     <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="K41:L41"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="G62:H62"/>
+    <mergeCell ref="A59:M59"/>
+    <mergeCell ref="A11:M11"/>
     <mergeCell ref="B51:G51"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="I70:L70"/>
+    <mergeCell ref="K64:M64"/>
     <mergeCell ref="G24:H24"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="K62:M62"/>
+    <mergeCell ref="A71:B71"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="I57:L57"/>
+    <mergeCell ref="K4:M4"/>
     <mergeCell ref="B41:G41"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="B50:G50"/>
-    <mergeCell ref="I54:L54"/>
-    <mergeCell ref="A58:L58"/>
-    <mergeCell ref="I72:L72"/>
+    <mergeCell ref="K49:M49"/>
     <mergeCell ref="E26:F26"/>
-    <mergeCell ref="C16:L16"/>
     <mergeCell ref="G26:H26"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="K33:M33"/>
     <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I56:L56"/>
-    <mergeCell ref="I71:L71"/>
+    <mergeCell ref="G69:M69"/>
+    <mergeCell ref="L6:M6"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A63:B63"/>
     <mergeCell ref="G25:H25"/>
-    <mergeCell ref="K66:L66"/>
     <mergeCell ref="C66:D66"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="E66:F66"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="D1:M2"/>
     <mergeCell ref="C71:F71"/>
     <mergeCell ref="B34:H34"/>
     <mergeCell ref="B28:H28"/>
-    <mergeCell ref="K25:L25"/>
     <mergeCell ref="B23:D23"/>
-    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="C68:M68"/>
     <mergeCell ref="B30:H30"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="C67:L67"/>
-    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="A53:M53"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A19:M19"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="I60:L60"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="D3:L3"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="K61:M61"/>
+    <mergeCell ref="A39:M39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="K48:M48"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="A55:B55"/>
     <mergeCell ref="B31:H31"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="L26:M26"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="C12:M12"/>
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="I62:J62"/>
+    <mergeCell ref="I55:M55"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="I23:J23"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="C61:D61"/>
     <mergeCell ref="E61:F61"/>
-    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="A65:M65"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="G64:H64"/>
-    <mergeCell ref="A59:L59"/>
     <mergeCell ref="I64:J64"/>
     <mergeCell ref="E57:F57"/>
-    <mergeCell ref="K7:L7"/>
     <mergeCell ref="E54:F54"/>
     <mergeCell ref="B22:D22"/>
+    <mergeCell ref="G74:M74"/>
     <mergeCell ref="G63:H63"/>
+    <mergeCell ref="D7:J7"/>
     <mergeCell ref="I63:J63"/>
     <mergeCell ref="B43:G43"/>
+    <mergeCell ref="K51:M51"/>
     <mergeCell ref="B52:G52"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="E56:F56"/>
     <mergeCell ref="C13:G13"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="K63:M63"/>
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="K41:M41"/>
     <mergeCell ref="I34:J34"/>
-    <mergeCell ref="C70:F70"/>
-    <mergeCell ref="K34:L34"/>
     <mergeCell ref="B42:G42"/>
+    <mergeCell ref="K50:M50"/>
     <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="J14:K14"/>
     <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:L17"/>
+    <mergeCell ref="D8:J8"/>
     <mergeCell ref="I36:J36"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="K43:M43"/>
     <mergeCell ref="B44:G44"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="I57:M57"/>
     <mergeCell ref="B36:H36"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="C68:L68"/>
+    <mergeCell ref="K42:M42"/>
     <mergeCell ref="A66:B66"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="I28:J28"/>
     <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I28:J28"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="A53:L53"/>
+    <mergeCell ref="I71:M71"/>
+    <mergeCell ref="D10:M10"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="K28:M28"/>
+    <mergeCell ref="K37:M37"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="K61:L61"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="A39:L39"/>
-    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="K30:M30"/>
+    <mergeCell ref="E60:H60"/>
     <mergeCell ref="I29:J29"/>
-    <mergeCell ref="E60:H60"/>
     <mergeCell ref="A72:B72"/>
     <mergeCell ref="B46:G46"/>
     <mergeCell ref="I38:J38"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="K38:L38"/>
     <mergeCell ref="H18:I18"/>
+    <mergeCell ref="B38:H38"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="I55:L55"/>
     <mergeCell ref="I31:J31"/>
-    <mergeCell ref="K62:L62"/>
     <mergeCell ref="B48:G48"/>
     <mergeCell ref="A69:F69"/>
     <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A65:L65"/>
+    <mergeCell ref="G72:H72"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.7" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" fitToHeight="0" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 Página &amp;P de &amp;N</oddFooter>

--- a/public/plantilla-permiso-trabajo.xlsx
+++ b/public/plantilla-permiso-trabajo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Permisos de Trabajo" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="39">
+  <numFmts count="0"/>
+  <fonts count="41">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -297,6 +298,15 @@
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -1024,7 +1034,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="385">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -1928,6 +1938,95 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="16" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2441,7 +2540,12 @@
   <cols>
     <col width="12.77734375" customWidth="1" style="127" min="1" max="1"/>
     <col width="13" customWidth="1" style="127" min="2" max="3"/>
+    <col width="13" customWidth="1" style="127" min="3" max="3"/>
     <col width="15.77734375" customWidth="1" style="127" min="4" max="10"/>
+    <col width="13" customWidth="1" style="127" min="5" max="5"/>
+    <col width="13" customWidth="1" style="127" min="6" max="6"/>
+    <col width="13" customWidth="1" style="127" min="7" max="7"/>
+    <col width="13" customWidth="1" style="127" min="8" max="8"/>
     <col width="20.77734375" customWidth="1" style="127" min="11" max="11"/>
     <col width="15.77734375" customWidth="1" style="127" min="12" max="12"/>
     <col width="13" customWidth="1" style="127" min="13" max="13"/>
@@ -2621,17 +2725,17 @@
         </is>
       </c>
       <c r="B12" s="89" t="n"/>
-      <c r="C12" s="211" t="n"/>
-      <c r="D12" s="93" t="n"/>
-      <c r="E12" s="93" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="93" t="n"/>
-      <c r="H12" s="93" t="n"/>
-      <c r="I12" s="93" t="n"/>
-      <c r="J12" s="93" t="n"/>
-      <c r="K12" s="93" t="n"/>
-      <c r="L12" s="93" t="n"/>
-      <c r="M12" s="89" t="n"/>
+      <c r="C12" s="360" t="n"/>
+      <c r="D12" s="361" t="n"/>
+      <c r="E12" s="361" t="n"/>
+      <c r="F12" s="361" t="n"/>
+      <c r="G12" s="361" t="n"/>
+      <c r="H12" s="361" t="n"/>
+      <c r="I12" s="361" t="n"/>
+      <c r="J12" s="361" t="n"/>
+      <c r="K12" s="361" t="n"/>
+      <c r="L12" s="361" t="n"/>
+      <c r="M12" s="362" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="127">
       <c r="A13" s="111" t="inlineStr">
@@ -2640,21 +2744,21 @@
         </is>
       </c>
       <c r="B13" s="89" t="n"/>
-      <c r="C13" s="114" t="n"/>
-      <c r="D13" s="93" t="n"/>
-      <c r="E13" s="93" t="n"/>
-      <c r="F13" s="93" t="n"/>
-      <c r="G13" s="89" t="n"/>
+      <c r="C13" s="363" t="n"/>
+      <c r="D13" s="361" t="n"/>
+      <c r="E13" s="361" t="n"/>
+      <c r="F13" s="361" t="n"/>
+      <c r="G13" s="362" t="n"/>
       <c r="H13" s="111" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="I13" s="89" t="n"/>
-      <c r="J13" s="114" t="n"/>
-      <c r="K13" s="93" t="n"/>
-      <c r="L13" s="93" t="n"/>
-      <c r="M13" s="89" t="n"/>
+      <c r="J13" s="363" t="n"/>
+      <c r="K13" s="361" t="n"/>
+      <c r="L13" s="361" t="n"/>
+      <c r="M13" s="362" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="127">
       <c r="A14" s="111" t="inlineStr">
@@ -2663,33 +2767,33 @@
         </is>
       </c>
       <c r="B14" s="89" t="n"/>
-      <c r="C14" s="115" t="n"/>
+      <c r="C14" s="364" t="n"/>
       <c r="D14" s="111" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="E14" s="115" t="n"/>
+      <c r="E14" s="364" t="n"/>
       <c r="F14" s="111" t="inlineStr">
         <is>
           <t>Hora inicio</t>
         </is>
       </c>
-      <c r="G14" s="115" t="n"/>
+      <c r="G14" s="364" t="n"/>
       <c r="H14" s="111" t="inlineStr">
         <is>
           <t>Hora fin</t>
         </is>
       </c>
-      <c r="I14" s="115" t="n"/>
+      <c r="I14" s="364" t="n"/>
       <c r="J14" s="111" t="inlineStr">
         <is>
           <t>Vigencia</t>
         </is>
       </c>
       <c r="K14" s="89" t="n"/>
-      <c r="L14" s="115" t="n"/>
-      <c r="M14" s="89" t="n"/>
+      <c r="L14" s="364" t="n"/>
+      <c r="M14" s="362" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1" s="127">
       <c r="A15" s="111" t="inlineStr">
@@ -2698,21 +2802,21 @@
         </is>
       </c>
       <c r="B15" s="89" t="n"/>
-      <c r="C15" s="114" t="n"/>
-      <c r="D15" s="93" t="n"/>
-      <c r="E15" s="93" t="n"/>
-      <c r="F15" s="93" t="n"/>
-      <c r="G15" s="89" t="n"/>
+      <c r="C15" s="363" t="n"/>
+      <c r="D15" s="361" t="n"/>
+      <c r="E15" s="361" t="n"/>
+      <c r="F15" s="361" t="n"/>
+      <c r="G15" s="362" t="n"/>
       <c r="H15" s="111" t="inlineStr">
         <is>
           <t>Altura o profundidad (m)</t>
         </is>
       </c>
       <c r="I15" s="89" t="n"/>
-      <c r="J15" s="114" t="n"/>
-      <c r="K15" s="93" t="n"/>
-      <c r="L15" s="93" t="n"/>
-      <c r="M15" s="89" t="n"/>
+      <c r="J15" s="363" t="n"/>
+      <c r="K15" s="361" t="n"/>
+      <c r="L15" s="361" t="n"/>
+      <c r="M15" s="362" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1" s="127">
       <c r="A16" s="111" t="inlineStr">
@@ -2721,17 +2825,17 @@
         </is>
       </c>
       <c r="B16" s="89" t="n"/>
-      <c r="C16" s="114" t="n"/>
-      <c r="D16" s="93" t="n"/>
-      <c r="E16" s="93" t="n"/>
-      <c r="F16" s="93" t="n"/>
-      <c r="G16" s="93" t="n"/>
-      <c r="H16" s="93" t="n"/>
-      <c r="I16" s="93" t="n"/>
-      <c r="J16" s="93" t="n"/>
-      <c r="K16" s="93" t="n"/>
-      <c r="L16" s="93" t="n"/>
-      <c r="M16" s="89" t="n"/>
+      <c r="C16" s="363" t="n"/>
+      <c r="D16" s="361" t="n"/>
+      <c r="E16" s="361" t="n"/>
+      <c r="F16" s="361" t="n"/>
+      <c r="G16" s="361" t="n"/>
+      <c r="H16" s="361" t="n"/>
+      <c r="I16" s="361" t="n"/>
+      <c r="J16" s="361" t="n"/>
+      <c r="K16" s="361" t="n"/>
+      <c r="L16" s="361" t="n"/>
+      <c r="M16" s="362" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1" s="127">
       <c r="A17" s="111" t="inlineStr">
@@ -2740,17 +2844,17 @@
         </is>
       </c>
       <c r="B17" s="89" t="n"/>
-      <c r="C17" s="116" t="n"/>
-      <c r="D17" s="93" t="n"/>
-      <c r="E17" s="93" t="n"/>
-      <c r="F17" s="93" t="n"/>
-      <c r="G17" s="93" t="n"/>
-      <c r="H17" s="93" t="n"/>
-      <c r="I17" s="93" t="n"/>
-      <c r="J17" s="93" t="n"/>
-      <c r="K17" s="93" t="n"/>
-      <c r="L17" s="93" t="n"/>
-      <c r="M17" s="89" t="n"/>
+      <c r="C17" s="365" t="n"/>
+      <c r="D17" s="361" t="n"/>
+      <c r="E17" s="361" t="n"/>
+      <c r="F17" s="361" t="n"/>
+      <c r="G17" s="361" t="n"/>
+      <c r="H17" s="361" t="n"/>
+      <c r="I17" s="361" t="n"/>
+      <c r="J17" s="361" t="n"/>
+      <c r="K17" s="361" t="n"/>
+      <c r="L17" s="361" t="n"/>
+      <c r="M17" s="362" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1" s="127">
       <c r="A18" s="111" t="inlineStr">
@@ -2759,21 +2863,21 @@
         </is>
       </c>
       <c r="B18" s="89" t="n"/>
-      <c r="C18" s="114" t="n"/>
-      <c r="D18" s="93" t="n"/>
-      <c r="E18" s="93" t="n"/>
-      <c r="F18" s="93" t="n"/>
-      <c r="G18" s="89" t="n"/>
+      <c r="C18" s="363" t="n"/>
+      <c r="D18" s="361" t="n"/>
+      <c r="E18" s="361" t="n"/>
+      <c r="F18" s="361" t="n"/>
+      <c r="G18" s="362" t="n"/>
       <c r="H18" s="111" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
       <c r="I18" s="89" t="n"/>
-      <c r="J18" s="114" t="n"/>
-      <c r="K18" s="93" t="n"/>
-      <c r="L18" s="93" t="n"/>
-      <c r="M18" s="89" t="n"/>
+      <c r="J18" s="363" t="n"/>
+      <c r="K18" s="361" t="n"/>
+      <c r="L18" s="361" t="n"/>
+      <c r="M18" s="362" t="n"/>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="127">
       <c r="A19" s="268" t="inlineStr">
@@ -2827,106 +2931,106 @@
       <c r="M20" s="348" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1" s="127">
-      <c r="A21" s="269" t="n">
+      <c r="A21" s="366" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="270" t="n"/>
-      <c r="C21" s="98" t="n"/>
-      <c r="D21" s="97" t="n"/>
-      <c r="E21" s="270" t="n"/>
-      <c r="F21" s="97" t="n"/>
-      <c r="G21" s="270" t="n"/>
-      <c r="H21" s="97" t="n"/>
-      <c r="I21" s="270" t="n"/>
-      <c r="J21" s="97" t="n"/>
-      <c r="K21" s="271" t="n"/>
-      <c r="L21" s="270" t="n"/>
-      <c r="M21" s="97" t="n"/>
+      <c r="B21" s="367" t="n"/>
+      <c r="C21" s="368" t="n"/>
+      <c r="D21" s="369" t="n"/>
+      <c r="E21" s="367" t="n"/>
+      <c r="F21" s="369" t="n"/>
+      <c r="G21" s="367" t="n"/>
+      <c r="H21" s="369" t="n"/>
+      <c r="I21" s="367" t="n"/>
+      <c r="J21" s="369" t="n"/>
+      <c r="K21" s="370" t="n"/>
+      <c r="L21" s="367" t="n"/>
+      <c r="M21" s="369" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1" s="127">
-      <c r="A22" s="110" t="n">
+      <c r="A22" s="371" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="117" t="n"/>
-      <c r="C22" s="93" t="n"/>
-      <c r="D22" s="89" t="n"/>
-      <c r="E22" s="117" t="n"/>
-      <c r="F22" s="89" t="n"/>
-      <c r="G22" s="117" t="n"/>
-      <c r="H22" s="89" t="n"/>
-      <c r="I22" s="117" t="n"/>
-      <c r="J22" s="89" t="n"/>
-      <c r="K22" s="37" t="n"/>
-      <c r="L22" s="117" t="n"/>
-      <c r="M22" s="89" t="n"/>
+      <c r="B22" s="372" t="n"/>
+      <c r="C22" s="361" t="n"/>
+      <c r="D22" s="362" t="n"/>
+      <c r="E22" s="372" t="n"/>
+      <c r="F22" s="362" t="n"/>
+      <c r="G22" s="372" t="n"/>
+      <c r="H22" s="362" t="n"/>
+      <c r="I22" s="372" t="n"/>
+      <c r="J22" s="362" t="n"/>
+      <c r="K22" s="373" t="n"/>
+      <c r="L22" s="372" t="n"/>
+      <c r="M22" s="362" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1" s="127">
-      <c r="A23" s="110" t="n">
+      <c r="A23" s="371" t="n">
         <v>3</v>
       </c>
-      <c r="B23" s="117" t="n"/>
-      <c r="C23" s="93" t="n"/>
-      <c r="D23" s="89" t="n"/>
-      <c r="E23" s="117" t="n"/>
-      <c r="F23" s="89" t="n"/>
-      <c r="G23" s="117" t="n"/>
-      <c r="H23" s="89" t="n"/>
-      <c r="I23" s="117" t="n"/>
-      <c r="J23" s="89" t="n"/>
-      <c r="K23" s="37" t="n"/>
-      <c r="L23" s="117" t="n"/>
-      <c r="M23" s="89" t="n"/>
+      <c r="B23" s="372" t="n"/>
+      <c r="C23" s="361" t="n"/>
+      <c r="D23" s="362" t="n"/>
+      <c r="E23" s="372" t="n"/>
+      <c r="F23" s="362" t="n"/>
+      <c r="G23" s="372" t="n"/>
+      <c r="H23" s="362" t="n"/>
+      <c r="I23" s="372" t="n"/>
+      <c r="J23" s="362" t="n"/>
+      <c r="K23" s="373" t="n"/>
+      <c r="L23" s="372" t="n"/>
+      <c r="M23" s="362" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1" s="127">
-      <c r="A24" s="110" t="n">
+      <c r="A24" s="371" t="n">
         <v>4</v>
       </c>
-      <c r="B24" s="117" t="n"/>
-      <c r="C24" s="93" t="n"/>
-      <c r="D24" s="89" t="n"/>
-      <c r="E24" s="117" t="n"/>
-      <c r="F24" s="89" t="n"/>
-      <c r="G24" s="117" t="n"/>
-      <c r="H24" s="89" t="n"/>
-      <c r="I24" s="117" t="n"/>
-      <c r="J24" s="89" t="n"/>
-      <c r="K24" s="37" t="n"/>
-      <c r="L24" s="117" t="n"/>
-      <c r="M24" s="89" t="n"/>
+      <c r="B24" s="372" t="n"/>
+      <c r="C24" s="361" t="n"/>
+      <c r="D24" s="362" t="n"/>
+      <c r="E24" s="372" t="n"/>
+      <c r="F24" s="362" t="n"/>
+      <c r="G24" s="372" t="n"/>
+      <c r="H24" s="362" t="n"/>
+      <c r="I24" s="372" t="n"/>
+      <c r="J24" s="362" t="n"/>
+      <c r="K24" s="373" t="n"/>
+      <c r="L24" s="372" t="n"/>
+      <c r="M24" s="362" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1" s="127">
-      <c r="A25" s="110" t="n">
+      <c r="A25" s="371" t="n">
         <v>5</v>
       </c>
-      <c r="B25" s="117" t="n"/>
-      <c r="C25" s="93" t="n"/>
-      <c r="D25" s="89" t="n"/>
-      <c r="E25" s="117" t="n"/>
-      <c r="F25" s="89" t="n"/>
-      <c r="G25" s="117" t="n"/>
-      <c r="H25" s="89" t="n"/>
-      <c r="I25" s="117" t="n"/>
-      <c r="J25" s="89" t="n"/>
-      <c r="K25" s="37" t="n"/>
-      <c r="L25" s="117" t="n"/>
-      <c r="M25" s="89" t="n"/>
+      <c r="B25" s="372" t="n"/>
+      <c r="C25" s="361" t="n"/>
+      <c r="D25" s="362" t="n"/>
+      <c r="E25" s="372" t="n"/>
+      <c r="F25" s="362" t="n"/>
+      <c r="G25" s="372" t="n"/>
+      <c r="H25" s="362" t="n"/>
+      <c r="I25" s="372" t="n"/>
+      <c r="J25" s="362" t="n"/>
+      <c r="K25" s="373" t="n"/>
+      <c r="L25" s="372" t="n"/>
+      <c r="M25" s="362" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1" s="127">
-      <c r="A26" s="110" t="n">
+      <c r="A26" s="371" t="n">
         <v>6</v>
       </c>
-      <c r="B26" s="117" t="n"/>
-      <c r="C26" s="93" t="n"/>
-      <c r="D26" s="89" t="n"/>
-      <c r="E26" s="117" t="n"/>
-      <c r="F26" s="89" t="n"/>
-      <c r="G26" s="117" t="n"/>
-      <c r="H26" s="89" t="n"/>
-      <c r="I26" s="117" t="n"/>
-      <c r="J26" s="89" t="n"/>
-      <c r="K26" s="37" t="n"/>
-      <c r="L26" s="117" t="n"/>
-      <c r="M26" s="89" t="n"/>
+      <c r="B26" s="372" t="n"/>
+      <c r="C26" s="361" t="n"/>
+      <c r="D26" s="362" t="n"/>
+      <c r="E26" s="372" t="n"/>
+      <c r="F26" s="362" t="n"/>
+      <c r="G26" s="372" t="n"/>
+      <c r="H26" s="362" t="n"/>
+      <c r="I26" s="372" t="n"/>
+      <c r="J26" s="362" t="n"/>
+      <c r="K26" s="373" t="n"/>
+      <c r="L26" s="372" t="n"/>
+      <c r="M26" s="362" t="n"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" s="127">
       <c r="A27" s="268" t="inlineStr">
@@ -2968,10 +3072,10 @@
       <c r="M28" s="348" t="n"/>
     </row>
     <row r="29" ht="16.95" customHeight="1" s="127">
-      <c r="A29" s="277" t="n">
+      <c r="A29" s="366" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="276" t="inlineStr">
+      <c r="B29" s="374" t="inlineStr">
         <is>
           <t>ATS elaborado, socializado y firmado por todo el personal que ejecuta</t>
         </is>
@@ -2982,17 +3086,17 @@
       <c r="F29" s="98" t="n"/>
       <c r="G29" s="98" t="n"/>
       <c r="H29" s="97" t="n"/>
-      <c r="I29" s="277" t="n"/>
-      <c r="J29" s="97" t="n"/>
+      <c r="I29" s="375" t="n"/>
+      <c r="J29" s="369" t="n"/>
       <c r="K29" s="132" t="n"/>
       <c r="L29" s="98" t="n"/>
       <c r="M29" s="97" t="n"/>
     </row>
     <row r="30" ht="16.95" customHeight="1" s="127">
-      <c r="A30" s="119" t="n">
+      <c r="A30" s="371" t="n">
         <v>2</v>
       </c>
-      <c r="B30" s="118" t="inlineStr">
+      <c r="B30" s="376" t="inlineStr">
         <is>
           <t>Personal con aptitud médica y capacitación o certificación vigente para este trabajo</t>
         </is>
@@ -3003,17 +3107,17 @@
       <c r="F30" s="93" t="n"/>
       <c r="G30" s="93" t="n"/>
       <c r="H30" s="89" t="n"/>
-      <c r="I30" s="119" t="n"/>
-      <c r="J30" s="89" t="n"/>
+      <c r="I30" s="377" t="n"/>
+      <c r="J30" s="362" t="n"/>
       <c r="K30" s="120" t="n"/>
       <c r="L30" s="93" t="n"/>
       <c r="M30" s="89" t="n"/>
     </row>
     <row r="31" ht="16.95" customHeight="1" s="127">
-      <c r="A31" s="119" t="n">
+      <c r="A31" s="371" t="n">
         <v>3</v>
       </c>
-      <c r="B31" s="118" t="inlineStr">
+      <c r="B31" s="376" t="inlineStr">
         <is>
           <t>Elementos de protección personal completos, certificados y en buen estado</t>
         </is>
@@ -3024,17 +3128,17 @@
       <c r="F31" s="93" t="n"/>
       <c r="G31" s="93" t="n"/>
       <c r="H31" s="89" t="n"/>
-      <c r="I31" s="119" t="n"/>
-      <c r="J31" s="89" t="n"/>
+      <c r="I31" s="377" t="n"/>
+      <c r="J31" s="362" t="n"/>
       <c r="K31" s="120" t="n"/>
       <c r="L31" s="93" t="n"/>
       <c r="M31" s="89" t="n"/>
     </row>
     <row r="32" ht="16.95" customHeight="1" s="127">
-      <c r="A32" s="119" t="n">
+      <c r="A32" s="371" t="n">
         <v>4</v>
       </c>
-      <c r="B32" s="118" t="inlineStr">
+      <c r="B32" s="376" t="inlineStr">
         <is>
           <t>Área demarcada, señalizada y con acceso restringido a personas ajenas</t>
         </is>
@@ -3045,17 +3149,17 @@
       <c r="F32" s="93" t="n"/>
       <c r="G32" s="93" t="n"/>
       <c r="H32" s="89" t="n"/>
-      <c r="I32" s="119" t="n"/>
-      <c r="J32" s="89" t="n"/>
+      <c r="I32" s="377" t="n"/>
+      <c r="J32" s="362" t="n"/>
       <c r="K32" s="120" t="n"/>
       <c r="L32" s="93" t="n"/>
       <c r="M32" s="89" t="n"/>
     </row>
     <row r="33" ht="16.95" customHeight="1" s="127">
-      <c r="A33" s="119" t="n">
+      <c r="A33" s="371" t="n">
         <v>5</v>
       </c>
-      <c r="B33" s="118" t="inlineStr">
+      <c r="B33" s="376" t="inlineStr">
         <is>
           <t>Herramientas, equipos y sistemas de protección inspeccionados</t>
         </is>
@@ -3066,17 +3170,17 @@
       <c r="F33" s="93" t="n"/>
       <c r="G33" s="93" t="n"/>
       <c r="H33" s="89" t="n"/>
-      <c r="I33" s="119" t="n"/>
-      <c r="J33" s="89" t="n"/>
+      <c r="I33" s="377" t="n"/>
+      <c r="J33" s="362" t="n"/>
       <c r="K33" s="120" t="n"/>
       <c r="L33" s="93" t="n"/>
       <c r="M33" s="89" t="n"/>
     </row>
     <row r="34" ht="16.95" customHeight="1" s="127">
-      <c r="A34" s="119" t="n">
+      <c r="A34" s="371" t="n">
         <v>6</v>
       </c>
-      <c r="B34" s="118" t="inlineStr">
+      <c r="B34" s="376" t="inlineStr">
         <is>
           <t>Plan de emergencia y de rescate conocido; medio de comunicación disponible</t>
         </is>
@@ -3087,17 +3191,17 @@
       <c r="F34" s="93" t="n"/>
       <c r="G34" s="93" t="n"/>
       <c r="H34" s="89" t="n"/>
-      <c r="I34" s="119" t="n"/>
-      <c r="J34" s="89" t="n"/>
+      <c r="I34" s="377" t="n"/>
+      <c r="J34" s="362" t="n"/>
       <c r="K34" s="120" t="n"/>
       <c r="L34" s="93" t="n"/>
       <c r="M34" s="89" t="n"/>
     </row>
     <row r="35" ht="16.95" customHeight="1" s="127">
-      <c r="A35" s="119" t="n">
+      <c r="A35" s="371" t="n">
         <v>7</v>
       </c>
-      <c r="B35" s="118" t="inlineStr">
+      <c r="B35" s="376" t="inlineStr">
         <is>
           <t>Extintor y botiquín disponibles en el sitio del trabajo</t>
         </is>
@@ -3108,17 +3212,17 @@
       <c r="F35" s="93" t="n"/>
       <c r="G35" s="93" t="n"/>
       <c r="H35" s="89" t="n"/>
-      <c r="I35" s="119" t="n"/>
-      <c r="J35" s="89" t="n"/>
+      <c r="I35" s="377" t="n"/>
+      <c r="J35" s="362" t="n"/>
       <c r="K35" s="120" t="n"/>
       <c r="L35" s="93" t="n"/>
       <c r="M35" s="89" t="n"/>
     </row>
     <row r="36" ht="16.95" customHeight="1" s="127">
-      <c r="A36" s="119" t="n">
+      <c r="A36" s="371" t="n">
         <v>8</v>
       </c>
-      <c r="B36" s="118" t="inlineStr">
+      <c r="B36" s="376" t="inlineStr">
         <is>
           <t>Condiciones del entorno evaluadas (lluvia, viento, tormenta eléctrica)</t>
         </is>
@@ -3129,17 +3233,17 @@
       <c r="F36" s="93" t="n"/>
       <c r="G36" s="93" t="n"/>
       <c r="H36" s="89" t="n"/>
-      <c r="I36" s="119" t="n"/>
-      <c r="J36" s="89" t="n"/>
+      <c r="I36" s="377" t="n"/>
+      <c r="J36" s="362" t="n"/>
       <c r="K36" s="120" t="n"/>
       <c r="L36" s="93" t="n"/>
       <c r="M36" s="89" t="n"/>
     </row>
     <row r="37" ht="16.95" customHeight="1" s="127">
-      <c r="A37" s="119" t="n">
+      <c r="A37" s="371" t="n">
         <v>9</v>
       </c>
-      <c r="B37" s="118" t="inlineStr">
+      <c r="B37" s="376" t="inlineStr">
         <is>
           <t>Permisos complementarios tramitados y adjuntos (si aplica)</t>
         </is>
@@ -3150,17 +3254,17 @@
       <c r="F37" s="93" t="n"/>
       <c r="G37" s="93" t="n"/>
       <c r="H37" s="89" t="n"/>
-      <c r="I37" s="119" t="n"/>
-      <c r="J37" s="89" t="n"/>
+      <c r="I37" s="377" t="n"/>
+      <c r="J37" s="362" t="n"/>
       <c r="K37" s="120" t="n"/>
       <c r="L37" s="93" t="n"/>
       <c r="M37" s="89" t="n"/>
     </row>
     <row r="38" ht="16.95" customHeight="1" s="127">
-      <c r="A38" s="119" t="n">
+      <c r="A38" s="371" t="n">
         <v>10</v>
       </c>
-      <c r="B38" s="118" t="inlineStr">
+      <c r="B38" s="376" t="inlineStr">
         <is>
           <t>Coordinación con otras actividades simultáneas en el área</t>
         </is>
@@ -3171,8 +3275,8 @@
       <c r="F38" s="93" t="n"/>
       <c r="G38" s="93" t="n"/>
       <c r="H38" s="89" t="n"/>
-      <c r="I38" s="119" t="n"/>
-      <c r="J38" s="89" t="n"/>
+      <c r="I38" s="377" t="n"/>
+      <c r="J38" s="362" t="n"/>
       <c r="K38" s="120" t="n"/>
       <c r="L38" s="93" t="n"/>
       <c r="M38" s="89" t="n"/>
@@ -3225,208 +3329,208 @@
       <c r="M40" s="348" t="n"/>
     </row>
     <row r="41" ht="24" customHeight="1" s="127">
-      <c r="A41" s="277" t="n">
+      <c r="A41" s="366" t="n">
         <v>1</v>
       </c>
-      <c r="B41" s="276" t="n"/>
-      <c r="C41" s="98" t="n"/>
-      <c r="D41" s="98" t="n"/>
-      <c r="E41" s="98" t="n"/>
-      <c r="F41" s="98" t="n"/>
-      <c r="G41" s="97" t="n"/>
-      <c r="H41" s="277" t="n"/>
-      <c r="I41" s="277" t="n"/>
-      <c r="J41" s="277" t="n"/>
-      <c r="K41" s="277" t="n"/>
-      <c r="L41" s="98" t="n"/>
-      <c r="M41" s="97" t="n"/>
+      <c r="B41" s="378" t="n"/>
+      <c r="C41" s="368" t="n"/>
+      <c r="D41" s="368" t="n"/>
+      <c r="E41" s="368" t="n"/>
+      <c r="F41" s="368" t="n"/>
+      <c r="G41" s="369" t="n"/>
+      <c r="H41" s="375" t="n"/>
+      <c r="I41" s="375" t="n"/>
+      <c r="J41" s="375" t="n"/>
+      <c r="K41" s="375" t="n"/>
+      <c r="L41" s="368" t="n"/>
+      <c r="M41" s="369" t="n"/>
     </row>
     <row r="42" ht="24" customHeight="1" s="127">
-      <c r="A42" s="119" t="n">
+      <c r="A42" s="371" t="n">
         <v>2</v>
       </c>
-      <c r="B42" s="118" t="n"/>
-      <c r="C42" s="93" t="n"/>
-      <c r="D42" s="93" t="n"/>
-      <c r="E42" s="93" t="n"/>
-      <c r="F42" s="93" t="n"/>
-      <c r="G42" s="89" t="n"/>
-      <c r="H42" s="119" t="n"/>
-      <c r="I42" s="119" t="n"/>
-      <c r="J42" s="119" t="n"/>
-      <c r="K42" s="119" t="n"/>
-      <c r="L42" s="93" t="n"/>
-      <c r="M42" s="89" t="n"/>
+      <c r="B42" s="363" t="n"/>
+      <c r="C42" s="361" t="n"/>
+      <c r="D42" s="361" t="n"/>
+      <c r="E42" s="361" t="n"/>
+      <c r="F42" s="361" t="n"/>
+      <c r="G42" s="362" t="n"/>
+      <c r="H42" s="377" t="n"/>
+      <c r="I42" s="377" t="n"/>
+      <c r="J42" s="377" t="n"/>
+      <c r="K42" s="377" t="n"/>
+      <c r="L42" s="361" t="n"/>
+      <c r="M42" s="362" t="n"/>
     </row>
     <row r="43" ht="24" customHeight="1" s="127">
-      <c r="A43" s="119" t="n">
+      <c r="A43" s="371" t="n">
         <v>3</v>
       </c>
-      <c r="B43" s="118" t="n"/>
-      <c r="C43" s="93" t="n"/>
-      <c r="D43" s="93" t="n"/>
-      <c r="E43" s="93" t="n"/>
-      <c r="F43" s="93" t="n"/>
-      <c r="G43" s="89" t="n"/>
-      <c r="H43" s="119" t="n"/>
-      <c r="I43" s="119" t="n"/>
-      <c r="J43" s="119" t="n"/>
-      <c r="K43" s="119" t="n"/>
-      <c r="L43" s="93" t="n"/>
-      <c r="M43" s="89" t="n"/>
+      <c r="B43" s="363" t="n"/>
+      <c r="C43" s="361" t="n"/>
+      <c r="D43" s="361" t="n"/>
+      <c r="E43" s="361" t="n"/>
+      <c r="F43" s="361" t="n"/>
+      <c r="G43" s="362" t="n"/>
+      <c r="H43" s="377" t="n"/>
+      <c r="I43" s="377" t="n"/>
+      <c r="J43" s="377" t="n"/>
+      <c r="K43" s="377" t="n"/>
+      <c r="L43" s="361" t="n"/>
+      <c r="M43" s="362" t="n"/>
     </row>
     <row r="44" ht="24" customHeight="1" s="127">
-      <c r="A44" s="119" t="n">
+      <c r="A44" s="371" t="n">
         <v>4</v>
       </c>
-      <c r="B44" s="118" t="n"/>
-      <c r="C44" s="93" t="n"/>
-      <c r="D44" s="93" t="n"/>
-      <c r="E44" s="93" t="n"/>
-      <c r="F44" s="93" t="n"/>
-      <c r="G44" s="89" t="n"/>
-      <c r="H44" s="119" t="n"/>
-      <c r="I44" s="119" t="n"/>
-      <c r="J44" s="119" t="n"/>
-      <c r="K44" s="119" t="n"/>
-      <c r="L44" s="93" t="n"/>
-      <c r="M44" s="89" t="n"/>
+      <c r="B44" s="363" t="n"/>
+      <c r="C44" s="361" t="n"/>
+      <c r="D44" s="361" t="n"/>
+      <c r="E44" s="361" t="n"/>
+      <c r="F44" s="361" t="n"/>
+      <c r="G44" s="362" t="n"/>
+      <c r="H44" s="377" t="n"/>
+      <c r="I44" s="377" t="n"/>
+      <c r="J44" s="377" t="n"/>
+      <c r="K44" s="377" t="n"/>
+      <c r="L44" s="361" t="n"/>
+      <c r="M44" s="362" t="n"/>
     </row>
     <row r="45" ht="24" customHeight="1" s="127">
-      <c r="A45" s="119" t="n">
+      <c r="A45" s="371" t="n">
         <v>5</v>
       </c>
-      <c r="B45" s="118" t="n"/>
-      <c r="C45" s="93" t="n"/>
-      <c r="D45" s="93" t="n"/>
-      <c r="E45" s="93" t="n"/>
-      <c r="F45" s="93" t="n"/>
-      <c r="G45" s="89" t="n"/>
-      <c r="H45" s="119" t="n"/>
-      <c r="I45" s="119" t="n"/>
-      <c r="J45" s="119" t="n"/>
-      <c r="K45" s="119" t="n"/>
-      <c r="L45" s="93" t="n"/>
-      <c r="M45" s="89" t="n"/>
+      <c r="B45" s="363" t="n"/>
+      <c r="C45" s="361" t="n"/>
+      <c r="D45" s="361" t="n"/>
+      <c r="E45" s="361" t="n"/>
+      <c r="F45" s="361" t="n"/>
+      <c r="G45" s="362" t="n"/>
+      <c r="H45" s="377" t="n"/>
+      <c r="I45" s="377" t="n"/>
+      <c r="J45" s="377" t="n"/>
+      <c r="K45" s="377" t="n"/>
+      <c r="L45" s="361" t="n"/>
+      <c r="M45" s="362" t="n"/>
     </row>
     <row r="46" ht="24" customHeight="1" s="127">
-      <c r="A46" s="119" t="n">
+      <c r="A46" s="371" t="n">
         <v>6</v>
       </c>
-      <c r="B46" s="118" t="n"/>
-      <c r="C46" s="93" t="n"/>
-      <c r="D46" s="93" t="n"/>
-      <c r="E46" s="93" t="n"/>
-      <c r="F46" s="93" t="n"/>
-      <c r="G46" s="89" t="n"/>
-      <c r="H46" s="119" t="n"/>
-      <c r="I46" s="119" t="n"/>
-      <c r="J46" s="119" t="n"/>
-      <c r="K46" s="119" t="n"/>
-      <c r="L46" s="93" t="n"/>
-      <c r="M46" s="89" t="n"/>
+      <c r="B46" s="363" t="n"/>
+      <c r="C46" s="361" t="n"/>
+      <c r="D46" s="361" t="n"/>
+      <c r="E46" s="361" t="n"/>
+      <c r="F46" s="361" t="n"/>
+      <c r="G46" s="362" t="n"/>
+      <c r="H46" s="377" t="n"/>
+      <c r="I46" s="377" t="n"/>
+      <c r="J46" s="377" t="n"/>
+      <c r="K46" s="377" t="n"/>
+      <c r="L46" s="361" t="n"/>
+      <c r="M46" s="362" t="n"/>
     </row>
     <row r="47" ht="24" customHeight="1" s="127">
-      <c r="A47" s="119" t="n">
+      <c r="A47" s="371" t="n">
         <v>7</v>
       </c>
-      <c r="B47" s="118" t="n"/>
-      <c r="C47" s="93" t="n"/>
-      <c r="D47" s="93" t="n"/>
-      <c r="E47" s="93" t="n"/>
-      <c r="F47" s="93" t="n"/>
-      <c r="G47" s="89" t="n"/>
-      <c r="H47" s="119" t="n"/>
-      <c r="I47" s="119" t="n"/>
-      <c r="J47" s="119" t="n"/>
-      <c r="K47" s="119" t="n"/>
-      <c r="L47" s="93" t="n"/>
-      <c r="M47" s="89" t="n"/>
+      <c r="B47" s="363" t="n"/>
+      <c r="C47" s="361" t="n"/>
+      <c r="D47" s="361" t="n"/>
+      <c r="E47" s="361" t="n"/>
+      <c r="F47" s="361" t="n"/>
+      <c r="G47" s="362" t="n"/>
+      <c r="H47" s="377" t="n"/>
+      <c r="I47" s="377" t="n"/>
+      <c r="J47" s="377" t="n"/>
+      <c r="K47" s="377" t="n"/>
+      <c r="L47" s="361" t="n"/>
+      <c r="M47" s="362" t="n"/>
     </row>
     <row r="48" ht="24" customHeight="1" s="127">
-      <c r="A48" s="119" t="n">
+      <c r="A48" s="371" t="n">
         <v>8</v>
       </c>
-      <c r="B48" s="118" t="n"/>
-      <c r="C48" s="93" t="n"/>
-      <c r="D48" s="93" t="n"/>
-      <c r="E48" s="93" t="n"/>
-      <c r="F48" s="93" t="n"/>
-      <c r="G48" s="89" t="n"/>
-      <c r="H48" s="119" t="n"/>
-      <c r="I48" s="119" t="n"/>
-      <c r="J48" s="119" t="n"/>
-      <c r="K48" s="119" t="n"/>
-      <c r="L48" s="93" t="n"/>
-      <c r="M48" s="89" t="n"/>
+      <c r="B48" s="363" t="n"/>
+      <c r="C48" s="361" t="n"/>
+      <c r="D48" s="361" t="n"/>
+      <c r="E48" s="361" t="n"/>
+      <c r="F48" s="361" t="n"/>
+      <c r="G48" s="362" t="n"/>
+      <c r="H48" s="377" t="n"/>
+      <c r="I48" s="377" t="n"/>
+      <c r="J48" s="377" t="n"/>
+      <c r="K48" s="377" t="n"/>
+      <c r="L48" s="361" t="n"/>
+      <c r="M48" s="362" t="n"/>
     </row>
     <row r="49" ht="24" customHeight="1" s="127">
-      <c r="A49" s="119" t="n">
+      <c r="A49" s="371" t="n">
         <v>9</v>
       </c>
-      <c r="B49" s="118" t="n"/>
-      <c r="C49" s="93" t="n"/>
-      <c r="D49" s="93" t="n"/>
-      <c r="E49" s="93" t="n"/>
-      <c r="F49" s="93" t="n"/>
-      <c r="G49" s="89" t="n"/>
-      <c r="H49" s="119" t="n"/>
-      <c r="I49" s="119" t="n"/>
-      <c r="J49" s="119" t="n"/>
-      <c r="K49" s="119" t="n"/>
-      <c r="L49" s="93" t="n"/>
-      <c r="M49" s="89" t="n"/>
+      <c r="B49" s="363" t="n"/>
+      <c r="C49" s="361" t="n"/>
+      <c r="D49" s="361" t="n"/>
+      <c r="E49" s="361" t="n"/>
+      <c r="F49" s="361" t="n"/>
+      <c r="G49" s="362" t="n"/>
+      <c r="H49" s="377" t="n"/>
+      <c r="I49" s="377" t="n"/>
+      <c r="J49" s="377" t="n"/>
+      <c r="K49" s="377" t="n"/>
+      <c r="L49" s="361" t="n"/>
+      <c r="M49" s="362" t="n"/>
     </row>
     <row r="50" ht="24" customHeight="1" s="127">
-      <c r="A50" s="119" t="n">
+      <c r="A50" s="371" t="n">
         <v>10</v>
       </c>
-      <c r="B50" s="118" t="n"/>
-      <c r="C50" s="93" t="n"/>
-      <c r="D50" s="93" t="n"/>
-      <c r="E50" s="93" t="n"/>
-      <c r="F50" s="93" t="n"/>
-      <c r="G50" s="89" t="n"/>
-      <c r="H50" s="119" t="n"/>
-      <c r="I50" s="119" t="n"/>
-      <c r="J50" s="119" t="n"/>
-      <c r="K50" s="119" t="n"/>
-      <c r="L50" s="93" t="n"/>
-      <c r="M50" s="89" t="n"/>
+      <c r="B50" s="363" t="n"/>
+      <c r="C50" s="361" t="n"/>
+      <c r="D50" s="361" t="n"/>
+      <c r="E50" s="361" t="n"/>
+      <c r="F50" s="361" t="n"/>
+      <c r="G50" s="362" t="n"/>
+      <c r="H50" s="377" t="n"/>
+      <c r="I50" s="377" t="n"/>
+      <c r="J50" s="377" t="n"/>
+      <c r="K50" s="377" t="n"/>
+      <c r="L50" s="361" t="n"/>
+      <c r="M50" s="362" t="n"/>
     </row>
     <row r="51" ht="24" customHeight="1" s="127">
-      <c r="A51" s="119" t="n">
+      <c r="A51" s="371" t="n">
         <v>11</v>
       </c>
-      <c r="B51" s="118" t="n"/>
-      <c r="C51" s="93" t="n"/>
-      <c r="D51" s="93" t="n"/>
-      <c r="E51" s="93" t="n"/>
-      <c r="F51" s="93" t="n"/>
-      <c r="G51" s="89" t="n"/>
-      <c r="H51" s="119" t="n"/>
-      <c r="I51" s="119" t="n"/>
-      <c r="J51" s="119" t="n"/>
-      <c r="K51" s="119" t="n"/>
-      <c r="L51" s="93" t="n"/>
-      <c r="M51" s="89" t="n"/>
+      <c r="B51" s="363" t="n"/>
+      <c r="C51" s="361" t="n"/>
+      <c r="D51" s="361" t="n"/>
+      <c r="E51" s="361" t="n"/>
+      <c r="F51" s="361" t="n"/>
+      <c r="G51" s="362" t="n"/>
+      <c r="H51" s="377" t="n"/>
+      <c r="I51" s="377" t="n"/>
+      <c r="J51" s="377" t="n"/>
+      <c r="K51" s="377" t="n"/>
+      <c r="L51" s="361" t="n"/>
+      <c r="M51" s="362" t="n"/>
     </row>
     <row r="52" ht="24" customHeight="1" s="127">
-      <c r="A52" s="119" t="n">
+      <c r="A52" s="371" t="n">
         <v>12</v>
       </c>
-      <c r="B52" s="118" t="n"/>
-      <c r="C52" s="93" t="n"/>
-      <c r="D52" s="93" t="n"/>
-      <c r="E52" s="93" t="n"/>
-      <c r="F52" s="93" t="n"/>
-      <c r="G52" s="89" t="n"/>
-      <c r="H52" s="119" t="n"/>
-      <c r="I52" s="119" t="n"/>
-      <c r="J52" s="119" t="n"/>
-      <c r="K52" s="119" t="n"/>
-      <c r="L52" s="93" t="n"/>
-      <c r="M52" s="89" t="n"/>
+      <c r="B52" s="363" t="n"/>
+      <c r="C52" s="361" t="n"/>
+      <c r="D52" s="361" t="n"/>
+      <c r="E52" s="361" t="n"/>
+      <c r="F52" s="361" t="n"/>
+      <c r="G52" s="362" t="n"/>
+      <c r="H52" s="377" t="n"/>
+      <c r="I52" s="377" t="n"/>
+      <c r="J52" s="377" t="n"/>
+      <c r="K52" s="377" t="n"/>
+      <c r="L52" s="361" t="n"/>
+      <c r="M52" s="362" t="n"/>
     </row>
     <row r="53" ht="16.5" customHeight="1" s="127">
       <c r="A53" s="268" t="inlineStr">
@@ -3480,61 +3584,61 @@
       <c r="M54" s="348" t="n"/>
     </row>
     <row r="55" ht="19.05" customHeight="1" s="127">
-      <c r="A55" s="278" t="inlineStr">
+      <c r="A55" s="374" t="inlineStr">
         <is>
           <t>Inicial</t>
         </is>
       </c>
       <c r="B55" s="97" t="n"/>
-      <c r="C55" s="277" t="n"/>
-      <c r="D55" s="277" t="n"/>
-      <c r="E55" s="277" t="n"/>
-      <c r="F55" s="97" t="n"/>
-      <c r="G55" s="277" t="n"/>
-      <c r="H55" s="277" t="n"/>
-      <c r="I55" s="278" t="n"/>
-      <c r="J55" s="98" t="n"/>
-      <c r="K55" s="98" t="n"/>
-      <c r="L55" s="98" t="n"/>
-      <c r="M55" s="97" t="n"/>
+      <c r="C55" s="375" t="n"/>
+      <c r="D55" s="375" t="n"/>
+      <c r="E55" s="375" t="n"/>
+      <c r="F55" s="369" t="n"/>
+      <c r="G55" s="375" t="n"/>
+      <c r="H55" s="375" t="n"/>
+      <c r="I55" s="378" t="n"/>
+      <c r="J55" s="368" t="n"/>
+      <c r="K55" s="368" t="n"/>
+      <c r="L55" s="368" t="n"/>
+      <c r="M55" s="369" t="n"/>
     </row>
     <row r="56" ht="19.05" customHeight="1" s="127">
-      <c r="A56" s="121" t="inlineStr">
+      <c r="A56" s="376" t="inlineStr">
         <is>
           <t>Intermedia</t>
         </is>
       </c>
       <c r="B56" s="89" t="n"/>
-      <c r="C56" s="119" t="n"/>
-      <c r="D56" s="119" t="n"/>
-      <c r="E56" s="119" t="n"/>
-      <c r="F56" s="89" t="n"/>
-      <c r="G56" s="119" t="n"/>
-      <c r="H56" s="119" t="n"/>
-      <c r="I56" s="121" t="n"/>
-      <c r="J56" s="93" t="n"/>
-      <c r="K56" s="93" t="n"/>
-      <c r="L56" s="93" t="n"/>
-      <c r="M56" s="89" t="n"/>
+      <c r="C56" s="377" t="n"/>
+      <c r="D56" s="377" t="n"/>
+      <c r="E56" s="377" t="n"/>
+      <c r="F56" s="362" t="n"/>
+      <c r="G56" s="377" t="n"/>
+      <c r="H56" s="377" t="n"/>
+      <c r="I56" s="363" t="n"/>
+      <c r="J56" s="361" t="n"/>
+      <c r="K56" s="361" t="n"/>
+      <c r="L56" s="361" t="n"/>
+      <c r="M56" s="362" t="n"/>
     </row>
     <row r="57" ht="19.05" customHeight="1" s="127">
-      <c r="A57" s="279" t="inlineStr">
+      <c r="A57" s="379" t="inlineStr">
         <is>
           <t>Final</t>
         </is>
       </c>
       <c r="B57" s="94" t="n"/>
-      <c r="C57" s="281" t="n"/>
-      <c r="D57" s="281" t="n"/>
-      <c r="E57" s="281" t="n"/>
-      <c r="F57" s="94" t="n"/>
-      <c r="G57" s="281" t="n"/>
-      <c r="H57" s="281" t="n"/>
-      <c r="I57" s="279" t="n"/>
-      <c r="J57" s="104" t="n"/>
-      <c r="K57" s="104" t="n"/>
-      <c r="L57" s="104" t="n"/>
-      <c r="M57" s="94" t="n"/>
+      <c r="C57" s="380" t="n"/>
+      <c r="D57" s="380" t="n"/>
+      <c r="E57" s="380" t="n"/>
+      <c r="F57" s="381" t="n"/>
+      <c r="G57" s="380" t="n"/>
+      <c r="H57" s="380" t="n"/>
+      <c r="I57" s="382" t="n"/>
+      <c r="J57" s="383" t="n"/>
+      <c r="K57" s="383" t="n"/>
+      <c r="L57" s="383" t="n"/>
+      <c r="M57" s="381" t="n"/>
     </row>
     <row r="58" ht="16.05" customHeight="1" s="127">
       <c r="A58" s="267" t="inlineStr">
@@ -3608,16 +3712,16 @@
         </is>
       </c>
       <c r="B61" s="89" t="n"/>
-      <c r="C61" s="114" t="n"/>
-      <c r="D61" s="89" t="n"/>
+      <c r="C61" s="363" t="n"/>
+      <c r="D61" s="362" t="n"/>
       <c r="E61" s="122" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F61" s="89" t="n"/>
-      <c r="G61" s="114" t="n"/>
-      <c r="H61" s="89" t="n"/>
+      <c r="G61" s="363" t="n"/>
+      <c r="H61" s="362" t="n"/>
       <c r="I61" s="122" t="inlineStr">
         <is>
           <t>Firma:</t>
@@ -3635,25 +3739,25 @@
         </is>
       </c>
       <c r="B62" s="89" t="n"/>
-      <c r="C62" s="114" t="n"/>
-      <c r="D62" s="89" t="n"/>
+      <c r="C62" s="363" t="n"/>
+      <c r="D62" s="362" t="n"/>
       <c r="E62" s="122" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="F62" s="89" t="n"/>
-      <c r="G62" s="114" t="n"/>
-      <c r="H62" s="89" t="n"/>
+      <c r="G62" s="363" t="n"/>
+      <c r="H62" s="362" t="n"/>
       <c r="I62" s="122" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="J62" s="89" t="n"/>
-      <c r="K62" s="114" t="n"/>
-      <c r="L62" s="93" t="n"/>
-      <c r="M62" s="89" t="n"/>
+      <c r="K62" s="363" t="n"/>
+      <c r="L62" s="361" t="n"/>
+      <c r="M62" s="362" t="n"/>
     </row>
     <row r="63" ht="21" customHeight="1" s="127">
       <c r="A63" s="122" t="inlineStr">
@@ -3662,25 +3766,25 @@
         </is>
       </c>
       <c r="B63" s="89" t="n"/>
-      <c r="C63" s="114" t="n"/>
-      <c r="D63" s="89" t="n"/>
+      <c r="C63" s="363" t="n"/>
+      <c r="D63" s="362" t="n"/>
       <c r="E63" s="122" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="F63" s="89" t="n"/>
-      <c r="G63" s="114" t="n"/>
-      <c r="H63" s="89" t="n"/>
+      <c r="G63" s="363" t="n"/>
+      <c r="H63" s="362" t="n"/>
       <c r="I63" s="122" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="J63" s="89" t="n"/>
-      <c r="K63" s="114" t="n"/>
-      <c r="L63" s="93" t="n"/>
-      <c r="M63" s="89" t="n"/>
+      <c r="K63" s="363" t="n"/>
+      <c r="L63" s="361" t="n"/>
+      <c r="M63" s="362" t="n"/>
     </row>
     <row r="64" ht="21" customHeight="1" s="127">
       <c r="A64" s="122" t="inlineStr">
@@ -3689,25 +3793,25 @@
         </is>
       </c>
       <c r="B64" s="89" t="n"/>
-      <c r="C64" s="114" t="n"/>
-      <c r="D64" s="89" t="n"/>
+      <c r="C64" s="363" t="n"/>
+      <c r="D64" s="362" t="n"/>
       <c r="E64" s="122" t="inlineStr">
         <is>
           <t>Hora:</t>
         </is>
       </c>
       <c r="F64" s="89" t="n"/>
-      <c r="G64" s="114" t="n"/>
-      <c r="H64" s="89" t="n"/>
+      <c r="G64" s="363" t="n"/>
+      <c r="H64" s="362" t="n"/>
       <c r="I64" s="122" t="inlineStr">
         <is>
           <t>Hora:</t>
         </is>
       </c>
       <c r="J64" s="89" t="n"/>
-      <c r="K64" s="114" t="n"/>
-      <c r="L64" s="93" t="n"/>
-      <c r="M64" s="89" t="n"/>
+      <c r="K64" s="363" t="n"/>
+      <c r="L64" s="361" t="n"/>
+      <c r="M64" s="362" t="n"/>
     </row>
     <row r="65" ht="16.5" customHeight="1" s="127">
       <c r="A65" s="210" t="inlineStr">
@@ -3735,16 +3839,16 @@
         </is>
       </c>
       <c r="B66" s="89" t="n"/>
-      <c r="C66" s="115" t="n"/>
-      <c r="D66" s="89" t="n"/>
+      <c r="C66" s="364" t="n"/>
+      <c r="D66" s="362" t="n"/>
       <c r="E66" s="111" t="inlineStr">
         <is>
           <t>¿Trabajo terminado?</t>
         </is>
       </c>
       <c r="F66" s="89" t="n"/>
-      <c r="G66" s="115" t="n"/>
-      <c r="H66" s="89" t="n"/>
+      <c r="G66" s="364" t="n"/>
+      <c r="H66" s="362" t="n"/>
       <c r="I66" s="111" t="inlineStr">
         <is>
           <t>¿Área en orden y sin energía residual?</t>
@@ -3762,17 +3866,17 @@
         </is>
       </c>
       <c r="B67" s="89" t="n"/>
-      <c r="C67" s="116" t="n"/>
-      <c r="D67" s="93" t="n"/>
-      <c r="E67" s="93" t="n"/>
-      <c r="F67" s="93" t="n"/>
-      <c r="G67" s="93" t="n"/>
-      <c r="H67" s="93" t="n"/>
-      <c r="I67" s="93" t="n"/>
-      <c r="J67" s="93" t="n"/>
-      <c r="K67" s="93" t="n"/>
-      <c r="L67" s="93" t="n"/>
-      <c r="M67" s="89" t="n"/>
+      <c r="C67" s="365" t="n"/>
+      <c r="D67" s="361" t="n"/>
+      <c r="E67" s="361" t="n"/>
+      <c r="F67" s="361" t="n"/>
+      <c r="G67" s="361" t="n"/>
+      <c r="H67" s="361" t="n"/>
+      <c r="I67" s="361" t="n"/>
+      <c r="J67" s="361" t="n"/>
+      <c r="K67" s="361" t="n"/>
+      <c r="L67" s="361" t="n"/>
+      <c r="M67" s="362" t="n"/>
     </row>
     <row r="68" ht="24" customHeight="1" s="127">
       <c r="A68" s="282" t="inlineStr">
@@ -3781,17 +3885,17 @@
         </is>
       </c>
       <c r="B68" s="94" t="n"/>
-      <c r="C68" s="283" t="n"/>
-      <c r="D68" s="104" t="n"/>
-      <c r="E68" s="104" t="n"/>
-      <c r="F68" s="104" t="n"/>
-      <c r="G68" s="104" t="n"/>
-      <c r="H68" s="104" t="n"/>
-      <c r="I68" s="104" t="n"/>
-      <c r="J68" s="104" t="n"/>
-      <c r="K68" s="104" t="n"/>
-      <c r="L68" s="104" t="n"/>
-      <c r="M68" s="94" t="n"/>
+      <c r="C68" s="384" t="n"/>
+      <c r="D68" s="383" t="n"/>
+      <c r="E68" s="383" t="n"/>
+      <c r="F68" s="383" t="n"/>
+      <c r="G68" s="383" t="n"/>
+      <c r="H68" s="383" t="n"/>
+      <c r="I68" s="383" t="n"/>
+      <c r="J68" s="383" t="n"/>
+      <c r="K68" s="383" t="n"/>
+      <c r="L68" s="383" t="n"/>
+      <c r="M68" s="381" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1" s="127">
       <c r="A69" s="286" t="inlineStr">
@@ -3823,21 +3927,21 @@
         </is>
       </c>
       <c r="B70" s="97" t="n"/>
-      <c r="C70" s="285" t="n"/>
-      <c r="D70" s="98" t="n"/>
-      <c r="E70" s="98" t="n"/>
-      <c r="F70" s="97" t="n"/>
+      <c r="C70" s="378" t="n"/>
+      <c r="D70" s="368" t="n"/>
+      <c r="E70" s="368" t="n"/>
+      <c r="F70" s="369" t="n"/>
       <c r="G70" s="284" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="H70" s="97" t="n"/>
-      <c r="I70" s="285" t="n"/>
-      <c r="J70" s="98" t="n"/>
-      <c r="K70" s="98" t="n"/>
-      <c r="L70" s="98" t="n"/>
-      <c r="M70" s="97" t="n"/>
+      <c r="I70" s="378" t="n"/>
+      <c r="J70" s="368" t="n"/>
+      <c r="K70" s="368" t="n"/>
+      <c r="L70" s="368" t="n"/>
+      <c r="M70" s="369" t="n"/>
     </row>
     <row r="71" ht="21" customHeight="1" s="127">
       <c r="A71" s="122" t="inlineStr">
@@ -3846,21 +3950,21 @@
         </is>
       </c>
       <c r="B71" s="89" t="n"/>
-      <c r="C71" s="114" t="n"/>
-      <c r="D71" s="93" t="n"/>
-      <c r="E71" s="93" t="n"/>
-      <c r="F71" s="89" t="n"/>
+      <c r="C71" s="363" t="n"/>
+      <c r="D71" s="361" t="n"/>
+      <c r="E71" s="361" t="n"/>
+      <c r="F71" s="362" t="n"/>
       <c r="G71" s="122" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="H71" s="89" t="n"/>
-      <c r="I71" s="114" t="n"/>
-      <c r="J71" s="93" t="n"/>
-      <c r="K71" s="93" t="n"/>
-      <c r="L71" s="93" t="n"/>
-      <c r="M71" s="89" t="n"/>
+      <c r="I71" s="363" t="n"/>
+      <c r="J71" s="361" t="n"/>
+      <c r="K71" s="361" t="n"/>
+      <c r="L71" s="361" t="n"/>
+      <c r="M71" s="362" t="n"/>
     </row>
     <row r="72" ht="21" customHeight="1" s="127">
       <c r="A72" s="122" t="inlineStr">
@@ -3869,21 +3973,21 @@
         </is>
       </c>
       <c r="B72" s="89" t="n"/>
-      <c r="C72" s="114" t="n"/>
-      <c r="D72" s="93" t="n"/>
-      <c r="E72" s="93" t="n"/>
-      <c r="F72" s="89" t="n"/>
+      <c r="C72" s="363" t="n"/>
+      <c r="D72" s="361" t="n"/>
+      <c r="E72" s="361" t="n"/>
+      <c r="F72" s="362" t="n"/>
       <c r="G72" s="122" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="H72" s="89" t="n"/>
-      <c r="I72" s="114" t="n"/>
-      <c r="J72" s="93" t="n"/>
-      <c r="K72" s="93" t="n"/>
-      <c r="L72" s="93" t="n"/>
-      <c r="M72" s="89" t="n"/>
+      <c r="I72" s="363" t="n"/>
+      <c r="J72" s="361" t="n"/>
+      <c r="K72" s="361" t="n"/>
+      <c r="L72" s="361" t="n"/>
+      <c r="M72" s="362" t="n"/>
     </row>
     <row r="73"/>
     <row r="74">
@@ -3898,12 +4002,13 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="202">
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="D4:J4"/>
-    <mergeCell ref="A64:B64"/>
     <mergeCell ref="C62:D62"/>
     <mergeCell ref="K32:M32"/>
+    <mergeCell ref="A64:B64"/>
     <mergeCell ref="E62:F62"/>
     <mergeCell ref="K46:M46"/>
     <mergeCell ref="A15:B15"/>
